--- a/tedarikci-proses-kontrol-formu.xlsx
+++ b/tedarikci-proses-kontrol-formu.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="BuÇalışmaKitabı" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\FMEA\Hazırlananlar\Proses Kontrol Fomu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\Opencode\Akıs-fmea programi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAD1EDB-43FF-4098-AA24-CA283E7C107D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B44EBFF-779D-4726-84D3-727ED657A7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Günlük-1" sheetId="8" r:id="rId1"/>
@@ -217,7 +217,7 @@
     <definedName name="ZONE_INVISIBLE" localSheetId="1">#REF!</definedName>
     <definedName name="ZONE_INVISIBLE">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="52">
   <si>
     <t>Proses Adımları</t>
   </si>
@@ -894,54 +894,6 @@
   <si>
     <t>Döf No</t>
   </si>
-  <si>
-    <t>EMS</t>
-  </si>
-  <si>
-    <t>Genel</t>
-  </si>
-  <si>
-    <t>EMS FMEA Rev.06</t>
-  </si>
-  <si>
-    <t>GKK</t>
-  </si>
-  <si>
-    <t>Karantina / Etiket Kontrolü</t>
-  </si>
-  <si>
-    <t>Raf Ömrü (SKT) Kontrolü</t>
-  </si>
-  <si>
-    <t>Bulgu yok (Uygun) — Ref: IPC-A-610F / J-STD-001</t>
-  </si>
-  <si>
-    <t>Görsel</t>
-  </si>
-  <si>
-    <t>Uygunsuz/şüpheli malzemenin karantinada tutulması ve kırmızı etiket varlığı kontrol edilir.</t>
-  </si>
-  <si>
-    <t>Krem lehim ve kimyasal malzemelerde SKT/raf ömrü aşımı kontrol edilir.</t>
-  </si>
-  <si>
-    <t>Reflow / Fırınlama</t>
-  </si>
-  <si>
-    <t>Fırınlama Oksijyen/Azot seviyesi kontrolü</t>
-  </si>
-  <si>
-    <t>&lt;500 PPM</t>
-  </si>
-  <si>
-    <t>BS202</t>
-  </si>
-  <si>
-    <t>Basınç Ölçümü</t>
-  </si>
-  <si>
-    <t>Fırınlama Oksijyen/Azot seviyesinin 500 PPM  değerinden küçük olduğu kontrol edilir.</t>
-  </si>
 </sst>
 </file>
 
@@ -1840,6 +1792,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2056,7 +2012,7 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2071,6 +2027,10 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2088,6 +2048,22 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2348,30 +2324,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -3598,104 +3550,102 @@
       <c r="AD9" s="2"/>
     </row>
     <row r="11" spans="2:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="116" t="s">
+      <c r="B11" s="117" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="116"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="116"/>
-      <c r="F11" s="116"/>
-      <c r="G11" s="116"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="116"/>
-      <c r="J11" s="116"/>
-      <c r="K11" s="116"/>
-      <c r="L11" s="116"/>
-      <c r="M11" s="116"/>
-      <c r="N11" s="116"/>
-      <c r="O11" s="116"/>
-      <c r="P11" s="116"/>
-      <c r="Q11" s="116"/>
-      <c r="R11" s="116"/>
-      <c r="S11" s="116"/>
-      <c r="T11" s="116"/>
-      <c r="U11" s="116"/>
-      <c r="V11" s="116"/>
-      <c r="W11" s="116"/>
-      <c r="X11" s="116"/>
-      <c r="Y11" s="116"/>
-      <c r="Z11" s="116"/>
-      <c r="AA11" s="116"/>
-      <c r="AB11" s="116"/>
-      <c r="AC11" s="116"/>
-      <c r="AD11" s="117"/>
+      <c r="C11" s="117"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="117"/>
+      <c r="I11" s="117"/>
+      <c r="J11" s="117"/>
+      <c r="K11" s="117"/>
+      <c r="L11" s="117"/>
+      <c r="M11" s="117"/>
+      <c r="N11" s="117"/>
+      <c r="O11" s="117"/>
+      <c r="P11" s="117"/>
+      <c r="Q11" s="117"/>
+      <c r="R11" s="117"/>
+      <c r="S11" s="117"/>
+      <c r="T11" s="117"/>
+      <c r="U11" s="117"/>
+      <c r="V11" s="117"/>
+      <c r="W11" s="117"/>
+      <c r="X11" s="117"/>
+      <c r="Y11" s="117"/>
+      <c r="Z11" s="117"/>
+      <c r="AA11" s="117"/>
+      <c r="AB11" s="117"/>
+      <c r="AC11" s="117"/>
+      <c r="AD11" s="118"/>
     </row>
     <row r="12" spans="2:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="118"/>
-      <c r="C12" s="118"/>
-      <c r="D12" s="118"/>
-      <c r="E12" s="118"/>
-      <c r="F12" s="118"/>
-      <c r="G12" s="118"/>
-      <c r="H12" s="118"/>
-      <c r="I12" s="118"/>
-      <c r="J12" s="118"/>
-      <c r="K12" s="118"/>
-      <c r="L12" s="118"/>
-      <c r="M12" s="118"/>
-      <c r="N12" s="118"/>
-      <c r="O12" s="118"/>
-      <c r="P12" s="118"/>
-      <c r="Q12" s="118"/>
-      <c r="R12" s="118"/>
-      <c r="S12" s="118"/>
-      <c r="T12" s="118"/>
-      <c r="U12" s="118"/>
-      <c r="V12" s="118"/>
-      <c r="W12" s="118"/>
-      <c r="X12" s="118"/>
-      <c r="Y12" s="118"/>
-      <c r="Z12" s="118"/>
-      <c r="AA12" s="118"/>
-      <c r="AB12" s="118"/>
-      <c r="AC12" s="118"/>
-      <c r="AD12" s="119"/>
+      <c r="B12" s="119"/>
+      <c r="C12" s="119"/>
+      <c r="D12" s="119"/>
+      <c r="E12" s="119"/>
+      <c r="F12" s="119"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="119"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="119"/>
+      <c r="K12" s="119"/>
+      <c r="L12" s="119"/>
+      <c r="M12" s="119"/>
+      <c r="N12" s="119"/>
+      <c r="O12" s="119"/>
+      <c r="P12" s="119"/>
+      <c r="Q12" s="119"/>
+      <c r="R12" s="119"/>
+      <c r="S12" s="119"/>
+      <c r="T12" s="119"/>
+      <c r="U12" s="119"/>
+      <c r="V12" s="119"/>
+      <c r="W12" s="119"/>
+      <c r="X12" s="119"/>
+      <c r="Y12" s="119"/>
+      <c r="Z12" s="119"/>
+      <c r="AA12" s="119"/>
+      <c r="AB12" s="119"/>
+      <c r="AC12" s="119"/>
+      <c r="AD12" s="120"/>
     </row>
     <row r="13" spans="2:30" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="115"/>
-      <c r="D13" s="138" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="139"/>
-      <c r="F13" s="114" t="s">
+      <c r="C13" s="116"/>
+      <c r="D13" s="139" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="140"/>
+      <c r="F13" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="115"/>
-      <c r="H13" s="220" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="221"/>
-      <c r="J13" s="221"/>
-      <c r="K13" s="221"/>
-      <c r="L13" s="223"/>
+      <c r="G13" s="116"/>
+      <c r="H13" s="152"/>
+      <c r="I13" s="153"/>
+      <c r="J13" s="153"/>
+      <c r="K13" s="153"/>
+      <c r="L13" s="154"/>
       <c r="M13" s="5"/>
-      <c r="N13" s="141"/>
-      <c r="O13" s="141"/>
-      <c r="P13" s="141"/>
-      <c r="Q13" s="141"/>
-      <c r="R13" s="141"/>
-      <c r="S13" s="141"/>
-      <c r="T13" s="141"/>
-      <c r="U13" s="141"/>
-      <c r="V13" s="141"/>
-      <c r="W13" s="141"/>
-      <c r="X13" s="141"/>
-      <c r="Y13" s="141"/>
-      <c r="Z13" s="141"/>
-      <c r="AA13" s="141"/>
+      <c r="N13" s="142"/>
+      <c r="O13" s="142"/>
+      <c r="P13" s="142"/>
+      <c r="Q13" s="142"/>
+      <c r="R13" s="142"/>
+      <c r="S13" s="142"/>
+      <c r="T13" s="142"/>
+      <c r="U13" s="142"/>
+      <c r="V13" s="142"/>
+      <c r="W13" s="142"/>
+      <c r="X13" s="142"/>
+      <c r="Y13" s="142"/>
+      <c r="Z13" s="142"/>
+      <c r="AA13" s="142"/>
       <c r="AB13" s="6"/>
       <c r="AC13" s="7" t="s">
         <v>15</v>
@@ -3703,103 +3653,101 @@
       <c r="AD13" s="8"/>
     </row>
     <row r="14" spans="2:30" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="114" t="s">
+      <c r="B14" s="115" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="115"/>
-      <c r="D14" s="138" t="b">
+      <c r="C14" s="116"/>
+      <c r="D14" s="139" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="139"/>
-      <c r="F14" s="114" t="s">
+      <c r="E14" s="140"/>
+      <c r="F14" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="115"/>
-      <c r="H14" s="220" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="221"/>
-      <c r="J14" s="221"/>
-      <c r="K14" s="221"/>
-      <c r="L14" s="222"/>
+      <c r="G14" s="116"/>
+      <c r="H14" s="152"/>
+      <c r="I14" s="153"/>
+      <c r="J14" s="153"/>
+      <c r="K14" s="153"/>
+      <c r="L14" s="155"/>
       <c r="M14" s="9"/>
-      <c r="N14" s="142"/>
-      <c r="O14" s="142"/>
-      <c r="P14" s="142"/>
-      <c r="Q14" s="142"/>
-      <c r="R14" s="142"/>
-      <c r="S14" s="142"/>
-      <c r="T14" s="142"/>
-      <c r="U14" s="142"/>
-      <c r="V14" s="142"/>
-      <c r="W14" s="142"/>
-      <c r="X14" s="142"/>
-      <c r="Y14" s="142"/>
-      <c r="Z14" s="142"/>
-      <c r="AA14" s="142"/>
+      <c r="N14" s="143"/>
+      <c r="O14" s="143"/>
+      <c r="P14" s="143"/>
+      <c r="Q14" s="143"/>
+      <c r="R14" s="143"/>
+      <c r="S14" s="143"/>
+      <c r="T14" s="143"/>
+      <c r="U14" s="143"/>
+      <c r="V14" s="143"/>
+      <c r="W14" s="143"/>
+      <c r="X14" s="143"/>
+      <c r="Y14" s="143"/>
+      <c r="Z14" s="143"/>
+      <c r="AA14" s="143"/>
       <c r="AC14" s="10" t="s">
         <v>13</v>
       </c>
       <c r="AD14" s="8"/>
     </row>
     <row r="15" spans="2:30" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="129" t="s">
+      <c r="B15" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="130" t="s">
+      <c r="C15" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="132" t="s">
+      <c r="D15" s="133" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="133"/>
-      <c r="F15" s="132" t="s">
+      <c r="E15" s="134"/>
+      <c r="F15" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="144"/>
-      <c r="K15" s="145"/>
+      <c r="G15" s="156"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="146"/>
+      <c r="K15" s="147"/>
       <c r="L15" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="M15" s="143" t="s">
+      <c r="M15" s="144" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="143"/>
-      <c r="O15" s="143"/>
-      <c r="P15" s="143"/>
-      <c r="Q15" s="143"/>
-      <c r="R15" s="143"/>
-      <c r="S15" s="143"/>
-      <c r="T15" s="143"/>
-      <c r="U15" s="143"/>
-      <c r="V15" s="143"/>
-      <c r="W15" s="143"/>
-      <c r="X15" s="143"/>
-      <c r="Y15" s="143"/>
-      <c r="Z15" s="143"/>
-      <c r="AA15" s="143"/>
-      <c r="AB15" s="120" t="s">
+      <c r="N15" s="144"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="144"/>
+      <c r="S15" s="144"/>
+      <c r="T15" s="144"/>
+      <c r="U15" s="144"/>
+      <c r="V15" s="144"/>
+      <c r="W15" s="144"/>
+      <c r="X15" s="144"/>
+      <c r="Y15" s="144"/>
+      <c r="Z15" s="144"/>
+      <c r="AA15" s="144"/>
+      <c r="AB15" s="121" t="s">
         <v>51</v>
       </c>
-      <c r="AC15" s="123" t="s">
+      <c r="AC15" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="AD15" s="124"/>
+      <c r="AD15" s="125"/>
     </row>
     <row r="16" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="129"/>
-      <c r="C16" s="130"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="135"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="151"/>
-      <c r="H16" s="151"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="146"/>
-      <c r="K16" s="147"/>
+      <c r="B16" s="130"/>
+      <c r="C16" s="131"/>
+      <c r="D16" s="135"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="157"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="148"/>
+      <c r="K16" s="149"/>
       <c r="L16" s="68" t="s">
         <v>12</v>
       </c>
@@ -3820,21 +3768,21 @@
       <c r="Y16" s="69"/>
       <c r="Z16" s="69"/>
       <c r="AA16" s="69"/>
-      <c r="AB16" s="120"/>
-      <c r="AC16" s="125"/>
-      <c r="AD16" s="126"/>
+      <c r="AB16" s="121"/>
+      <c r="AC16" s="126"/>
+      <c r="AD16" s="127"/>
     </row>
     <row r="17" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="129"/>
-      <c r="C17" s="130"/>
-      <c r="D17" s="134"/>
-      <c r="E17" s="135"/>
-      <c r="F17" s="134"/>
-      <c r="G17" s="151"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="135"/>
-      <c r="J17" s="146"/>
-      <c r="K17" s="147"/>
+      <c r="B17" s="130"/>
+      <c r="C17" s="131"/>
+      <c r="D17" s="135"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="148"/>
+      <c r="K17" s="149"/>
       <c r="L17" s="70" t="s">
         <v>16</v>
       </c>
@@ -3855,21 +3803,21 @@
       <c r="Y17" s="67"/>
       <c r="Z17" s="67"/>
       <c r="AA17" s="67"/>
-      <c r="AB17" s="120"/>
-      <c r="AC17" s="125"/>
-      <c r="AD17" s="126"/>
+      <c r="AB17" s="121"/>
+      <c r="AC17" s="126"/>
+      <c r="AD17" s="127"/>
     </row>
     <row r="18" spans="2:34" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="129"/>
-      <c r="C18" s="130"/>
-      <c r="D18" s="136"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="136"/>
-      <c r="G18" s="152"/>
-      <c r="H18" s="152"/>
-      <c r="I18" s="137"/>
-      <c r="J18" s="148"/>
-      <c r="K18" s="149"/>
+      <c r="B18" s="130"/>
+      <c r="C18" s="131"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="138"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="158"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="150"/>
+      <c r="K18" s="151"/>
       <c r="L18" s="70" t="s">
         <v>17</v>
       </c>
@@ -3890,13 +3838,13 @@
       <c r="Y18" s="67"/>
       <c r="Z18" s="67"/>
       <c r="AA18" s="67"/>
-      <c r="AB18" s="120"/>
-      <c r="AC18" s="125"/>
-      <c r="AD18" s="126"/>
+      <c r="AB18" s="121"/>
+      <c r="AC18" s="126"/>
+      <c r="AD18" s="127"/>
     </row>
     <row r="19" spans="2:34" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="129"/>
-      <c r="C19" s="130"/>
+      <c r="B19" s="130"/>
+      <c r="C19" s="131"/>
       <c r="D19" s="65" t="s">
         <v>1</v>
       </c>
@@ -3915,11 +3863,11 @@
       <c r="I19" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="131" t="s">
+      <c r="J19" s="132" t="s">
         <v>29</v>
       </c>
-      <c r="K19" s="131"/>
-      <c r="L19" s="131"/>
+      <c r="K19" s="132"/>
+      <c r="L19" s="132"/>
       <c r="M19" s="71">
         <v>1</v>
       </c>
@@ -3965,40 +3913,24 @@
       <c r="AA19" s="71">
         <v>15</v>
       </c>
-      <c r="AB19" s="120"/>
-      <c r="AC19" s="127"/>
-      <c r="AD19" s="128"/>
+      <c r="AB19" s="121"/>
+      <c r="AC19" s="128"/>
+      <c r="AD19" s="129"/>
     </row>
     <row r="20" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="14">
         <v>1</v>
       </c>
-      <c r="C20" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="11">
-        <v>1</v>
-      </c>
-      <c r="E20" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="F20" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="G20" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="I20" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="J20" s="224" t="s">
-        <v>60</v>
-      </c>
-      <c r="K20" s="224"/>
-      <c r="L20" s="224"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="72"/>
+      <c r="J20" s="141"/>
+      <c r="K20" s="141"/>
+      <c r="L20" s="141"/>
       <c r="M20" s="19"/>
       <c r="N20" s="20"/>
       <c r="O20" s="20"/>
@@ -4015,39 +3947,23 @@
       <c r="Z20" s="20"/>
       <c r="AA20" s="20"/>
       <c r="AB20" s="54"/>
-      <c r="AC20" s="121"/>
-      <c r="AD20" s="122"/>
+      <c r="AC20" s="122"/>
+      <c r="AD20" s="123"/>
     </row>
     <row r="21" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="14">
         <v>2</v>
       </c>
-      <c r="C21" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="13">
-        <v>1</v>
-      </c>
-      <c r="E21" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="H21" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="I21" s="72" t="s">
-        <v>30</v>
-      </c>
-      <c r="J21" s="224" t="s">
-        <v>61</v>
-      </c>
-      <c r="K21" s="224"/>
-      <c r="L21" s="224"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="72"/>
+      <c r="J21" s="141"/>
+      <c r="K21" s="141"/>
+      <c r="L21" s="141"/>
       <c r="M21" s="21"/>
       <c r="N21" s="21"/>
       <c r="O21" s="21"/>
@@ -4064,39 +3980,23 @@
       <c r="Z21" s="21"/>
       <c r="AA21" s="21"/>
       <c r="AB21" s="54"/>
-      <c r="AC21" s="112"/>
-      <c r="AD21" s="113"/>
+      <c r="AC21" s="113"/>
+      <c r="AD21" s="114"/>
     </row>
     <row r="22" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="14">
         <v>3</v>
       </c>
-      <c r="C22" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="13">
-        <v>2</v>
-      </c>
-      <c r="E22" s="225" t="s">
-        <v>62</v>
-      </c>
-      <c r="F22" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="I22" s="72" t="s">
-        <v>65</v>
-      </c>
-      <c r="J22" s="112" t="s">
-        <v>67</v>
-      </c>
-      <c r="K22" s="140"/>
-      <c r="L22" s="113"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="72"/>
+      <c r="J22" s="113"/>
+      <c r="K22" s="145"/>
+      <c r="L22" s="114"/>
       <c r="M22" s="21"/>
       <c r="N22" s="21"/>
       <c r="O22" s="21"/>
@@ -4113,8 +4013,8 @@
       <c r="Z22" s="21"/>
       <c r="AA22" s="21"/>
       <c r="AB22" s="54"/>
-      <c r="AC22" s="112"/>
-      <c r="AD22" s="113"/>
+      <c r="AC22" s="113"/>
+      <c r="AD22" s="114"/>
     </row>
     <row r="23" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="14">
@@ -4127,9 +4027,9 @@
       <c r="G23" s="14"/>
       <c r="H23" s="12"/>
       <c r="I23" s="72"/>
-      <c r="J23" s="112"/>
-      <c r="K23" s="140"/>
-      <c r="L23" s="113"/>
+      <c r="J23" s="113"/>
+      <c r="K23" s="145"/>
+      <c r="L23" s="114"/>
       <c r="M23" s="21"/>
       <c r="N23" s="21"/>
       <c r="O23" s="21"/>
@@ -4146,8 +4046,8 @@
       <c r="Z23" s="21"/>
       <c r="AA23" s="21"/>
       <c r="AB23" s="54"/>
-      <c r="AC23" s="112"/>
-      <c r="AD23" s="113"/>
+      <c r="AC23" s="113"/>
+      <c r="AD23" s="114"/>
     </row>
     <row r="24" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="14">
@@ -4160,9 +4060,9 @@
       <c r="G24" s="14"/>
       <c r="H24" s="12"/>
       <c r="I24" s="72"/>
-      <c r="J24" s="112"/>
-      <c r="K24" s="140"/>
-      <c r="L24" s="113"/>
+      <c r="J24" s="113"/>
+      <c r="K24" s="145"/>
+      <c r="L24" s="114"/>
       <c r="M24" s="21"/>
       <c r="N24" s="21"/>
       <c r="O24" s="21"/>
@@ -4179,8 +4079,8 @@
       <c r="Z24" s="21"/>
       <c r="AA24" s="21"/>
       <c r="AB24" s="54"/>
-      <c r="AC24" s="112"/>
-      <c r="AD24" s="113"/>
+      <c r="AC24" s="113"/>
+      <c r="AD24" s="114"/>
     </row>
     <row r="25" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="14">
@@ -4193,9 +4093,9 @@
       <c r="G25" s="14"/>
       <c r="H25" s="12"/>
       <c r="I25" s="72"/>
-      <c r="J25" s="112"/>
-      <c r="K25" s="140"/>
-      <c r="L25" s="113"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="145"/>
+      <c r="L25" s="114"/>
       <c r="M25" s="21"/>
       <c r="N25" s="21"/>
       <c r="O25" s="21"/>
@@ -4212,8 +4112,8 @@
       <c r="Z25" s="21"/>
       <c r="AA25" s="21"/>
       <c r="AB25" s="54"/>
-      <c r="AC25" s="112"/>
-      <c r="AD25" s="113"/>
+      <c r="AC25" s="113"/>
+      <c r="AD25" s="114"/>
     </row>
     <row r="26" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="14">
@@ -4226,9 +4126,9 @@
       <c r="G26" s="14"/>
       <c r="H26" s="12"/>
       <c r="I26" s="72"/>
-      <c r="J26" s="112"/>
-      <c r="K26" s="140"/>
-      <c r="L26" s="113"/>
+      <c r="J26" s="113"/>
+      <c r="K26" s="145"/>
+      <c r="L26" s="114"/>
       <c r="M26" s="21"/>
       <c r="N26" s="21"/>
       <c r="O26" s="21"/>
@@ -4245,8 +4145,8 @@
       <c r="Z26" s="21"/>
       <c r="AA26" s="21"/>
       <c r="AB26" s="54"/>
-      <c r="AC26" s="112"/>
-      <c r="AD26" s="113"/>
+      <c r="AC26" s="113"/>
+      <c r="AD26" s="114"/>
       <c r="AG26" s="4" t="s">
         <v>19</v>
       </c>
@@ -4262,9 +4162,9 @@
       <c r="G27" s="14"/>
       <c r="H27" s="12"/>
       <c r="I27" s="72"/>
-      <c r="J27" s="112"/>
-      <c r="K27" s="140"/>
-      <c r="L27" s="113"/>
+      <c r="J27" s="113"/>
+      <c r="K27" s="145"/>
+      <c r="L27" s="114"/>
       <c r="M27" s="21"/>
       <c r="N27" s="21"/>
       <c r="O27" s="21"/>
@@ -4281,8 +4181,8 @@
       <c r="Z27" s="21"/>
       <c r="AA27" s="21"/>
       <c r="AB27" s="54"/>
-      <c r="AC27" s="112"/>
-      <c r="AD27" s="113"/>
+      <c r="AC27" s="113"/>
+      <c r="AD27" s="114"/>
       <c r="AG27" s="4" t="s">
         <v>20</v>
       </c>
@@ -4298,9 +4198,9 @@
       <c r="G28" s="14"/>
       <c r="H28" s="12"/>
       <c r="I28" s="72"/>
-      <c r="J28" s="112"/>
-      <c r="K28" s="140"/>
-      <c r="L28" s="113"/>
+      <c r="J28" s="113"/>
+      <c r="K28" s="145"/>
+      <c r="L28" s="114"/>
       <c r="M28" s="21"/>
       <c r="N28" s="21"/>
       <c r="O28" s="21"/>
@@ -4317,8 +4217,8 @@
       <c r="Z28" s="21"/>
       <c r="AA28" s="21"/>
       <c r="AB28" s="54"/>
-      <c r="AC28" s="112"/>
-      <c r="AD28" s="113"/>
+      <c r="AC28" s="113"/>
+      <c r="AD28" s="114"/>
       <c r="AG28" s="4" t="s">
         <v>25</v>
       </c>
@@ -4334,9 +4234,9 @@
       <c r="G29" s="14"/>
       <c r="H29" s="12"/>
       <c r="I29" s="72"/>
-      <c r="J29" s="112"/>
-      <c r="K29" s="140"/>
-      <c r="L29" s="113"/>
+      <c r="J29" s="113"/>
+      <c r="K29" s="145"/>
+      <c r="L29" s="114"/>
       <c r="M29" s="21"/>
       <c r="N29" s="21"/>
       <c r="O29" s="21"/>
@@ -4353,8 +4253,8 @@
       <c r="Z29" s="21"/>
       <c r="AA29" s="21"/>
       <c r="AB29" s="54"/>
-      <c r="AC29" s="112"/>
-      <c r="AD29" s="113"/>
+      <c r="AC29" s="113"/>
+      <c r="AD29" s="114"/>
     </row>
     <row r="30" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="14">
@@ -4367,9 +4267,9 @@
       <c r="G30" s="14"/>
       <c r="H30" s="12"/>
       <c r="I30" s="72"/>
-      <c r="J30" s="112"/>
-      <c r="K30" s="140"/>
-      <c r="L30" s="113"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="145"/>
+      <c r="L30" s="114"/>
       <c r="M30" s="21"/>
       <c r="N30" s="21"/>
       <c r="O30" s="21"/>
@@ -4386,8 +4286,8 @@
       <c r="Z30" s="21"/>
       <c r="AA30" s="21"/>
       <c r="AB30" s="54"/>
-      <c r="AC30" s="112"/>
-      <c r="AD30" s="113"/>
+      <c r="AC30" s="113"/>
+      <c r="AD30" s="114"/>
       <c r="AH30" s="15" t="s">
         <v>21</v>
       </c>
@@ -4403,9 +4303,9 @@
       <c r="G31" s="14"/>
       <c r="H31" s="12"/>
       <c r="I31" s="72"/>
-      <c r="J31" s="112"/>
-      <c r="K31" s="140"/>
-      <c r="L31" s="113"/>
+      <c r="J31" s="113"/>
+      <c r="K31" s="145"/>
+      <c r="L31" s="114"/>
       <c r="M31" s="21"/>
       <c r="N31" s="21"/>
       <c r="O31" s="21"/>
@@ -4422,8 +4322,8 @@
       <c r="Z31" s="21"/>
       <c r="AA31" s="21"/>
       <c r="AB31" s="54"/>
-      <c r="AC31" s="112"/>
-      <c r="AD31" s="113"/>
+      <c r="AC31" s="113"/>
+      <c r="AD31" s="114"/>
       <c r="AH31" s="15" t="s">
         <v>22</v>
       </c>
@@ -4439,9 +4339,9 @@
       <c r="G32" s="14"/>
       <c r="H32" s="12"/>
       <c r="I32" s="72"/>
-      <c r="J32" s="112"/>
-      <c r="K32" s="140"/>
-      <c r="L32" s="113"/>
+      <c r="J32" s="113"/>
+      <c r="K32" s="145"/>
+      <c r="L32" s="114"/>
       <c r="M32" s="21"/>
       <c r="N32" s="21"/>
       <c r="O32" s="21"/>
@@ -4458,8 +4358,8 @@
       <c r="Z32" s="21"/>
       <c r="AA32" s="21"/>
       <c r="AB32" s="54"/>
-      <c r="AC32" s="112"/>
-      <c r="AD32" s="113"/>
+      <c r="AC32" s="113"/>
+      <c r="AD32" s="114"/>
       <c r="AH32" s="15" t="s">
         <v>23</v>
       </c>
@@ -4475,9 +4375,9 @@
       <c r="G33" s="17"/>
       <c r="H33" s="12"/>
       <c r="I33" s="72"/>
-      <c r="J33" s="112"/>
-      <c r="K33" s="140"/>
-      <c r="L33" s="113"/>
+      <c r="J33" s="113"/>
+      <c r="K33" s="145"/>
+      <c r="L33" s="114"/>
       <c r="M33" s="22"/>
       <c r="N33" s="22"/>
       <c r="O33" s="22"/>
@@ -4494,8 +4394,8 @@
       <c r="Z33" s="22"/>
       <c r="AA33" s="22"/>
       <c r="AB33" s="55"/>
-      <c r="AC33" s="112"/>
-      <c r="AD33" s="113"/>
+      <c r="AC33" s="113"/>
+      <c r="AD33" s="114"/>
       <c r="AH33" s="15" t="s">
         <v>24</v>
       </c>
@@ -4511,9 +4411,9 @@
       <c r="G34" s="14"/>
       <c r="H34" s="12"/>
       <c r="I34" s="72"/>
-      <c r="J34" s="112"/>
-      <c r="K34" s="140"/>
-      <c r="L34" s="113"/>
+      <c r="J34" s="113"/>
+      <c r="K34" s="145"/>
+      <c r="L34" s="114"/>
       <c r="M34" s="21"/>
       <c r="N34" s="21"/>
       <c r="O34" s="21"/>
@@ -4530,8 +4430,8 @@
       <c r="Z34" s="21"/>
       <c r="AA34" s="21"/>
       <c r="AB34" s="54"/>
-      <c r="AC34" s="112"/>
-      <c r="AD34" s="113"/>
+      <c r="AC34" s="113"/>
+      <c r="AD34" s="114"/>
     </row>
     <row r="35" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="14">
@@ -4544,9 +4444,9 @@
       <c r="G35" s="14"/>
       <c r="H35" s="12"/>
       <c r="I35" s="72"/>
-      <c r="J35" s="112"/>
-      <c r="K35" s="140"/>
-      <c r="L35" s="113"/>
+      <c r="J35" s="113"/>
+      <c r="K35" s="145"/>
+      <c r="L35" s="114"/>
       <c r="M35" s="21"/>
       <c r="N35" s="21"/>
       <c r="O35" s="21"/>
@@ -4563,8 +4463,8 @@
       <c r="Z35" s="21"/>
       <c r="AA35" s="21"/>
       <c r="AB35" s="54"/>
-      <c r="AC35" s="112"/>
-      <c r="AD35" s="113"/>
+      <c r="AC35" s="113"/>
+      <c r="AD35" s="114"/>
     </row>
     <row r="36" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="14">
@@ -4577,9 +4477,9 @@
       <c r="G36" s="17"/>
       <c r="H36" s="12"/>
       <c r="I36" s="72"/>
-      <c r="J36" s="112"/>
-      <c r="K36" s="140"/>
-      <c r="L36" s="113"/>
+      <c r="J36" s="113"/>
+      <c r="K36" s="145"/>
+      <c r="L36" s="114"/>
       <c r="M36" s="22"/>
       <c r="N36" s="22"/>
       <c r="O36" s="22"/>
@@ -4596,8 +4496,8 @@
       <c r="Z36" s="22"/>
       <c r="AA36" s="22"/>
       <c r="AB36" s="55"/>
-      <c r="AC36" s="112"/>
-      <c r="AD36" s="113"/>
+      <c r="AC36" s="113"/>
+      <c r="AD36" s="114"/>
     </row>
     <row r="37" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="14">
@@ -4610,9 +4510,9 @@
       <c r="G37" s="14"/>
       <c r="H37" s="12"/>
       <c r="I37" s="72"/>
-      <c r="J37" s="112"/>
-      <c r="K37" s="140"/>
-      <c r="L37" s="113"/>
+      <c r="J37" s="113"/>
+      <c r="K37" s="145"/>
+      <c r="L37" s="114"/>
       <c r="M37" s="21"/>
       <c r="N37" s="21"/>
       <c r="O37" s="21"/>
@@ -4629,8 +4529,8 @@
       <c r="Z37" s="21"/>
       <c r="AA37" s="21"/>
       <c r="AB37" s="54"/>
-      <c r="AC37" s="112"/>
-      <c r="AD37" s="113"/>
+      <c r="AC37" s="113"/>
+      <c r="AD37" s="114"/>
     </row>
     <row r="38" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="14">
@@ -4643,9 +4543,9 @@
       <c r="G38" s="14"/>
       <c r="H38" s="12"/>
       <c r="I38" s="72"/>
-      <c r="J38" s="112"/>
-      <c r="K38" s="140"/>
-      <c r="L38" s="113"/>
+      <c r="J38" s="113"/>
+      <c r="K38" s="145"/>
+      <c r="L38" s="114"/>
       <c r="M38" s="21"/>
       <c r="N38" s="21"/>
       <c r="O38" s="21"/>
@@ -4662,8 +4562,8 @@
       <c r="Z38" s="21"/>
       <c r="AA38" s="21"/>
       <c r="AB38" s="54"/>
-      <c r="AC38" s="112"/>
-      <c r="AD38" s="113"/>
+      <c r="AC38" s="113"/>
+      <c r="AD38" s="114"/>
     </row>
     <row r="39" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="14">
@@ -4676,9 +4576,9 @@
       <c r="G39" s="17"/>
       <c r="H39" s="12"/>
       <c r="I39" s="72"/>
-      <c r="J39" s="112"/>
-      <c r="K39" s="140"/>
-      <c r="L39" s="113"/>
+      <c r="J39" s="113"/>
+      <c r="K39" s="145"/>
+      <c r="L39" s="114"/>
       <c r="M39" s="22"/>
       <c r="N39" s="22"/>
       <c r="O39" s="22"/>
@@ -4695,8 +4595,8 @@
       <c r="Z39" s="22"/>
       <c r="AA39" s="22"/>
       <c r="AB39" s="55"/>
-      <c r="AC39" s="112"/>
-      <c r="AD39" s="113"/>
+      <c r="AC39" s="113"/>
+      <c r="AD39" s="114"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
@@ -4877,210 +4777,210 @@
       <c r="AE9" s="23"/>
     </row>
     <row r="11" spans="2:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="161" t="s">
+      <c r="B11" s="167" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="161"/>
-      <c r="D11" s="161"/>
-      <c r="E11" s="161"/>
-      <c r="F11" s="161"/>
-      <c r="G11" s="161"/>
-      <c r="H11" s="161"/>
-      <c r="I11" s="161"/>
-      <c r="J11" s="161"/>
-      <c r="K11" s="161"/>
-      <c r="L11" s="161"/>
-      <c r="M11" s="161"/>
-      <c r="N11" s="161"/>
-      <c r="O11" s="161"/>
-      <c r="P11" s="161"/>
-      <c r="Q11" s="161"/>
-      <c r="R11" s="161"/>
-      <c r="S11" s="161"/>
-      <c r="T11" s="161"/>
-      <c r="U11" s="161"/>
-      <c r="V11" s="161"/>
-      <c r="W11" s="161"/>
-      <c r="X11" s="161"/>
-      <c r="Y11" s="161"/>
-      <c r="Z11" s="161"/>
-      <c r="AA11" s="161"/>
-      <c r="AB11" s="161"/>
-      <c r="AC11" s="161"/>
-      <c r="AD11" s="161"/>
-      <c r="AE11" s="162"/>
+      <c r="C11" s="167"/>
+      <c r="D11" s="167"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="167"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
+      <c r="J11" s="167"/>
+      <c r="K11" s="167"/>
+      <c r="L11" s="167"/>
+      <c r="M11" s="167"/>
+      <c r="N11" s="167"/>
+      <c r="O11" s="167"/>
+      <c r="P11" s="167"/>
+      <c r="Q11" s="167"/>
+      <c r="R11" s="167"/>
+      <c r="S11" s="167"/>
+      <c r="T11" s="167"/>
+      <c r="U11" s="167"/>
+      <c r="V11" s="167"/>
+      <c r="W11" s="167"/>
+      <c r="X11" s="167"/>
+      <c r="Y11" s="167"/>
+      <c r="Z11" s="167"/>
+      <c r="AA11" s="167"/>
+      <c r="AB11" s="167"/>
+      <c r="AC11" s="167"/>
+      <c r="AD11" s="167"/>
+      <c r="AE11" s="168"/>
     </row>
     <row r="12" spans="2:31" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="163"/>
-      <c r="C12" s="163"/>
-      <c r="D12" s="163"/>
-      <c r="E12" s="163"/>
-      <c r="F12" s="163"/>
-      <c r="G12" s="163"/>
-      <c r="H12" s="163"/>
-      <c r="I12" s="163"/>
-      <c r="J12" s="163"/>
-      <c r="K12" s="163"/>
-      <c r="L12" s="163"/>
-      <c r="M12" s="163"/>
-      <c r="N12" s="163"/>
-      <c r="O12" s="163"/>
-      <c r="P12" s="163"/>
-      <c r="Q12" s="163"/>
-      <c r="R12" s="163"/>
-      <c r="S12" s="163"/>
-      <c r="T12" s="163"/>
-      <c r="U12" s="163"/>
-      <c r="V12" s="163"/>
-      <c r="W12" s="163"/>
-      <c r="X12" s="163"/>
-      <c r="Y12" s="163"/>
-      <c r="Z12" s="163"/>
-      <c r="AA12" s="163"/>
-      <c r="AB12" s="163"/>
-      <c r="AC12" s="163"/>
-      <c r="AD12" s="163"/>
-      <c r="AE12" s="164"/>
+      <c r="B12" s="169"/>
+      <c r="C12" s="169"/>
+      <c r="D12" s="169"/>
+      <c r="E12" s="169"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="169"/>
+      <c r="H12" s="169"/>
+      <c r="I12" s="169"/>
+      <c r="J12" s="169"/>
+      <c r="K12" s="169"/>
+      <c r="L12" s="169"/>
+      <c r="M12" s="169"/>
+      <c r="N12" s="169"/>
+      <c r="O12" s="169"/>
+      <c r="P12" s="169"/>
+      <c r="Q12" s="169"/>
+      <c r="R12" s="169"/>
+      <c r="S12" s="169"/>
+      <c r="T12" s="169"/>
+      <c r="U12" s="169"/>
+      <c r="V12" s="169"/>
+      <c r="W12" s="169"/>
+      <c r="X12" s="169"/>
+      <c r="Y12" s="169"/>
+      <c r="Z12" s="169"/>
+      <c r="AA12" s="169"/>
+      <c r="AB12" s="169"/>
+      <c r="AC12" s="169"/>
+      <c r="AD12" s="169"/>
+      <c r="AE12" s="170"/>
     </row>
     <row r="13" spans="2:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="194" t="s">
+      <c r="B13" s="200" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="195"/>
-      <c r="D13" s="138" t="b">
+      <c r="C13" s="201"/>
+      <c r="D13" s="139" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="139"/>
-      <c r="F13" s="114" t="s">
+      <c r="E13" s="140"/>
+      <c r="F13" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="115"/>
-      <c r="H13" s="191"/>
-      <c r="I13" s="192"/>
-      <c r="J13" s="192"/>
-      <c r="K13" s="192"/>
-      <c r="L13" s="193"/>
+      <c r="G13" s="116"/>
+      <c r="H13" s="197"/>
+      <c r="I13" s="198"/>
+      <c r="J13" s="198"/>
+      <c r="K13" s="198"/>
+      <c r="L13" s="199"/>
       <c r="M13" s="26"/>
-      <c r="N13" s="165"/>
-      <c r="O13" s="165"/>
-      <c r="P13" s="165"/>
-      <c r="Q13" s="165"/>
-      <c r="R13" s="165"/>
-      <c r="S13" s="165"/>
-      <c r="T13" s="165"/>
-      <c r="U13" s="165"/>
-      <c r="V13" s="165"/>
-      <c r="W13" s="165"/>
-      <c r="X13" s="165"/>
-      <c r="Y13" s="165"/>
-      <c r="Z13" s="165"/>
-      <c r="AA13" s="165"/>
-      <c r="AB13" s="165"/>
-      <c r="AC13" s="166"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="171"/>
+      <c r="Q13" s="171"/>
+      <c r="R13" s="171"/>
+      <c r="S13" s="171"/>
+      <c r="T13" s="171"/>
+      <c r="U13" s="171"/>
+      <c r="V13" s="171"/>
+      <c r="W13" s="171"/>
+      <c r="X13" s="171"/>
+      <c r="Y13" s="171"/>
+      <c r="Z13" s="171"/>
+      <c r="AA13" s="171"/>
+      <c r="AB13" s="171"/>
+      <c r="AC13" s="172"/>
       <c r="AD13" s="27" t="s">
         <v>15</v>
       </c>
       <c r="AE13" s="28"/>
     </row>
     <row r="14" spans="2:31" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="194" t="s">
+      <c r="B14" s="200" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="195"/>
-      <c r="D14" s="138" t="b">
+      <c r="C14" s="201"/>
+      <c r="D14" s="139" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="139"/>
-      <c r="F14" s="114" t="s">
+      <c r="E14" s="140"/>
+      <c r="F14" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="115"/>
-      <c r="H14" s="191"/>
-      <c r="I14" s="192"/>
-      <c r="J14" s="192"/>
-      <c r="K14" s="192"/>
-      <c r="L14" s="193"/>
+      <c r="G14" s="116"/>
+      <c r="H14" s="197"/>
+      <c r="I14" s="198"/>
+      <c r="J14" s="198"/>
+      <c r="K14" s="198"/>
+      <c r="L14" s="199"/>
       <c r="M14" s="29"/>
-      <c r="N14" s="167"/>
-      <c r="O14" s="167"/>
-      <c r="P14" s="167"/>
-      <c r="Q14" s="167"/>
-      <c r="R14" s="167"/>
-      <c r="S14" s="167"/>
-      <c r="T14" s="167"/>
-      <c r="U14" s="167"/>
-      <c r="V14" s="167"/>
-      <c r="W14" s="167"/>
-      <c r="X14" s="167"/>
-      <c r="Y14" s="167"/>
-      <c r="Z14" s="167"/>
-      <c r="AA14" s="167"/>
-      <c r="AB14" s="167"/>
-      <c r="AC14" s="168"/>
+      <c r="N14" s="173"/>
+      <c r="O14" s="173"/>
+      <c r="P14" s="173"/>
+      <c r="Q14" s="173"/>
+      <c r="R14" s="173"/>
+      <c r="S14" s="173"/>
+      <c r="T14" s="173"/>
+      <c r="U14" s="173"/>
+      <c r="V14" s="173"/>
+      <c r="W14" s="173"/>
+      <c r="X14" s="173"/>
+      <c r="Y14" s="173"/>
+      <c r="Z14" s="173"/>
+      <c r="AA14" s="173"/>
+      <c r="AB14" s="173"/>
+      <c r="AC14" s="174"/>
       <c r="AD14" s="30" t="s">
         <v>13</v>
       </c>
       <c r="AE14" s="28"/>
     </row>
     <row r="15" spans="2:31" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="169" t="s">
+      <c r="B15" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="170" t="s">
+      <c r="C15" s="176" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="171" t="s">
+      <c r="D15" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="172"/>
-      <c r="F15" s="132" t="s">
+      <c r="E15" s="178"/>
+      <c r="F15" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="185"/>
-      <c r="K15" s="186"/>
+      <c r="G15" s="156"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="191"/>
+      <c r="K15" s="192"/>
       <c r="L15" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="M15" s="177" t="s">
+      <c r="M15" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="177"/>
-      <c r="O15" s="177"/>
-      <c r="P15" s="177"/>
-      <c r="Q15" s="177"/>
-      <c r="R15" s="177"/>
-      <c r="S15" s="177"/>
-      <c r="T15" s="177"/>
-      <c r="U15" s="177"/>
-      <c r="V15" s="177"/>
-      <c r="W15" s="177"/>
-      <c r="X15" s="177"/>
-      <c r="Y15" s="177"/>
-      <c r="Z15" s="177"/>
-      <c r="AA15" s="177"/>
-      <c r="AB15" s="177"/>
-      <c r="AC15" s="170" t="s">
+      <c r="N15" s="183"/>
+      <c r="O15" s="183"/>
+      <c r="P15" s="183"/>
+      <c r="Q15" s="183"/>
+      <c r="R15" s="183"/>
+      <c r="S15" s="183"/>
+      <c r="T15" s="183"/>
+      <c r="U15" s="183"/>
+      <c r="V15" s="183"/>
+      <c r="W15" s="183"/>
+      <c r="X15" s="183"/>
+      <c r="Y15" s="183"/>
+      <c r="Z15" s="183"/>
+      <c r="AA15" s="183"/>
+      <c r="AB15" s="183"/>
+      <c r="AC15" s="176" t="s">
         <v>51</v>
       </c>
-      <c r="AD15" s="178" t="s">
+      <c r="AD15" s="184" t="s">
         <v>10</v>
       </c>
-      <c r="AE15" s="179"/>
+      <c r="AE15" s="185"/>
     </row>
     <row r="16" spans="2:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="169"/>
-      <c r="C16" s="170"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="174"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="151"/>
-      <c r="H16" s="151"/>
-      <c r="I16" s="135"/>
-      <c r="J16" s="187"/>
-      <c r="K16" s="188"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="179"/>
+      <c r="E16" s="180"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="157"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="193"/>
+      <c r="K16" s="194"/>
       <c r="L16" s="60" t="s">
         <v>12</v>
       </c>
@@ -5100,21 +5000,21 @@
       <c r="Z16" s="64"/>
       <c r="AA16" s="64"/>
       <c r="AB16" s="64"/>
-      <c r="AC16" s="170"/>
-      <c r="AD16" s="180"/>
-      <c r="AE16" s="181"/>
+      <c r="AC16" s="176"/>
+      <c r="AD16" s="186"/>
+      <c r="AE16" s="187"/>
     </row>
     <row r="17" spans="2:35" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="169"/>
-      <c r="C17" s="170"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="174"/>
-      <c r="F17" s="134"/>
-      <c r="G17" s="151"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="135"/>
-      <c r="J17" s="187"/>
-      <c r="K17" s="188"/>
+      <c r="B17" s="175"/>
+      <c r="C17" s="176"/>
+      <c r="D17" s="179"/>
+      <c r="E17" s="180"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="136"/>
+      <c r="J17" s="193"/>
+      <c r="K17" s="194"/>
       <c r="L17" s="61" t="s">
         <v>16</v>
       </c>
@@ -5134,21 +5034,21 @@
       <c r="Z17" s="58"/>
       <c r="AA17" s="58"/>
       <c r="AB17" s="58"/>
-      <c r="AC17" s="170"/>
-      <c r="AD17" s="180"/>
-      <c r="AE17" s="181"/>
+      <c r="AC17" s="176"/>
+      <c r="AD17" s="186"/>
+      <c r="AE17" s="187"/>
     </row>
     <row r="18" spans="2:35" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="169"/>
-      <c r="C18" s="170"/>
-      <c r="D18" s="175"/>
-      <c r="E18" s="176"/>
-      <c r="F18" s="136"/>
-      <c r="G18" s="152"/>
-      <c r="H18" s="152"/>
-      <c r="I18" s="137"/>
-      <c r="J18" s="189"/>
-      <c r="K18" s="190"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="176"/>
+      <c r="D18" s="181"/>
+      <c r="E18" s="182"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="158"/>
+      <c r="I18" s="138"/>
+      <c r="J18" s="195"/>
+      <c r="K18" s="196"/>
       <c r="L18" s="61" t="s">
         <v>17</v>
       </c>
@@ -5168,13 +5068,13 @@
       <c r="Z18" s="58"/>
       <c r="AA18" s="58"/>
       <c r="AB18" s="58"/>
-      <c r="AC18" s="170"/>
-      <c r="AD18" s="180"/>
-      <c r="AE18" s="181"/>
+      <c r="AC18" s="176"/>
+      <c r="AD18" s="186"/>
+      <c r="AE18" s="187"/>
     </row>
     <row r="19" spans="2:35" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="169"/>
-      <c r="C19" s="170"/>
+      <c r="B19" s="175"/>
+      <c r="C19" s="176"/>
       <c r="D19" s="56" t="s">
         <v>1</v>
       </c>
@@ -5193,11 +5093,11 @@
       <c r="I19" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="184" t="s">
+      <c r="J19" s="190" t="s">
         <v>29</v>
       </c>
-      <c r="K19" s="184"/>
-      <c r="L19" s="184"/>
+      <c r="K19" s="190"/>
+      <c r="L19" s="190"/>
       <c r="M19" s="66">
         <v>16</v>
       </c>
@@ -5246,9 +5146,9 @@
       <c r="AB19" s="66">
         <v>31</v>
       </c>
-      <c r="AC19" s="170"/>
-      <c r="AD19" s="182"/>
-      <c r="AE19" s="183"/>
+      <c r="AC19" s="176"/>
+      <c r="AD19" s="188"/>
+      <c r="AE19" s="189"/>
     </row>
     <row r="20" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="36">
@@ -5261,9 +5161,9 @@
       <c r="G20" s="31"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="158"/>
-      <c r="K20" s="159"/>
-      <c r="L20" s="160"/>
+      <c r="J20" s="164"/>
+      <c r="K20" s="165"/>
+      <c r="L20" s="166"/>
       <c r="M20" s="32"/>
       <c r="N20" s="33"/>
       <c r="O20" s="33"/>
@@ -5281,8 +5181,8 @@
       <c r="AA20" s="33"/>
       <c r="AB20" s="33"/>
       <c r="AC20" s="34"/>
-      <c r="AD20" s="156"/>
-      <c r="AE20" s="157"/>
+      <c r="AD20" s="162"/>
+      <c r="AE20" s="163"/>
     </row>
     <row r="21" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="36">
@@ -5295,9 +5195,9 @@
       <c r="G21" s="36"/>
       <c r="H21" s="40"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="153"/>
-      <c r="K21" s="154"/>
-      <c r="L21" s="155"/>
+      <c r="J21" s="159"/>
+      <c r="K21" s="160"/>
+      <c r="L21" s="161"/>
       <c r="M21" s="37"/>
       <c r="N21" s="37"/>
       <c r="O21" s="37"/>
@@ -5315,8 +5215,8 @@
       <c r="AA21" s="37"/>
       <c r="AB21" s="37"/>
       <c r="AC21" s="38"/>
-      <c r="AD21" s="153"/>
-      <c r="AE21" s="155"/>
+      <c r="AD21" s="159"/>
+      <c r="AE21" s="161"/>
     </row>
     <row r="22" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="36">
@@ -5329,9 +5229,9 @@
       <c r="G22" s="36"/>
       <c r="H22" s="40"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="153"/>
-      <c r="K22" s="154"/>
-      <c r="L22" s="155"/>
+      <c r="J22" s="159"/>
+      <c r="K22" s="160"/>
+      <c r="L22" s="161"/>
       <c r="M22" s="37"/>
       <c r="N22" s="37"/>
       <c r="O22" s="37"/>
@@ -5349,8 +5249,8 @@
       <c r="AA22" s="37"/>
       <c r="AB22" s="37"/>
       <c r="AC22" s="38"/>
-      <c r="AD22" s="153"/>
-      <c r="AE22" s="155"/>
+      <c r="AD22" s="159"/>
+      <c r="AE22" s="161"/>
     </row>
     <row r="23" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="36">
@@ -5363,9 +5263,9 @@
       <c r="G23" s="36"/>
       <c r="H23" s="40"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="153"/>
-      <c r="K23" s="154"/>
-      <c r="L23" s="155"/>
+      <c r="J23" s="159"/>
+      <c r="K23" s="160"/>
+      <c r="L23" s="161"/>
       <c r="M23" s="37"/>
       <c r="N23" s="37"/>
       <c r="O23" s="37"/>
@@ -5383,8 +5283,8 @@
       <c r="AA23" s="37"/>
       <c r="AB23" s="37"/>
       <c r="AC23" s="38"/>
-      <c r="AD23" s="153"/>
-      <c r="AE23" s="155"/>
+      <c r="AD23" s="159"/>
+      <c r="AE23" s="161"/>
     </row>
     <row r="24" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="36">
@@ -5397,9 +5297,9 @@
       <c r="G24" s="36"/>
       <c r="H24" s="40"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="153"/>
-      <c r="K24" s="154"/>
-      <c r="L24" s="155"/>
+      <c r="J24" s="159"/>
+      <c r="K24" s="160"/>
+      <c r="L24" s="161"/>
       <c r="M24" s="37"/>
       <c r="N24" s="37"/>
       <c r="O24" s="37"/>
@@ -5417,8 +5317,8 @@
       <c r="AA24" s="37"/>
       <c r="AB24" s="37"/>
       <c r="AC24" s="38"/>
-      <c r="AD24" s="153"/>
-      <c r="AE24" s="155"/>
+      <c r="AD24" s="159"/>
+      <c r="AE24" s="161"/>
     </row>
     <row r="25" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="36">
@@ -5431,9 +5331,9 @@
       <c r="G25" s="36"/>
       <c r="H25" s="40"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="153"/>
-      <c r="K25" s="154"/>
-      <c r="L25" s="155"/>
+      <c r="J25" s="159"/>
+      <c r="K25" s="160"/>
+      <c r="L25" s="161"/>
       <c r="M25" s="37"/>
       <c r="N25" s="37"/>
       <c r="O25" s="37"/>
@@ -5451,8 +5351,8 @@
       <c r="AA25" s="37"/>
       <c r="AB25" s="37"/>
       <c r="AC25" s="38"/>
-      <c r="AD25" s="153"/>
-      <c r="AE25" s="155"/>
+      <c r="AD25" s="159"/>
+      <c r="AE25" s="161"/>
     </row>
     <row r="26" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="36">
@@ -5465,9 +5365,9 @@
       <c r="G26" s="36"/>
       <c r="H26" s="40"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="154"/>
-      <c r="L26" s="155"/>
+      <c r="J26" s="159"/>
+      <c r="K26" s="160"/>
+      <c r="L26" s="161"/>
       <c r="M26" s="37"/>
       <c r="N26" s="37"/>
       <c r="O26" s="37"/>
@@ -5485,8 +5385,8 @@
       <c r="AA26" s="37"/>
       <c r="AB26" s="37"/>
       <c r="AC26" s="38"/>
-      <c r="AD26" s="153"/>
-      <c r="AE26" s="155"/>
+      <c r="AD26" s="159"/>
+      <c r="AE26" s="161"/>
       <c r="AH26" s="25" t="s">
         <v>19</v>
       </c>
@@ -5502,9 +5402,9 @@
       <c r="G27" s="36"/>
       <c r="H27" s="40"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="154"/>
-      <c r="L27" s="155"/>
+      <c r="J27" s="159"/>
+      <c r="K27" s="160"/>
+      <c r="L27" s="161"/>
       <c r="M27" s="37"/>
       <c r="N27" s="37"/>
       <c r="O27" s="37"/>
@@ -5522,8 +5422,8 @@
       <c r="AA27" s="37"/>
       <c r="AB27" s="37"/>
       <c r="AC27" s="38"/>
-      <c r="AD27" s="153"/>
-      <c r="AE27" s="155"/>
+      <c r="AD27" s="159"/>
+      <c r="AE27" s="161"/>
       <c r="AH27" s="25" t="s">
         <v>20</v>
       </c>
@@ -5539,9 +5439,9 @@
       <c r="G28" s="36"/>
       <c r="H28" s="40"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="154"/>
-      <c r="L28" s="155"/>
+      <c r="J28" s="159"/>
+      <c r="K28" s="160"/>
+      <c r="L28" s="161"/>
       <c r="M28" s="37"/>
       <c r="N28" s="37"/>
       <c r="O28" s="37"/>
@@ -5559,8 +5459,8 @@
       <c r="AA28" s="37"/>
       <c r="AB28" s="37"/>
       <c r="AC28" s="38"/>
-      <c r="AD28" s="153"/>
-      <c r="AE28" s="155"/>
+      <c r="AD28" s="159"/>
+      <c r="AE28" s="161"/>
       <c r="AH28" s="25" t="s">
         <v>25</v>
       </c>
@@ -5576,9 +5476,9 @@
       <c r="G29" s="36"/>
       <c r="H29" s="40"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="154"/>
-      <c r="L29" s="155"/>
+      <c r="J29" s="159"/>
+      <c r="K29" s="160"/>
+      <c r="L29" s="161"/>
       <c r="M29" s="37"/>
       <c r="N29" s="37"/>
       <c r="O29" s="37"/>
@@ -5596,8 +5496,8 @@
       <c r="AA29" s="37"/>
       <c r="AB29" s="37"/>
       <c r="AC29" s="38"/>
-      <c r="AD29" s="153"/>
-      <c r="AE29" s="155"/>
+      <c r="AD29" s="159"/>
+      <c r="AE29" s="161"/>
     </row>
     <row r="30" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="36">
@@ -5610,9 +5510,9 @@
       <c r="G30" s="36"/>
       <c r="H30" s="40"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="153"/>
-      <c r="K30" s="154"/>
-      <c r="L30" s="155"/>
+      <c r="J30" s="159"/>
+      <c r="K30" s="160"/>
+      <c r="L30" s="161"/>
       <c r="M30" s="37"/>
       <c r="N30" s="37"/>
       <c r="O30" s="37"/>
@@ -5630,8 +5530,8 @@
       <c r="AA30" s="37"/>
       <c r="AB30" s="37"/>
       <c r="AC30" s="38"/>
-      <c r="AD30" s="153"/>
-      <c r="AE30" s="155"/>
+      <c r="AD30" s="159"/>
+      <c r="AE30" s="161"/>
       <c r="AI30" t="s">
         <v>21</v>
       </c>
@@ -5647,9 +5547,9 @@
       <c r="G31" s="36"/>
       <c r="H31" s="40"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="153"/>
-      <c r="K31" s="154"/>
-      <c r="L31" s="155"/>
+      <c r="J31" s="159"/>
+      <c r="K31" s="160"/>
+      <c r="L31" s="161"/>
       <c r="M31" s="37"/>
       <c r="N31" s="37"/>
       <c r="O31" s="37"/>
@@ -5667,8 +5567,8 @@
       <c r="AA31" s="37"/>
       <c r="AB31" s="37"/>
       <c r="AC31" s="38"/>
-      <c r="AD31" s="153"/>
-      <c r="AE31" s="155"/>
+      <c r="AD31" s="159"/>
+      <c r="AE31" s="161"/>
       <c r="AI31" t="s">
         <v>22</v>
       </c>
@@ -5684,9 +5584,9 @@
       <c r="G32" s="36"/>
       <c r="H32" s="40"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="153"/>
-      <c r="K32" s="154"/>
-      <c r="L32" s="155"/>
+      <c r="J32" s="159"/>
+      <c r="K32" s="160"/>
+      <c r="L32" s="161"/>
       <c r="M32" s="37"/>
       <c r="N32" s="37"/>
       <c r="O32" s="37"/>
@@ -5704,8 +5604,8 @@
       <c r="AA32" s="37"/>
       <c r="AB32" s="37"/>
       <c r="AC32" s="38"/>
-      <c r="AD32" s="153"/>
-      <c r="AE32" s="155"/>
+      <c r="AD32" s="159"/>
+      <c r="AE32" s="161"/>
       <c r="AI32" t="s">
         <v>23</v>
       </c>
@@ -5721,9 +5621,9 @@
       <c r="G33" s="40"/>
       <c r="H33" s="40"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="154"/>
-      <c r="L33" s="155"/>
+      <c r="J33" s="159"/>
+      <c r="K33" s="160"/>
+      <c r="L33" s="161"/>
       <c r="M33" s="41"/>
       <c r="N33" s="41"/>
       <c r="O33" s="41"/>
@@ -5741,8 +5641,8 @@
       <c r="AA33" s="41"/>
       <c r="AB33" s="41"/>
       <c r="AC33" s="42"/>
-      <c r="AD33" s="153"/>
-      <c r="AE33" s="155"/>
+      <c r="AD33" s="159"/>
+      <c r="AE33" s="161"/>
       <c r="AI33" t="s">
         <v>24</v>
       </c>
@@ -5758,9 +5658,9 @@
       <c r="G34" s="36"/>
       <c r="H34" s="40"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="153"/>
-      <c r="K34" s="154"/>
-      <c r="L34" s="155"/>
+      <c r="J34" s="159"/>
+      <c r="K34" s="160"/>
+      <c r="L34" s="161"/>
       <c r="M34" s="37"/>
       <c r="N34" s="37"/>
       <c r="O34" s="37"/>
@@ -5778,8 +5678,8 @@
       <c r="AA34" s="37"/>
       <c r="AB34" s="37"/>
       <c r="AC34" s="38"/>
-      <c r="AD34" s="153"/>
-      <c r="AE34" s="155"/>
+      <c r="AD34" s="159"/>
+      <c r="AE34" s="161"/>
     </row>
     <row r="35" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="36">
@@ -5792,9 +5692,9 @@
       <c r="G35" s="36"/>
       <c r="H35" s="40"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="153"/>
-      <c r="K35" s="154"/>
-      <c r="L35" s="155"/>
+      <c r="J35" s="159"/>
+      <c r="K35" s="160"/>
+      <c r="L35" s="161"/>
       <c r="M35" s="37"/>
       <c r="N35" s="37"/>
       <c r="O35" s="37"/>
@@ -5812,8 +5712,8 @@
       <c r="AA35" s="37"/>
       <c r="AB35" s="37"/>
       <c r="AC35" s="38"/>
-      <c r="AD35" s="153"/>
-      <c r="AE35" s="155"/>
+      <c r="AD35" s="159"/>
+      <c r="AE35" s="161"/>
     </row>
     <row r="36" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="36">
@@ -5826,9 +5726,9 @@
       <c r="G36" s="40"/>
       <c r="H36" s="40"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="153"/>
-      <c r="K36" s="154"/>
-      <c r="L36" s="155"/>
+      <c r="J36" s="159"/>
+      <c r="K36" s="160"/>
+      <c r="L36" s="161"/>
       <c r="M36" s="41"/>
       <c r="N36" s="41"/>
       <c r="O36" s="41"/>
@@ -5846,8 +5746,8 @@
       <c r="AA36" s="41"/>
       <c r="AB36" s="41"/>
       <c r="AC36" s="42"/>
-      <c r="AD36" s="153"/>
-      <c r="AE36" s="155"/>
+      <c r="AD36" s="159"/>
+      <c r="AE36" s="161"/>
     </row>
     <row r="37" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="36">
@@ -5860,9 +5760,9 @@
       <c r="G37" s="36"/>
       <c r="H37" s="40"/>
       <c r="I37" s="1"/>
-      <c r="J37" s="153"/>
-      <c r="K37" s="154"/>
-      <c r="L37" s="155"/>
+      <c r="J37" s="159"/>
+      <c r="K37" s="160"/>
+      <c r="L37" s="161"/>
       <c r="M37" s="37"/>
       <c r="N37" s="37"/>
       <c r="O37" s="37"/>
@@ -5880,8 +5780,8 @@
       <c r="AA37" s="37"/>
       <c r="AB37" s="37"/>
       <c r="AC37" s="38"/>
-      <c r="AD37" s="153"/>
-      <c r="AE37" s="155"/>
+      <c r="AD37" s="159"/>
+      <c r="AE37" s="161"/>
     </row>
     <row r="38" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="36">
@@ -5894,9 +5794,9 @@
       <c r="G38" s="36"/>
       <c r="H38" s="40"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="153"/>
-      <c r="K38" s="154"/>
-      <c r="L38" s="155"/>
+      <c r="J38" s="159"/>
+      <c r="K38" s="160"/>
+      <c r="L38" s="161"/>
       <c r="M38" s="37"/>
       <c r="N38" s="37"/>
       <c r="O38" s="37"/>
@@ -5914,8 +5814,8 @@
       <c r="AA38" s="37"/>
       <c r="AB38" s="37"/>
       <c r="AC38" s="38"/>
-      <c r="AD38" s="153"/>
-      <c r="AE38" s="155"/>
+      <c r="AD38" s="159"/>
+      <c r="AE38" s="161"/>
     </row>
     <row r="39" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="36">
@@ -5928,9 +5828,9 @@
       <c r="G39" s="40"/>
       <c r="H39" s="40"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="153"/>
-      <c r="K39" s="154"/>
-      <c r="L39" s="155"/>
+      <c r="J39" s="159"/>
+      <c r="K39" s="160"/>
+      <c r="L39" s="161"/>
       <c r="M39" s="41"/>
       <c r="N39" s="41"/>
       <c r="O39" s="41"/>
@@ -5948,8 +5848,8 @@
       <c r="AA39" s="41"/>
       <c r="AB39" s="41"/>
       <c r="AC39" s="42"/>
-      <c r="AD39" s="153"/>
-      <c r="AE39" s="155"/>
+      <c r="AD39" s="159"/>
+      <c r="AE39" s="161"/>
     </row>
     <row r="40" spans="2:35" ht="25.8" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
@@ -6107,73 +6007,73 @@
       <c r="R9" s="23"/>
     </row>
     <row r="11" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="161" t="s">
+      <c r="B11" s="167" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="161"/>
-      <c r="D11" s="161"/>
-      <c r="E11" s="161"/>
-      <c r="F11" s="161"/>
-      <c r="G11" s="161"/>
-      <c r="H11" s="161"/>
-      <c r="I11" s="161"/>
-      <c r="J11" s="161"/>
-      <c r="K11" s="161"/>
-      <c r="L11" s="161"/>
-      <c r="M11" s="161"/>
-      <c r="N11" s="161"/>
-      <c r="O11" s="161"/>
-      <c r="P11" s="161"/>
-      <c r="Q11" s="161"/>
-      <c r="R11" s="162"/>
+      <c r="C11" s="167"/>
+      <c r="D11" s="167"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="167"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
+      <c r="J11" s="167"/>
+      <c r="K11" s="167"/>
+      <c r="L11" s="167"/>
+      <c r="M11" s="167"/>
+      <c r="N11" s="167"/>
+      <c r="O11" s="167"/>
+      <c r="P11" s="167"/>
+      <c r="Q11" s="167"/>
+      <c r="R11" s="168"/>
       <c r="U11" s="25" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="163"/>
-      <c r="C12" s="163"/>
-      <c r="D12" s="163"/>
-      <c r="E12" s="163"/>
-      <c r="F12" s="163"/>
-      <c r="G12" s="163"/>
-      <c r="H12" s="163"/>
-      <c r="I12" s="163"/>
-      <c r="J12" s="163"/>
-      <c r="K12" s="163"/>
-      <c r="L12" s="163"/>
-      <c r="M12" s="163"/>
-      <c r="N12" s="163"/>
-      <c r="O12" s="163"/>
-      <c r="P12" s="163"/>
-      <c r="Q12" s="163"/>
-      <c r="R12" s="164"/>
+      <c r="B12" s="169"/>
+      <c r="C12" s="169"/>
+      <c r="D12" s="169"/>
+      <c r="E12" s="169"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="169"/>
+      <c r="H12" s="169"/>
+      <c r="I12" s="169"/>
+      <c r="J12" s="169"/>
+      <c r="K12" s="169"/>
+      <c r="L12" s="169"/>
+      <c r="M12" s="169"/>
+      <c r="N12" s="169"/>
+      <c r="O12" s="169"/>
+      <c r="P12" s="169"/>
+      <c r="Q12" s="169"/>
+      <c r="R12" s="170"/>
       <c r="U12" s="25" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="114" t="s">
+      <c r="B13" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="115"/>
-      <c r="D13" s="198" t="b">
+      <c r="C13" s="116"/>
+      <c r="D13" s="204" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="199"/>
-      <c r="F13" s="200" t="s">
+      <c r="E13" s="205"/>
+      <c r="F13" s="206" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="201"/>
-      <c r="H13" s="206"/>
-      <c r="I13" s="207"/>
-      <c r="J13" s="208"/>
-      <c r="K13" s="196"/>
-      <c r="L13" s="165"/>
-      <c r="M13" s="165"/>
-      <c r="N13" s="165"/>
-      <c r="O13" s="165"/>
-      <c r="P13" s="166"/>
+      <c r="G13" s="207"/>
+      <c r="H13" s="212"/>
+      <c r="I13" s="213"/>
+      <c r="J13" s="214"/>
+      <c r="K13" s="202"/>
+      <c r="L13" s="171"/>
+      <c r="M13" s="171"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="172"/>
       <c r="Q13" s="53" t="s">
         <v>15</v>
       </c>
@@ -6183,79 +6083,79 @@
       </c>
     </row>
     <row r="14" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="114" t="s">
+      <c r="B14" s="115" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="115"/>
-      <c r="D14" s="198" t="b">
+      <c r="C14" s="116"/>
+      <c r="D14" s="204" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="199"/>
+      <c r="E14" s="205"/>
       <c r="F14" s="51" t="s">
         <v>11</v>
       </c>
       <c r="G14" s="52"/>
-      <c r="H14" s="209"/>
-      <c r="I14" s="210"/>
-      <c r="J14" s="211"/>
-      <c r="K14" s="197"/>
-      <c r="L14" s="167"/>
-      <c r="M14" s="167"/>
-      <c r="N14" s="167"/>
-      <c r="O14" s="167"/>
-      <c r="P14" s="168"/>
+      <c r="H14" s="215"/>
+      <c r="I14" s="216"/>
+      <c r="J14" s="217"/>
+      <c r="K14" s="203"/>
+      <c r="L14" s="173"/>
+      <c r="M14" s="173"/>
+      <c r="N14" s="173"/>
+      <c r="O14" s="173"/>
+      <c r="P14" s="174"/>
       <c r="Q14" s="53" t="s">
         <v>35</v>
       </c>
       <c r="R14" s="28"/>
     </row>
     <row r="15" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="169" t="s">
+      <c r="B15" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="170" t="s">
+      <c r="C15" s="176" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="171" t="s">
+      <c r="D15" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="172"/>
-      <c r="F15" s="132" t="s">
+      <c r="E15" s="178"/>
+      <c r="F15" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="133"/>
+      <c r="G15" s="156"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="134"/>
       <c r="J15" s="62"/>
       <c r="K15" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="L15" s="177" t="s">
+      <c r="L15" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="177"/>
-      <c r="N15" s="177"/>
-      <c r="O15" s="177"/>
-      <c r="P15" s="170" t="s">
+      <c r="M15" s="183"/>
+      <c r="N15" s="183"/>
+      <c r="O15" s="183"/>
+      <c r="P15" s="176" t="s">
         <v>51</v>
       </c>
-      <c r="Q15" s="204" t="s">
+      <c r="Q15" s="210" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="179"/>
+      <c r="R15" s="185"/>
       <c r="V15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="169"/>
-      <c r="C16" s="170"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="174"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="151"/>
-      <c r="H16" s="151"/>
-      <c r="I16" s="135"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="179"/>
+      <c r="E16" s="180"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="157"/>
+      <c r="I16" s="136"/>
       <c r="J16" s="63"/>
       <c r="K16" s="60" t="s">
         <v>12</v>
@@ -6264,22 +6164,22 @@
       <c r="M16" s="64"/>
       <c r="N16" s="64"/>
       <c r="O16" s="64"/>
-      <c r="P16" s="170"/>
-      <c r="Q16" s="205"/>
-      <c r="R16" s="181"/>
+      <c r="P16" s="176"/>
+      <c r="Q16" s="211"/>
+      <c r="R16" s="187"/>
       <c r="V16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="169"/>
-      <c r="C17" s="170"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="174"/>
-      <c r="F17" s="134"/>
-      <c r="G17" s="151"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="135"/>
+      <c r="B17" s="175"/>
+      <c r="C17" s="176"/>
+      <c r="D17" s="179"/>
+      <c r="E17" s="180"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="136"/>
       <c r="J17" s="63"/>
       <c r="K17" s="61" t="s">
         <v>16</v>
@@ -6288,22 +6188,22 @@
       <c r="M17" s="64"/>
       <c r="N17" s="64"/>
       <c r="O17" s="64"/>
-      <c r="P17" s="170"/>
-      <c r="Q17" s="205"/>
-      <c r="R17" s="181"/>
+      <c r="P17" s="176"/>
+      <c r="Q17" s="211"/>
+      <c r="R17" s="187"/>
       <c r="V17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="169"/>
-      <c r="C18" s="170"/>
-      <c r="D18" s="175"/>
-      <c r="E18" s="176"/>
-      <c r="F18" s="136"/>
-      <c r="G18" s="152"/>
-      <c r="H18" s="152"/>
-      <c r="I18" s="137"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="176"/>
+      <c r="D18" s="181"/>
+      <c r="E18" s="182"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="158"/>
+      <c r="I18" s="138"/>
       <c r="J18" s="63"/>
       <c r="K18" s="61" t="s">
         <v>17</v>
@@ -6312,16 +6212,16 @@
       <c r="M18" s="64"/>
       <c r="N18" s="64"/>
       <c r="O18" s="64"/>
-      <c r="P18" s="170"/>
-      <c r="Q18" s="205"/>
-      <c r="R18" s="181"/>
+      <c r="P18" s="176"/>
+      <c r="Q18" s="211"/>
+      <c r="R18" s="187"/>
       <c r="V18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="169"/>
-      <c r="C19" s="170"/>
+      <c r="B19" s="175"/>
+      <c r="C19" s="176"/>
       <c r="D19" s="56" t="s">
         <v>1</v>
       </c>
@@ -6340,10 +6240,10 @@
       <c r="I19" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="202" t="s">
+      <c r="J19" s="208" t="s">
         <v>29</v>
       </c>
-      <c r="K19" s="203"/>
+      <c r="K19" s="209"/>
       <c r="L19" s="66">
         <v>1</v>
       </c>
@@ -6356,9 +6256,9 @@
       <c r="O19" s="66">
         <v>4</v>
       </c>
-      <c r="P19" s="170"/>
-      <c r="Q19" s="182"/>
-      <c r="R19" s="183"/>
+      <c r="P19" s="176"/>
+      <c r="Q19" s="188"/>
+      <c r="R19" s="189"/>
     </row>
     <row r="20" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="36">
@@ -6371,15 +6271,15 @@
       <c r="G20" s="36"/>
       <c r="H20" s="36"/>
       <c r="I20" s="45"/>
-      <c r="J20" s="153"/>
-      <c r="K20" s="155"/>
+      <c r="J20" s="159"/>
+      <c r="K20" s="161"/>
       <c r="L20" s="46"/>
       <c r="M20" s="46"/>
       <c r="N20" s="46"/>
       <c r="O20" s="46"/>
       <c r="P20" s="49"/>
-      <c r="Q20" s="153"/>
-      <c r="R20" s="155"/>
+      <c r="Q20" s="159"/>
+      <c r="R20" s="161"/>
     </row>
     <row r="21" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="36">
@@ -6392,15 +6292,15 @@
       <c r="G21" s="36"/>
       <c r="H21" s="36"/>
       <c r="I21" s="45"/>
-      <c r="J21" s="153"/>
-      <c r="K21" s="155"/>
+      <c r="J21" s="159"/>
+      <c r="K21" s="161"/>
       <c r="L21" s="46"/>
       <c r="M21" s="46"/>
       <c r="N21" s="46"/>
       <c r="O21" s="46"/>
       <c r="P21" s="49"/>
-      <c r="Q21" s="153"/>
-      <c r="R21" s="155"/>
+      <c r="Q21" s="159"/>
+      <c r="R21" s="161"/>
     </row>
     <row r="22" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="36">
@@ -6413,15 +6313,15 @@
       <c r="G22" s="36"/>
       <c r="H22" s="36"/>
       <c r="I22" s="45"/>
-      <c r="J22" s="153"/>
-      <c r="K22" s="155"/>
+      <c r="J22" s="159"/>
+      <c r="K22" s="161"/>
       <c r="L22" s="46"/>
       <c r="M22" s="46"/>
       <c r="N22" s="46"/>
       <c r="O22" s="46"/>
       <c r="P22" s="49"/>
-      <c r="Q22" s="153"/>
-      <c r="R22" s="155"/>
+      <c r="Q22" s="159"/>
+      <c r="R22" s="161"/>
     </row>
     <row r="23" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="36">
@@ -6434,15 +6334,15 @@
       <c r="G23" s="36"/>
       <c r="H23" s="36"/>
       <c r="I23" s="45"/>
-      <c r="J23" s="153"/>
-      <c r="K23" s="155"/>
+      <c r="J23" s="159"/>
+      <c r="K23" s="161"/>
       <c r="L23" s="46"/>
       <c r="M23" s="46"/>
       <c r="N23" s="46"/>
       <c r="O23" s="46"/>
       <c r="P23" s="49"/>
-      <c r="Q23" s="153"/>
-      <c r="R23" s="155"/>
+      <c r="Q23" s="159"/>
+      <c r="R23" s="161"/>
     </row>
     <row r="24" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="36">
@@ -6455,15 +6355,15 @@
       <c r="G24" s="36"/>
       <c r="H24" s="36"/>
       <c r="I24" s="45"/>
-      <c r="J24" s="153"/>
-      <c r="K24" s="155"/>
+      <c r="J24" s="159"/>
+      <c r="K24" s="161"/>
       <c r="L24" s="46"/>
       <c r="M24" s="46"/>
       <c r="N24" s="46"/>
       <c r="O24" s="46"/>
       <c r="P24" s="49"/>
-      <c r="Q24" s="153"/>
-      <c r="R24" s="155"/>
+      <c r="Q24" s="159"/>
+      <c r="R24" s="161"/>
     </row>
     <row r="25" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="36">
@@ -6476,15 +6376,15 @@
       <c r="G25" s="36"/>
       <c r="H25" s="36"/>
       <c r="I25" s="45"/>
-      <c r="J25" s="153"/>
-      <c r="K25" s="155"/>
+      <c r="J25" s="159"/>
+      <c r="K25" s="161"/>
       <c r="L25" s="46"/>
       <c r="M25" s="46"/>
       <c r="N25" s="46"/>
       <c r="O25" s="46"/>
       <c r="P25" s="49"/>
-      <c r="Q25" s="153"/>
-      <c r="R25" s="155"/>
+      <c r="Q25" s="159"/>
+      <c r="R25" s="161"/>
     </row>
     <row r="26" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="36">
@@ -6497,15 +6397,15 @@
       <c r="G26" s="36"/>
       <c r="H26" s="36"/>
       <c r="I26" s="45"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="155"/>
+      <c r="J26" s="159"/>
+      <c r="K26" s="161"/>
       <c r="L26" s="46"/>
       <c r="M26" s="46"/>
       <c r="N26" s="46"/>
       <c r="O26" s="46"/>
       <c r="P26" s="49"/>
-      <c r="Q26" s="153"/>
-      <c r="R26" s="155"/>
+      <c r="Q26" s="159"/>
+      <c r="R26" s="161"/>
     </row>
     <row r="27" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="36">
@@ -6518,15 +6418,15 @@
       <c r="G27" s="36"/>
       <c r="H27" s="36"/>
       <c r="I27" s="45"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="155"/>
+      <c r="J27" s="159"/>
+      <c r="K27" s="161"/>
       <c r="L27" s="46"/>
       <c r="M27" s="46"/>
       <c r="N27" s="46"/>
       <c r="O27" s="46"/>
       <c r="P27" s="49"/>
-      <c r="Q27" s="153"/>
-      <c r="R27" s="155"/>
+      <c r="Q27" s="159"/>
+      <c r="R27" s="161"/>
     </row>
     <row r="28" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="36">
@@ -6539,15 +6439,15 @@
       <c r="G28" s="36"/>
       <c r="H28" s="36"/>
       <c r="I28" s="45"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="155"/>
+      <c r="J28" s="159"/>
+      <c r="K28" s="161"/>
       <c r="L28" s="46"/>
       <c r="M28" s="46"/>
       <c r="N28" s="46"/>
       <c r="O28" s="46"/>
       <c r="P28" s="49"/>
-      <c r="Q28" s="153"/>
-      <c r="R28" s="155"/>
+      <c r="Q28" s="159"/>
+      <c r="R28" s="161"/>
     </row>
     <row r="29" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="36">
@@ -6560,15 +6460,15 @@
       <c r="G29" s="36"/>
       <c r="H29" s="36"/>
       <c r="I29" s="45"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="155"/>
+      <c r="J29" s="159"/>
+      <c r="K29" s="161"/>
       <c r="L29" s="46"/>
       <c r="M29" s="46"/>
       <c r="N29" s="46"/>
       <c r="O29" s="46"/>
       <c r="P29" s="49"/>
-      <c r="Q29" s="153"/>
-      <c r="R29" s="155"/>
+      <c r="Q29" s="159"/>
+      <c r="R29" s="161"/>
     </row>
     <row r="30" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="36">
@@ -6581,15 +6481,15 @@
       <c r="G30" s="36"/>
       <c r="H30" s="36"/>
       <c r="I30" s="45"/>
-      <c r="J30" s="153"/>
-      <c r="K30" s="155"/>
+      <c r="J30" s="159"/>
+      <c r="K30" s="161"/>
       <c r="L30" s="46"/>
       <c r="M30" s="46"/>
       <c r="N30" s="46"/>
       <c r="O30" s="46"/>
       <c r="P30" s="49"/>
-      <c r="Q30" s="153"/>
-      <c r="R30" s="155"/>
+      <c r="Q30" s="159"/>
+      <c r="R30" s="161"/>
     </row>
     <row r="31" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="36">
@@ -6602,15 +6502,15 @@
       <c r="G31" s="36"/>
       <c r="H31" s="36"/>
       <c r="I31" s="45"/>
-      <c r="J31" s="153"/>
-      <c r="K31" s="155"/>
+      <c r="J31" s="159"/>
+      <c r="K31" s="161"/>
       <c r="L31" s="46"/>
       <c r="M31" s="46"/>
       <c r="N31" s="46"/>
       <c r="O31" s="46"/>
       <c r="P31" s="49"/>
-      <c r="Q31" s="153"/>
-      <c r="R31" s="155"/>
+      <c r="Q31" s="159"/>
+      <c r="R31" s="161"/>
     </row>
     <row r="32" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="36">
@@ -6623,15 +6523,15 @@
       <c r="G32" s="40"/>
       <c r="H32" s="40"/>
       <c r="I32" s="47"/>
-      <c r="J32" s="153"/>
-      <c r="K32" s="155"/>
+      <c r="J32" s="159"/>
+      <c r="K32" s="161"/>
       <c r="L32" s="48"/>
       <c r="M32" s="48"/>
       <c r="N32" s="48"/>
       <c r="O32" s="48"/>
       <c r="P32" s="50"/>
-      <c r="Q32" s="153"/>
-      <c r="R32" s="155"/>
+      <c r="Q32" s="159"/>
+      <c r="R32" s="161"/>
     </row>
     <row r="33" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="36">
@@ -6644,15 +6544,15 @@
       <c r="G33" s="36"/>
       <c r="H33" s="36"/>
       <c r="I33" s="45"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="155"/>
+      <c r="J33" s="159"/>
+      <c r="K33" s="161"/>
       <c r="L33" s="46"/>
       <c r="M33" s="46"/>
       <c r="N33" s="46"/>
       <c r="O33" s="46"/>
       <c r="P33" s="49"/>
-      <c r="Q33" s="153"/>
-      <c r="R33" s="155"/>
+      <c r="Q33" s="159"/>
+      <c r="R33" s="161"/>
     </row>
     <row r="34" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="36">
@@ -6665,15 +6565,15 @@
       <c r="G34" s="36"/>
       <c r="H34" s="36"/>
       <c r="I34" s="45"/>
-      <c r="J34" s="153"/>
-      <c r="K34" s="155"/>
+      <c r="J34" s="159"/>
+      <c r="K34" s="161"/>
       <c r="L34" s="46"/>
       <c r="M34" s="46"/>
       <c r="N34" s="46"/>
       <c r="O34" s="46"/>
       <c r="P34" s="49"/>
-      <c r="Q34" s="153"/>
-      <c r="R34" s="155"/>
+      <c r="Q34" s="159"/>
+      <c r="R34" s="161"/>
     </row>
     <row r="35" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="36">
@@ -6686,15 +6586,15 @@
       <c r="G35" s="40"/>
       <c r="H35" s="40"/>
       <c r="I35" s="47"/>
-      <c r="J35" s="153"/>
-      <c r="K35" s="155"/>
+      <c r="J35" s="159"/>
+      <c r="K35" s="161"/>
       <c r="L35" s="48"/>
       <c r="M35" s="48"/>
       <c r="N35" s="48"/>
       <c r="O35" s="48"/>
       <c r="P35" s="50"/>
-      <c r="Q35" s="153"/>
-      <c r="R35" s="155"/>
+      <c r="Q35" s="159"/>
+      <c r="R35" s="161"/>
     </row>
     <row r="36" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="36">
@@ -6707,15 +6607,15 @@
       <c r="G36" s="36"/>
       <c r="H36" s="36"/>
       <c r="I36" s="45"/>
-      <c r="J36" s="153"/>
-      <c r="K36" s="155"/>
+      <c r="J36" s="159"/>
+      <c r="K36" s="161"/>
       <c r="L36" s="46"/>
       <c r="M36" s="46"/>
       <c r="N36" s="46"/>
       <c r="O36" s="46"/>
       <c r="P36" s="49"/>
-      <c r="Q36" s="153"/>
-      <c r="R36" s="155"/>
+      <c r="Q36" s="159"/>
+      <c r="R36" s="161"/>
     </row>
     <row r="37" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="36">
@@ -6728,15 +6628,15 @@
       <c r="G37" s="36"/>
       <c r="H37" s="36"/>
       <c r="I37" s="45"/>
-      <c r="J37" s="153"/>
-      <c r="K37" s="155"/>
+      <c r="J37" s="159"/>
+      <c r="K37" s="161"/>
       <c r="L37" s="46"/>
       <c r="M37" s="46"/>
       <c r="N37" s="46"/>
       <c r="O37" s="46"/>
       <c r="P37" s="49"/>
-      <c r="Q37" s="153"/>
-      <c r="R37" s="155"/>
+      <c r="Q37" s="159"/>
+      <c r="R37" s="161"/>
     </row>
     <row r="38" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="36">
@@ -6749,15 +6649,15 @@
       <c r="G38" s="40"/>
       <c r="H38" s="40"/>
       <c r="I38" s="47"/>
-      <c r="J38" s="153"/>
-      <c r="K38" s="155"/>
+      <c r="J38" s="159"/>
+      <c r="K38" s="161"/>
       <c r="L38" s="48"/>
       <c r="M38" s="48"/>
       <c r="N38" s="48"/>
       <c r="O38" s="48"/>
       <c r="P38" s="50"/>
-      <c r="Q38" s="153"/>
-      <c r="R38" s="155"/>
+      <c r="Q38" s="159"/>
+      <c r="R38" s="161"/>
     </row>
     <row r="39" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="36">
@@ -6770,15 +6670,15 @@
       <c r="G39" s="36"/>
       <c r="H39" s="36"/>
       <c r="I39" s="45"/>
-      <c r="J39" s="153"/>
-      <c r="K39" s="155"/>
+      <c r="J39" s="159"/>
+      <c r="K39" s="161"/>
       <c r="L39" s="46"/>
       <c r="M39" s="46"/>
       <c r="N39" s="46"/>
       <c r="O39" s="46"/>
       <c r="P39" s="49"/>
-      <c r="Q39" s="153"/>
-      <c r="R39" s="155"/>
+      <c r="Q39" s="159"/>
+      <c r="R39" s="161"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
@@ -6945,101 +6845,101 @@
       <c r="Z9" s="23"/>
     </row>
     <row r="11" spans="2:29" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="161" t="s">
+      <c r="B11" s="167" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="161"/>
-      <c r="D11" s="161"/>
-      <c r="E11" s="161"/>
-      <c r="F11" s="161"/>
-      <c r="G11" s="161"/>
-      <c r="H11" s="161"/>
-      <c r="I11" s="161"/>
-      <c r="J11" s="161"/>
-      <c r="K11" s="161"/>
-      <c r="L11" s="161"/>
-      <c r="M11" s="161"/>
-      <c r="N11" s="161"/>
-      <c r="O11" s="161"/>
-      <c r="P11" s="161"/>
-      <c r="Q11" s="161"/>
-      <c r="R11" s="161"/>
-      <c r="S11" s="161"/>
-      <c r="T11" s="161"/>
-      <c r="U11" s="161"/>
-      <c r="V11" s="161"/>
-      <c r="W11" s="161"/>
-      <c r="X11" s="161"/>
-      <c r="Y11" s="161"/>
-      <c r="Z11" s="162"/>
+      <c r="C11" s="167"/>
+      <c r="D11" s="167"/>
+      <c r="E11" s="167"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="167"/>
+      <c r="H11" s="167"/>
+      <c r="I11" s="167"/>
+      <c r="J11" s="167"/>
+      <c r="K11" s="167"/>
+      <c r="L11" s="167"/>
+      <c r="M11" s="167"/>
+      <c r="N11" s="167"/>
+      <c r="O11" s="167"/>
+      <c r="P11" s="167"/>
+      <c r="Q11" s="167"/>
+      <c r="R11" s="167"/>
+      <c r="S11" s="167"/>
+      <c r="T11" s="167"/>
+      <c r="U11" s="167"/>
+      <c r="V11" s="167"/>
+      <c r="W11" s="167"/>
+      <c r="X11" s="167"/>
+      <c r="Y11" s="167"/>
+      <c r="Z11" s="168"/>
     </row>
     <row r="12" spans="2:29" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="163"/>
-      <c r="C12" s="163"/>
-      <c r="D12" s="163"/>
-      <c r="E12" s="163"/>
-      <c r="F12" s="163"/>
-      <c r="G12" s="163"/>
-      <c r="H12" s="163"/>
-      <c r="I12" s="163"/>
-      <c r="J12" s="163"/>
-      <c r="K12" s="163"/>
-      <c r="L12" s="163"/>
-      <c r="M12" s="163"/>
-      <c r="N12" s="163"/>
-      <c r="O12" s="163"/>
-      <c r="P12" s="163"/>
-      <c r="Q12" s="163"/>
-      <c r="R12" s="163"/>
-      <c r="S12" s="163"/>
-      <c r="T12" s="163"/>
-      <c r="U12" s="163"/>
-      <c r="V12" s="163"/>
-      <c r="W12" s="163"/>
-      <c r="X12" s="163"/>
-      <c r="Y12" s="163"/>
-      <c r="Z12" s="164"/>
+      <c r="B12" s="169"/>
+      <c r="C12" s="169"/>
+      <c r="D12" s="169"/>
+      <c r="E12" s="169"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="169"/>
+      <c r="H12" s="169"/>
+      <c r="I12" s="169"/>
+      <c r="J12" s="169"/>
+      <c r="K12" s="169"/>
+      <c r="L12" s="169"/>
+      <c r="M12" s="169"/>
+      <c r="N12" s="169"/>
+      <c r="O12" s="169"/>
+      <c r="P12" s="169"/>
+      <c r="Q12" s="169"/>
+      <c r="R12" s="169"/>
+      <c r="S12" s="169"/>
+      <c r="T12" s="169"/>
+      <c r="U12" s="169"/>
+      <c r="V12" s="169"/>
+      <c r="W12" s="169"/>
+      <c r="X12" s="169"/>
+      <c r="Y12" s="169"/>
+      <c r="Z12" s="170"/>
     </row>
     <row r="13" spans="2:29" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="212" t="s">
+      <c r="B13" s="218" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="213"/>
+      <c r="C13" s="219"/>
       <c r="D13" s="44" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="200" t="s">
+      <c r="E13" s="206" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="201"/>
-      <c r="G13" s="219"/>
-      <c r="H13" s="219"/>
-      <c r="I13" s="219"/>
-      <c r="J13" s="219"/>
-      <c r="K13" s="196"/>
-      <c r="L13" s="165"/>
-      <c r="M13" s="165"/>
-      <c r="N13" s="165"/>
-      <c r="O13" s="165"/>
-      <c r="P13" s="165"/>
-      <c r="Q13" s="165"/>
-      <c r="R13" s="165"/>
-      <c r="S13" s="165"/>
-      <c r="T13" s="165"/>
-      <c r="U13" s="165"/>
-      <c r="V13" s="165"/>
-      <c r="W13" s="165"/>
-      <c r="X13" s="166"/>
+      <c r="F13" s="207"/>
+      <c r="G13" s="225"/>
+      <c r="H13" s="225"/>
+      <c r="I13" s="225"/>
+      <c r="J13" s="225"/>
+      <c r="K13" s="202"/>
+      <c r="L13" s="171"/>
+      <c r="M13" s="171"/>
+      <c r="N13" s="171"/>
+      <c r="O13" s="171"/>
+      <c r="P13" s="171"/>
+      <c r="Q13" s="171"/>
+      <c r="R13" s="171"/>
+      <c r="S13" s="171"/>
+      <c r="T13" s="171"/>
+      <c r="U13" s="171"/>
+      <c r="V13" s="171"/>
+      <c r="W13" s="171"/>
+      <c r="X13" s="172"/>
       <c r="Y13" s="53" t="s">
         <v>14</v>
       </c>
       <c r="Z13" s="28"/>
     </row>
     <row r="14" spans="2:29" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="212" t="s">
+      <c r="B14" s="218" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="213"/>
+      <c r="C14" s="219"/>
       <c r="D14" s="44" t="b">
         <v>0</v>
       </c>
@@ -7047,81 +6947,81 @@
         <v>11</v>
       </c>
       <c r="F14" s="52"/>
-      <c r="G14" s="219"/>
-      <c r="H14" s="219"/>
-      <c r="I14" s="219"/>
-      <c r="J14" s="219"/>
-      <c r="K14" s="197"/>
-      <c r="L14" s="167"/>
-      <c r="M14" s="167"/>
-      <c r="N14" s="167"/>
-      <c r="O14" s="167"/>
-      <c r="P14" s="167"/>
-      <c r="Q14" s="167"/>
-      <c r="R14" s="167"/>
-      <c r="S14" s="167"/>
-      <c r="T14" s="167"/>
-      <c r="U14" s="167"/>
-      <c r="V14" s="167"/>
-      <c r="W14" s="167"/>
-      <c r="X14" s="168"/>
+      <c r="G14" s="225"/>
+      <c r="H14" s="225"/>
+      <c r="I14" s="225"/>
+      <c r="J14" s="225"/>
+      <c r="K14" s="203"/>
+      <c r="L14" s="173"/>
+      <c r="M14" s="173"/>
+      <c r="N14" s="173"/>
+      <c r="O14" s="173"/>
+      <c r="P14" s="173"/>
+      <c r="Q14" s="173"/>
+      <c r="R14" s="173"/>
+      <c r="S14" s="173"/>
+      <c r="T14" s="173"/>
+      <c r="U14" s="173"/>
+      <c r="V14" s="173"/>
+      <c r="W14" s="173"/>
+      <c r="X14" s="174"/>
       <c r="Y14" s="53" t="s">
         <v>35</v>
       </c>
       <c r="Z14" s="28"/>
     </row>
     <row r="15" spans="2:29" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="169" t="s">
+      <c r="B15" s="175" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="170" t="s">
+      <c r="C15" s="176" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="171" t="s">
+      <c r="D15" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="172"/>
-      <c r="F15" s="132" t="s">
+      <c r="E15" s="178"/>
+      <c r="F15" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="133"/>
+      <c r="G15" s="156"/>
+      <c r="H15" s="156"/>
+      <c r="I15" s="134"/>
       <c r="J15" s="57"/>
       <c r="K15" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="L15" s="214" t="s">
+      <c r="L15" s="220" t="s">
         <v>34</v>
       </c>
-      <c r="M15" s="215"/>
-      <c r="N15" s="215"/>
-      <c r="O15" s="215"/>
-      <c r="P15" s="215"/>
-      <c r="Q15" s="215"/>
-      <c r="R15" s="215"/>
-      <c r="S15" s="215"/>
-      <c r="T15" s="215"/>
-      <c r="U15" s="215"/>
-      <c r="V15" s="215"/>
-      <c r="W15" s="216"/>
-      <c r="X15" s="170" t="s">
+      <c r="M15" s="221"/>
+      <c r="N15" s="221"/>
+      <c r="O15" s="221"/>
+      <c r="P15" s="221"/>
+      <c r="Q15" s="221"/>
+      <c r="R15" s="221"/>
+      <c r="S15" s="221"/>
+      <c r="T15" s="221"/>
+      <c r="U15" s="221"/>
+      <c r="V15" s="221"/>
+      <c r="W15" s="222"/>
+      <c r="X15" s="176" t="s">
         <v>51</v>
       </c>
-      <c r="Y15" s="204" t="s">
+      <c r="Y15" s="210" t="s">
         <v>10</v>
       </c>
-      <c r="Z15" s="179"/>
+      <c r="Z15" s="185"/>
     </row>
     <row r="16" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="169"/>
-      <c r="C16" s="170"/>
-      <c r="D16" s="173"/>
-      <c r="E16" s="174"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="151"/>
-      <c r="H16" s="151"/>
-      <c r="I16" s="135"/>
+      <c r="B16" s="175"/>
+      <c r="C16" s="176"/>
+      <c r="D16" s="179"/>
+      <c r="E16" s="180"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="157"/>
+      <c r="H16" s="157"/>
+      <c r="I16" s="136"/>
       <c r="J16" s="59"/>
       <c r="K16" s="60" t="s">
         <v>12</v>
@@ -7138,22 +7038,22 @@
       <c r="U16" s="58"/>
       <c r="V16" s="58"/>
       <c r="W16" s="58"/>
-      <c r="X16" s="170"/>
-      <c r="Y16" s="205"/>
-      <c r="Z16" s="181"/>
+      <c r="X16" s="176"/>
+      <c r="Y16" s="211"/>
+      <c r="Z16" s="187"/>
       <c r="AC16" s="25" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="2:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="169"/>
-      <c r="C17" s="170"/>
-      <c r="D17" s="173"/>
-      <c r="E17" s="174"/>
-      <c r="F17" s="134"/>
-      <c r="G17" s="151"/>
-      <c r="H17" s="151"/>
-      <c r="I17" s="135"/>
+      <c r="B17" s="175"/>
+      <c r="C17" s="176"/>
+      <c r="D17" s="179"/>
+      <c r="E17" s="180"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="136"/>
       <c r="J17" s="59"/>
       <c r="K17" s="61" t="s">
         <v>16</v>
@@ -7170,22 +7070,22 @@
       <c r="U17" s="58"/>
       <c r="V17" s="58"/>
       <c r="W17" s="58"/>
-      <c r="X17" s="170"/>
-      <c r="Y17" s="205"/>
-      <c r="Z17" s="181"/>
+      <c r="X17" s="176"/>
+      <c r="Y17" s="211"/>
+      <c r="Z17" s="187"/>
       <c r="AC17" s="25" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="2:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="169"/>
-      <c r="C18" s="170"/>
-      <c r="D18" s="175"/>
-      <c r="E18" s="176"/>
-      <c r="F18" s="136"/>
-      <c r="G18" s="152"/>
-      <c r="H18" s="152"/>
-      <c r="I18" s="137"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="176"/>
+      <c r="D18" s="181"/>
+      <c r="E18" s="182"/>
+      <c r="F18" s="137"/>
+      <c r="G18" s="158"/>
+      <c r="H18" s="158"/>
+      <c r="I18" s="138"/>
       <c r="J18" s="59"/>
       <c r="K18" s="61" t="s">
         <v>17</v>
@@ -7202,16 +7102,16 @@
       <c r="U18" s="58"/>
       <c r="V18" s="58"/>
       <c r="W18" s="58"/>
-      <c r="X18" s="170"/>
-      <c r="Y18" s="205"/>
-      <c r="Z18" s="181"/>
+      <c r="X18" s="176"/>
+      <c r="Y18" s="211"/>
+      <c r="Z18" s="187"/>
       <c r="AC18" s="25" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" spans="2:30" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="169"/>
-      <c r="C19" s="170"/>
+      <c r="B19" s="175"/>
+      <c r="C19" s="176"/>
       <c r="D19" s="56" t="s">
         <v>1</v>
       </c>
@@ -7230,10 +7130,10 @@
       <c r="I19" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="217" t="s">
+      <c r="J19" s="223" t="s">
         <v>29</v>
       </c>
-      <c r="K19" s="218"/>
+      <c r="K19" s="224"/>
       <c r="L19" s="56">
         <v>1</v>
       </c>
@@ -7270,9 +7170,9 @@
       <c r="W19" s="56">
         <v>12</v>
       </c>
-      <c r="X19" s="170"/>
-      <c r="Y19" s="182"/>
-      <c r="Z19" s="183"/>
+      <c r="X19" s="176"/>
+      <c r="Y19" s="188"/>
+      <c r="Z19" s="189"/>
     </row>
     <row r="20" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="36">
@@ -7285,8 +7185,8 @@
       <c r="G20" s="36"/>
       <c r="H20" s="36"/>
       <c r="I20" s="35"/>
-      <c r="J20" s="153"/>
-      <c r="K20" s="155"/>
+      <c r="J20" s="159"/>
+      <c r="K20" s="161"/>
       <c r="L20" s="46"/>
       <c r="M20" s="46"/>
       <c r="N20" s="46"/>
@@ -7300,8 +7200,8 @@
       <c r="V20" s="46"/>
       <c r="W20" s="46"/>
       <c r="X20" s="49"/>
-      <c r="Y20" s="153"/>
-      <c r="Z20" s="155"/>
+      <c r="Y20" s="159"/>
+      <c r="Z20" s="161"/>
       <c r="AD20" t="s">
         <v>21</v>
       </c>
@@ -7317,8 +7217,8 @@
       <c r="G21" s="36"/>
       <c r="H21" s="36"/>
       <c r="I21" s="35"/>
-      <c r="J21" s="153"/>
-      <c r="K21" s="155"/>
+      <c r="J21" s="159"/>
+      <c r="K21" s="161"/>
       <c r="L21" s="46"/>
       <c r="M21" s="46"/>
       <c r="N21" s="46"/>
@@ -7332,8 +7232,8 @@
       <c r="V21" s="46"/>
       <c r="W21" s="46"/>
       <c r="X21" s="49"/>
-      <c r="Y21" s="153"/>
-      <c r="Z21" s="155"/>
+      <c r="Y21" s="159"/>
+      <c r="Z21" s="161"/>
       <c r="AD21" t="s">
         <v>22</v>
       </c>
@@ -7349,8 +7249,8 @@
       <c r="G22" s="36"/>
       <c r="H22" s="36"/>
       <c r="I22" s="35"/>
-      <c r="J22" s="153"/>
-      <c r="K22" s="155"/>
+      <c r="J22" s="159"/>
+      <c r="K22" s="161"/>
       <c r="L22" s="46"/>
       <c r="M22" s="46"/>
       <c r="N22" s="46"/>
@@ -7364,8 +7264,8 @@
       <c r="V22" s="46"/>
       <c r="W22" s="46"/>
       <c r="X22" s="49"/>
-      <c r="Y22" s="153"/>
-      <c r="Z22" s="155"/>
+      <c r="Y22" s="159"/>
+      <c r="Z22" s="161"/>
       <c r="AD22" t="s">
         <v>23</v>
       </c>
@@ -7381,8 +7281,8 @@
       <c r="G23" s="36"/>
       <c r="H23" s="36"/>
       <c r="I23" s="35"/>
-      <c r="J23" s="153"/>
-      <c r="K23" s="155"/>
+      <c r="J23" s="159"/>
+      <c r="K23" s="161"/>
       <c r="L23" s="46"/>
       <c r="M23" s="46"/>
       <c r="N23" s="46"/>
@@ -7396,8 +7296,8 @@
       <c r="V23" s="46"/>
       <c r="W23" s="46"/>
       <c r="X23" s="49"/>
-      <c r="Y23" s="153"/>
-      <c r="Z23" s="155"/>
+      <c r="Y23" s="159"/>
+      <c r="Z23" s="161"/>
       <c r="AD23" t="s">
         <v>24</v>
       </c>
@@ -7413,8 +7313,8 @@
       <c r="G24" s="36"/>
       <c r="H24" s="36"/>
       <c r="I24" s="35"/>
-      <c r="J24" s="153"/>
-      <c r="K24" s="155"/>
+      <c r="J24" s="159"/>
+      <c r="K24" s="161"/>
       <c r="L24" s="46"/>
       <c r="M24" s="46"/>
       <c r="N24" s="46"/>
@@ -7428,8 +7328,8 @@
       <c r="V24" s="46"/>
       <c r="W24" s="46"/>
       <c r="X24" s="49"/>
-      <c r="Y24" s="153"/>
-      <c r="Z24" s="155"/>
+      <c r="Y24" s="159"/>
+      <c r="Z24" s="161"/>
     </row>
     <row r="25" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="36">
@@ -7442,8 +7342,8 @@
       <c r="G25" s="36"/>
       <c r="H25" s="36"/>
       <c r="I25" s="35"/>
-      <c r="J25" s="153"/>
-      <c r="K25" s="155"/>
+      <c r="J25" s="159"/>
+      <c r="K25" s="161"/>
       <c r="L25" s="46"/>
       <c r="M25" s="46"/>
       <c r="N25" s="46"/>
@@ -7457,8 +7357,8 @@
       <c r="V25" s="46"/>
       <c r="W25" s="46"/>
       <c r="X25" s="49"/>
-      <c r="Y25" s="153"/>
-      <c r="Z25" s="155"/>
+      <c r="Y25" s="159"/>
+      <c r="Z25" s="161"/>
     </row>
     <row r="26" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="36">
@@ -7471,8 +7371,8 @@
       <c r="G26" s="36"/>
       <c r="H26" s="36"/>
       <c r="I26" s="35"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="155"/>
+      <c r="J26" s="159"/>
+      <c r="K26" s="161"/>
       <c r="L26" s="46"/>
       <c r="M26" s="46"/>
       <c r="N26" s="46"/>
@@ -7486,8 +7386,8 @@
       <c r="V26" s="46"/>
       <c r="W26" s="46"/>
       <c r="X26" s="49"/>
-      <c r="Y26" s="153"/>
-      <c r="Z26" s="155"/>
+      <c r="Y26" s="159"/>
+      <c r="Z26" s="161"/>
     </row>
     <row r="27" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="36">
@@ -7500,8 +7400,8 @@
       <c r="G27" s="36"/>
       <c r="H27" s="36"/>
       <c r="I27" s="35"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="155"/>
+      <c r="J27" s="159"/>
+      <c r="K27" s="161"/>
       <c r="L27" s="46"/>
       <c r="M27" s="46"/>
       <c r="N27" s="46"/>
@@ -7515,8 +7415,8 @@
       <c r="V27" s="46"/>
       <c r="W27" s="46"/>
       <c r="X27" s="49"/>
-      <c r="Y27" s="153"/>
-      <c r="Z27" s="155"/>
+      <c r="Y27" s="159"/>
+      <c r="Z27" s="161"/>
     </row>
     <row r="28" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="36">
@@ -7529,8 +7429,8 @@
       <c r="G28" s="36"/>
       <c r="H28" s="36"/>
       <c r="I28" s="35"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="155"/>
+      <c r="J28" s="159"/>
+      <c r="K28" s="161"/>
       <c r="L28" s="46"/>
       <c r="M28" s="46"/>
       <c r="N28" s="46"/>
@@ -7544,8 +7444,8 @@
       <c r="V28" s="46"/>
       <c r="W28" s="46"/>
       <c r="X28" s="49"/>
-      <c r="Y28" s="153"/>
-      <c r="Z28" s="155"/>
+      <c r="Y28" s="159"/>
+      <c r="Z28" s="161"/>
     </row>
     <row r="29" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="36">
@@ -7558,8 +7458,8 @@
       <c r="G29" s="36"/>
       <c r="H29" s="36"/>
       <c r="I29" s="35"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="155"/>
+      <c r="J29" s="159"/>
+      <c r="K29" s="161"/>
       <c r="L29" s="46"/>
       <c r="M29" s="46"/>
       <c r="N29" s="46"/>
@@ -7573,8 +7473,8 @@
       <c r="V29" s="46"/>
       <c r="W29" s="46"/>
       <c r="X29" s="49"/>
-      <c r="Y29" s="153"/>
-      <c r="Z29" s="155"/>
+      <c r="Y29" s="159"/>
+      <c r="Z29" s="161"/>
     </row>
     <row r="30" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="36">
@@ -7587,8 +7487,8 @@
       <c r="G30" s="36"/>
       <c r="H30" s="36"/>
       <c r="I30" s="35"/>
-      <c r="J30" s="153"/>
-      <c r="K30" s="155"/>
+      <c r="J30" s="159"/>
+      <c r="K30" s="161"/>
       <c r="L30" s="46"/>
       <c r="M30" s="46"/>
       <c r="N30" s="46"/>
@@ -7602,8 +7502,8 @@
       <c r="V30" s="46"/>
       <c r="W30" s="46"/>
       <c r="X30" s="49"/>
-      <c r="Y30" s="153"/>
-      <c r="Z30" s="155"/>
+      <c r="Y30" s="159"/>
+      <c r="Z30" s="161"/>
     </row>
     <row r="31" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="36">
@@ -7616,8 +7516,8 @@
       <c r="G31" s="36"/>
       <c r="H31" s="36"/>
       <c r="I31" s="35"/>
-      <c r="J31" s="153"/>
-      <c r="K31" s="155"/>
+      <c r="J31" s="159"/>
+      <c r="K31" s="161"/>
       <c r="L31" s="46"/>
       <c r="M31" s="46"/>
       <c r="N31" s="46"/>
@@ -7631,8 +7531,8 @@
       <c r="V31" s="46"/>
       <c r="W31" s="46"/>
       <c r="X31" s="49"/>
-      <c r="Y31" s="153"/>
-      <c r="Z31" s="155"/>
+      <c r="Y31" s="159"/>
+      <c r="Z31" s="161"/>
     </row>
     <row r="32" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="36">
@@ -7645,8 +7545,8 @@
       <c r="G32" s="40"/>
       <c r="H32" s="40"/>
       <c r="I32" s="35"/>
-      <c r="J32" s="153"/>
-      <c r="K32" s="155"/>
+      <c r="J32" s="159"/>
+      <c r="K32" s="161"/>
       <c r="L32" s="48"/>
       <c r="M32" s="48"/>
       <c r="N32" s="48"/>
@@ -7660,8 +7560,8 @@
       <c r="V32" s="48"/>
       <c r="W32" s="48"/>
       <c r="X32" s="50"/>
-      <c r="Y32" s="153"/>
-      <c r="Z32" s="155"/>
+      <c r="Y32" s="159"/>
+      <c r="Z32" s="161"/>
     </row>
     <row r="33" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="36">
@@ -7674,8 +7574,8 @@
       <c r="G33" s="36"/>
       <c r="H33" s="36"/>
       <c r="I33" s="35"/>
-      <c r="J33" s="153"/>
-      <c r="K33" s="155"/>
+      <c r="J33" s="159"/>
+      <c r="K33" s="161"/>
       <c r="L33" s="46"/>
       <c r="M33" s="46"/>
       <c r="N33" s="46"/>
@@ -7689,8 +7589,8 @@
       <c r="V33" s="46"/>
       <c r="W33" s="46"/>
       <c r="X33" s="49"/>
-      <c r="Y33" s="153"/>
-      <c r="Z33" s="155"/>
+      <c r="Y33" s="159"/>
+      <c r="Z33" s="161"/>
     </row>
     <row r="34" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="36">
@@ -7703,8 +7603,8 @@
       <c r="G34" s="36"/>
       <c r="H34" s="36"/>
       <c r="I34" s="35"/>
-      <c r="J34" s="153"/>
-      <c r="K34" s="155"/>
+      <c r="J34" s="159"/>
+      <c r="K34" s="161"/>
       <c r="L34" s="46"/>
       <c r="M34" s="46"/>
       <c r="N34" s="46"/>
@@ -7718,8 +7618,8 @@
       <c r="V34" s="46"/>
       <c r="W34" s="46"/>
       <c r="X34" s="49"/>
-      <c r="Y34" s="153"/>
-      <c r="Z34" s="155"/>
+      <c r="Y34" s="159"/>
+      <c r="Z34" s="161"/>
     </row>
     <row r="35" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="36">
@@ -7732,8 +7632,8 @@
       <c r="G35" s="40"/>
       <c r="H35" s="40"/>
       <c r="I35" s="35"/>
-      <c r="J35" s="153"/>
-      <c r="K35" s="155"/>
+      <c r="J35" s="159"/>
+      <c r="K35" s="161"/>
       <c r="L35" s="48"/>
       <c r="M35" s="48"/>
       <c r="N35" s="48"/>
@@ -7747,8 +7647,8 @@
       <c r="V35" s="48"/>
       <c r="W35" s="48"/>
       <c r="X35" s="50"/>
-      <c r="Y35" s="153"/>
-      <c r="Z35" s="155"/>
+      <c r="Y35" s="159"/>
+      <c r="Z35" s="161"/>
     </row>
     <row r="36" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="36">
@@ -7761,8 +7661,8 @@
       <c r="G36" s="36"/>
       <c r="H36" s="36"/>
       <c r="I36" s="35"/>
-      <c r="J36" s="153"/>
-      <c r="K36" s="155"/>
+      <c r="J36" s="159"/>
+      <c r="K36" s="161"/>
       <c r="L36" s="46"/>
       <c r="M36" s="46"/>
       <c r="N36" s="46"/>
@@ -7776,8 +7676,8 @@
       <c r="V36" s="46"/>
       <c r="W36" s="46"/>
       <c r="X36" s="49"/>
-      <c r="Y36" s="153"/>
-      <c r="Z36" s="155"/>
+      <c r="Y36" s="159"/>
+      <c r="Z36" s="161"/>
     </row>
     <row r="37" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="36">
@@ -7790,8 +7690,8 @@
       <c r="G37" s="36"/>
       <c r="H37" s="36"/>
       <c r="I37" s="35"/>
-      <c r="J37" s="153"/>
-      <c r="K37" s="155"/>
+      <c r="J37" s="159"/>
+      <c r="K37" s="161"/>
       <c r="L37" s="46"/>
       <c r="M37" s="46"/>
       <c r="N37" s="46"/>
@@ -7805,8 +7705,8 @@
       <c r="V37" s="46"/>
       <c r="W37" s="46"/>
       <c r="X37" s="49"/>
-      <c r="Y37" s="153"/>
-      <c r="Z37" s="155"/>
+      <c r="Y37" s="159"/>
+      <c r="Z37" s="161"/>
     </row>
     <row r="38" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="36">
@@ -7819,8 +7719,8 @@
       <c r="G38" s="40"/>
       <c r="H38" s="40"/>
       <c r="I38" s="35"/>
-      <c r="J38" s="153"/>
-      <c r="K38" s="155"/>
+      <c r="J38" s="159"/>
+      <c r="K38" s="161"/>
       <c r="L38" s="48"/>
       <c r="M38" s="48"/>
       <c r="N38" s="48"/>
@@ -7834,8 +7734,8 @@
       <c r="V38" s="48"/>
       <c r="W38" s="48"/>
       <c r="X38" s="50"/>
-      <c r="Y38" s="153"/>
-      <c r="Z38" s="155"/>
+      <c r="Y38" s="159"/>
+      <c r="Z38" s="161"/>
     </row>
     <row r="39" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="36">
@@ -7848,8 +7748,8 @@
       <c r="G39" s="36"/>
       <c r="H39" s="36"/>
       <c r="I39" s="35"/>
-      <c r="J39" s="153"/>
-      <c r="K39" s="155"/>
+      <c r="J39" s="159"/>
+      <c r="K39" s="161"/>
       <c r="L39" s="46"/>
       <c r="M39" s="46"/>
       <c r="N39" s="46"/>
@@ -7863,8 +7763,8 @@
       <c r="V39" s="46"/>
       <c r="W39" s="46"/>
       <c r="X39" s="49"/>
-      <c r="Y39" s="153"/>
-      <c r="Z39" s="155"/>
+      <c r="Y39" s="159"/>
+      <c r="Z39" s="161"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
@@ -7958,140 +7858,140 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="77"/>
-      <c r="B1" s="80" t="s">
+      <c r="A1" s="78"/>
+      <c r="B1" s="81" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="80"/>
-      <c r="D1" s="80"/>
-      <c r="E1" s="80"/>
-      <c r="F1" s="80"/>
-      <c r="G1" s="80"/>
-      <c r="H1" s="80"/>
-      <c r="I1" s="83" t="s">
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="84" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="84"/>
+      <c r="J1" s="85"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="78"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="85" t="s">
+      <c r="A2" s="79"/>
+      <c r="B2" s="82"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
+      <c r="I2" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="86"/>
+      <c r="J2" s="87"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="78"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="87" t="s">
+      <c r="A3" s="79"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="82"/>
+      <c r="D3" s="82"/>
+      <c r="E3" s="82"/>
+      <c r="F3" s="82"/>
+      <c r="G3" s="82"/>
+      <c r="H3" s="82"/>
+      <c r="I3" s="88" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="88"/>
+      <c r="J3" s="89"/>
     </row>
     <row r="4" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="78"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
-      <c r="I4" s="85" t="s">
+      <c r="A4" s="79"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
+      <c r="I4" s="86" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="86"/>
+      <c r="J4" s="87"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="78"/>
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="87" t="s">
+      <c r="A5" s="79"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+      <c r="F5" s="82"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="82"/>
+      <c r="I5" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="88"/>
+      <c r="J5" s="89"/>
     </row>
     <row r="6" spans="1:10" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="79"/>
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="89">
+      <c r="A6" s="80"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="90">
         <v>46237</v>
       </c>
-      <c r="J6" s="90"/>
+      <c r="J6" s="91"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="91"/>
-      <c r="B7" s="92"/>
-      <c r="C7" s="92"/>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="92"/>
-      <c r="H7" s="92"/>
-      <c r="I7" s="92"/>
-      <c r="J7" s="93"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="93"/>
+      <c r="C7" s="93"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="93"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="93"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="93"/>
+      <c r="J7" s="94"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="94" t="s">
+      <c r="A8" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="95"/>
-      <c r="C8" s="95"/>
-      <c r="D8" s="95"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="95"/>
-      <c r="G8" s="95"/>
-      <c r="H8" s="95"/>
-      <c r="I8" s="95"/>
-      <c r="J8" s="96"/>
+      <c r="B8" s="96"/>
+      <c r="C8" s="96"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="96"/>
+      <c r="H8" s="96"/>
+      <c r="I8" s="96"/>
+      <c r="J8" s="97"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="97"/>
-      <c r="B9" s="98"/>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="98"/>
-      <c r="F9" s="98"/>
-      <c r="G9" s="98"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="99"/>
+      <c r="A9" s="98"/>
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="99"/>
+      <c r="G9" s="99"/>
+      <c r="H9" s="99"/>
+      <c r="I9" s="99"/>
+      <c r="J9" s="100"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="100"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101"/>
-      <c r="H10" s="101"/>
-      <c r="I10" s="101"/>
-      <c r="J10" s="102"/>
+      <c r="A10" s="101"/>
+      <c r="B10" s="102"/>
+      <c r="C10" s="102"/>
+      <c r="D10" s="102"/>
+      <c r="E10" s="102"/>
+      <c r="F10" s="102"/>
+      <c r="G10" s="102"/>
+      <c r="H10" s="102"/>
+      <c r="I10" s="102"/>
+      <c r="J10" s="103"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="73"/>
@@ -8106,492 +8006,492 @@
       <c r="J11" s="75"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="105"/>
+      <c r="B12" s="105"/>
+      <c r="C12" s="105"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="105"/>
+      <c r="G12" s="105"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="106"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="103"/>
-      <c r="B13" s="104"/>
-      <c r="C13" s="104"/>
-      <c r="D13" s="104"/>
-      <c r="E13" s="104"/>
-      <c r="F13" s="104"/>
-      <c r="G13" s="104"/>
-      <c r="H13" s="104"/>
-      <c r="I13" s="104"/>
-      <c r="J13" s="105"/>
+      <c r="A13" s="104"/>
+      <c r="B13" s="105"/>
+      <c r="C13" s="105"/>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="105"/>
+      <c r="G13" s="105"/>
+      <c r="H13" s="105"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="106"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="103"/>
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="104"/>
-      <c r="H14" s="104"/>
-      <c r="I14" s="104"/>
-      <c r="J14" s="105"/>
+      <c r="A14" s="104"/>
+      <c r="B14" s="105"/>
+      <c r="C14" s="105"/>
+      <c r="D14" s="105"/>
+      <c r="E14" s="105"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="105"/>
+      <c r="H14" s="105"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="106"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="103"/>
-      <c r="B15" s="104"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="104"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="104"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="104"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="105"/>
+      <c r="A15" s="104"/>
+      <c r="B15" s="105"/>
+      <c r="C15" s="105"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="105"/>
+      <c r="J15" s="106"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="103"/>
-      <c r="B16" s="104"/>
-      <c r="C16" s="104"/>
-      <c r="D16" s="104"/>
-      <c r="E16" s="104"/>
-      <c r="F16" s="104"/>
-      <c r="G16" s="104"/>
-      <c r="H16" s="104"/>
-      <c r="I16" s="104"/>
-      <c r="J16" s="105"/>
+      <c r="A16" s="104"/>
+      <c r="B16" s="105"/>
+      <c r="C16" s="105"/>
+      <c r="D16" s="105"/>
+      <c r="E16" s="105"/>
+      <c r="F16" s="105"/>
+      <c r="G16" s="105"/>
+      <c r="H16" s="105"/>
+      <c r="I16" s="105"/>
+      <c r="J16" s="106"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="103"/>
-      <c r="B17" s="104"/>
-      <c r="C17" s="104"/>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="105"/>
+      <c r="A17" s="104"/>
+      <c r="B17" s="105"/>
+      <c r="C17" s="105"/>
+      <c r="D17" s="105"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="105"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="106"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="103"/>
-      <c r="B18" s="104"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="104"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="104"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="104"/>
-      <c r="I18" s="104"/>
-      <c r="J18" s="105"/>
+      <c r="A18" s="104"/>
+      <c r="B18" s="105"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="106"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="103"/>
-      <c r="B19" s="104"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="104"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="104"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="104"/>
-      <c r="I19" s="104"/>
-      <c r="J19" s="105"/>
+      <c r="A19" s="104"/>
+      <c r="B19" s="105"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="105"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="105"/>
+      <c r="G19" s="105"/>
+      <c r="H19" s="105"/>
+      <c r="I19" s="105"/>
+      <c r="J19" s="106"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="103"/>
-      <c r="B20" s="104"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="104"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="104"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="104"/>
-      <c r="I20" s="104"/>
-      <c r="J20" s="105"/>
+      <c r="A20" s="104"/>
+      <c r="B20" s="105"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="105"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="105"/>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="106"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="103"/>
-      <c r="B21" s="104"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="104"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="104"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="104"/>
-      <c r="I21" s="104"/>
-      <c r="J21" s="105"/>
+      <c r="A21" s="104"/>
+      <c r="B21" s="105"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="105"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="106"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="103"/>
-      <c r="B22" s="104"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="104"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="104"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="104"/>
-      <c r="I22" s="104"/>
-      <c r="J22" s="105"/>
+      <c r="A22" s="104"/>
+      <c r="B22" s="105"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="106"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="103"/>
-      <c r="B23" s="104"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="104"/>
-      <c r="I23" s="104"/>
-      <c r="J23" s="105"/>
+      <c r="A23" s="104"/>
+      <c r="B23" s="105"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="105"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="105"/>
+      <c r="G23" s="105"/>
+      <c r="H23" s="105"/>
+      <c r="I23" s="105"/>
+      <c r="J23" s="106"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="103"/>
-      <c r="B24" s="104"/>
-      <c r="C24" s="104"/>
-      <c r="D24" s="104"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="104"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="104"/>
-      <c r="I24" s="104"/>
-      <c r="J24" s="105"/>
+      <c r="A24" s="104"/>
+      <c r="B24" s="105"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="105"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="105"/>
+      <c r="G24" s="105"/>
+      <c r="H24" s="105"/>
+      <c r="I24" s="105"/>
+      <c r="J24" s="106"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="103"/>
-      <c r="B25" s="104"/>
-      <c r="C25" s="104"/>
-      <c r="D25" s="104"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="104"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="104"/>
-      <c r="I25" s="104"/>
-      <c r="J25" s="105"/>
+      <c r="A25" s="104"/>
+      <c r="B25" s="105"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="105"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="105"/>
+      <c r="G25" s="105"/>
+      <c r="H25" s="105"/>
+      <c r="I25" s="105"/>
+      <c r="J25" s="106"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="103"/>
-      <c r="B26" s="104"/>
-      <c r="C26" s="104"/>
-      <c r="D26" s="104"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="104"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="104"/>
-      <c r="I26" s="104"/>
-      <c r="J26" s="105"/>
+      <c r="A26" s="104"/>
+      <c r="B26" s="105"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="105"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="105"/>
+      <c r="G26" s="105"/>
+      <c r="H26" s="105"/>
+      <c r="I26" s="105"/>
+      <c r="J26" s="106"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="103"/>
-      <c r="B27" s="104"/>
-      <c r="C27" s="104"/>
-      <c r="D27" s="104"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="104"/>
-      <c r="G27" s="104"/>
-      <c r="H27" s="104"/>
-      <c r="I27" s="104"/>
-      <c r="J27" s="105"/>
+      <c r="A27" s="104"/>
+      <c r="B27" s="105"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="105"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="105"/>
+      <c r="G27" s="105"/>
+      <c r="H27" s="105"/>
+      <c r="I27" s="105"/>
+      <c r="J27" s="106"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="103"/>
-      <c r="B28" s="104"/>
-      <c r="C28" s="104"/>
-      <c r="D28" s="104"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="104"/>
-      <c r="I28" s="104"/>
-      <c r="J28" s="105"/>
+      <c r="A28" s="104"/>
+      <c r="B28" s="105"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="105"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="105"/>
+      <c r="G28" s="105"/>
+      <c r="H28" s="105"/>
+      <c r="I28" s="105"/>
+      <c r="J28" s="106"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="103"/>
-      <c r="B29" s="104"/>
-      <c r="C29" s="104"/>
-      <c r="D29" s="104"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="104"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="104"/>
-      <c r="I29" s="104"/>
-      <c r="J29" s="105"/>
+      <c r="A29" s="104"/>
+      <c r="B29" s="105"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="105"/>
+      <c r="G29" s="105"/>
+      <c r="H29" s="105"/>
+      <c r="I29" s="105"/>
+      <c r="J29" s="106"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="103"/>
-      <c r="B30" s="104"/>
-      <c r="C30" s="104"/>
-      <c r="D30" s="104"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="104"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="104"/>
-      <c r="I30" s="104"/>
-      <c r="J30" s="105"/>
+      <c r="A30" s="104"/>
+      <c r="B30" s="105"/>
+      <c r="C30" s="105"/>
+      <c r="D30" s="105"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="105"/>
+      <c r="G30" s="105"/>
+      <c r="H30" s="105"/>
+      <c r="I30" s="105"/>
+      <c r="J30" s="106"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="103"/>
-      <c r="B31" s="104"/>
-      <c r="C31" s="104"/>
-      <c r="D31" s="104"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="105"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="105"/>
+      <c r="H31" s="105"/>
+      <c r="I31" s="105"/>
+      <c r="J31" s="106"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="103"/>
-      <c r="B32" s="104"/>
-      <c r="C32" s="104"/>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="104"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="104"/>
-      <c r="I32" s="104"/>
-      <c r="J32" s="105"/>
+      <c r="A32" s="104"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="105"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="105"/>
+      <c r="J32" s="106"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="103"/>
-      <c r="B33" s="104"/>
-      <c r="C33" s="104"/>
-      <c r="D33" s="104"/>
-      <c r="E33" s="104"/>
-      <c r="F33" s="104"/>
-      <c r="G33" s="104"/>
-      <c r="H33" s="104"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="105"/>
+      <c r="A33" s="104"/>
+      <c r="B33" s="105"/>
+      <c r="C33" s="105"/>
+      <c r="D33" s="105"/>
+      <c r="E33" s="105"/>
+      <c r="F33" s="105"/>
+      <c r="G33" s="105"/>
+      <c r="H33" s="105"/>
+      <c r="I33" s="105"/>
+      <c r="J33" s="106"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="103"/>
-      <c r="B34" s="104"/>
-      <c r="C34" s="104"/>
-      <c r="D34" s="104"/>
-      <c r="E34" s="104"/>
-      <c r="F34" s="104"/>
-      <c r="G34" s="104"/>
-      <c r="H34" s="104"/>
-      <c r="I34" s="104"/>
-      <c r="J34" s="105"/>
+      <c r="A34" s="104"/>
+      <c r="B34" s="105"/>
+      <c r="C34" s="105"/>
+      <c r="D34" s="105"/>
+      <c r="E34" s="105"/>
+      <c r="F34" s="105"/>
+      <c r="G34" s="105"/>
+      <c r="H34" s="105"/>
+      <c r="I34" s="105"/>
+      <c r="J34" s="106"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="103"/>
-      <c r="B35" s="104"/>
-      <c r="C35" s="104"/>
-      <c r="D35" s="104"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="104"/>
-      <c r="I35" s="104"/>
-      <c r="J35" s="105"/>
+      <c r="A35" s="104"/>
+      <c r="B35" s="105"/>
+      <c r="C35" s="105"/>
+      <c r="D35" s="105"/>
+      <c r="E35" s="105"/>
+      <c r="F35" s="105"/>
+      <c r="G35" s="105"/>
+      <c r="H35" s="105"/>
+      <c r="I35" s="105"/>
+      <c r="J35" s="106"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="103"/>
-      <c r="B36" s="104"/>
-      <c r="C36" s="104"/>
-      <c r="D36" s="104"/>
-      <c r="E36" s="104"/>
-      <c r="F36" s="104"/>
-      <c r="G36" s="104"/>
-      <c r="H36" s="104"/>
-      <c r="I36" s="104"/>
-      <c r="J36" s="105"/>
+      <c r="A36" s="104"/>
+      <c r="B36" s="105"/>
+      <c r="C36" s="105"/>
+      <c r="D36" s="105"/>
+      <c r="E36" s="105"/>
+      <c r="F36" s="105"/>
+      <c r="G36" s="105"/>
+      <c r="H36" s="105"/>
+      <c r="I36" s="105"/>
+      <c r="J36" s="106"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="103"/>
-      <c r="B37" s="104"/>
-      <c r="C37" s="104"/>
-      <c r="D37" s="104"/>
-      <c r="E37" s="104"/>
-      <c r="F37" s="104"/>
-      <c r="G37" s="104"/>
-      <c r="H37" s="104"/>
-      <c r="I37" s="104"/>
-      <c r="J37" s="105"/>
+      <c r="A37" s="104"/>
+      <c r="B37" s="105"/>
+      <c r="C37" s="105"/>
+      <c r="D37" s="105"/>
+      <c r="E37" s="105"/>
+      <c r="F37" s="105"/>
+      <c r="G37" s="105"/>
+      <c r="H37" s="105"/>
+      <c r="I37" s="105"/>
+      <c r="J37" s="106"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="103"/>
-      <c r="B38" s="104"/>
-      <c r="C38" s="104"/>
-      <c r="D38" s="104"/>
-      <c r="E38" s="104"/>
-      <c r="F38" s="104"/>
-      <c r="G38" s="104"/>
-      <c r="H38" s="104"/>
-      <c r="I38" s="104"/>
-      <c r="J38" s="105"/>
+      <c r="A38" s="104"/>
+      <c r="B38" s="105"/>
+      <c r="C38" s="105"/>
+      <c r="D38" s="105"/>
+      <c r="E38" s="105"/>
+      <c r="F38" s="105"/>
+      <c r="G38" s="105"/>
+      <c r="H38" s="105"/>
+      <c r="I38" s="105"/>
+      <c r="J38" s="106"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="103"/>
-      <c r="B39" s="104"/>
-      <c r="C39" s="104"/>
-      <c r="D39" s="104"/>
-      <c r="E39" s="104"/>
-      <c r="F39" s="104"/>
-      <c r="G39" s="104"/>
-      <c r="H39" s="104"/>
-      <c r="I39" s="104"/>
-      <c r="J39" s="105"/>
+      <c r="A39" s="104"/>
+      <c r="B39" s="105"/>
+      <c r="C39" s="105"/>
+      <c r="D39" s="105"/>
+      <c r="E39" s="105"/>
+      <c r="F39" s="105"/>
+      <c r="G39" s="105"/>
+      <c r="H39" s="105"/>
+      <c r="I39" s="105"/>
+      <c r="J39" s="106"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="103"/>
-      <c r="B40" s="104"/>
-      <c r="C40" s="104"/>
-      <c r="D40" s="104"/>
-      <c r="E40" s="104"/>
-      <c r="F40" s="104"/>
-      <c r="G40" s="104"/>
-      <c r="H40" s="104"/>
-      <c r="I40" s="104"/>
-      <c r="J40" s="105"/>
+      <c r="A40" s="104"/>
+      <c r="B40" s="105"/>
+      <c r="C40" s="105"/>
+      <c r="D40" s="105"/>
+      <c r="E40" s="105"/>
+      <c r="F40" s="105"/>
+      <c r="G40" s="105"/>
+      <c r="H40" s="105"/>
+      <c r="I40" s="105"/>
+      <c r="J40" s="106"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="103"/>
-      <c r="B41" s="104"/>
-      <c r="C41" s="104"/>
-      <c r="D41" s="104"/>
-      <c r="E41" s="104"/>
-      <c r="F41" s="104"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="104"/>
-      <c r="I41" s="104"/>
-      <c r="J41" s="105"/>
+      <c r="A41" s="104"/>
+      <c r="B41" s="105"/>
+      <c r="C41" s="105"/>
+      <c r="D41" s="105"/>
+      <c r="E41" s="105"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="105"/>
+      <c r="H41" s="105"/>
+      <c r="I41" s="105"/>
+      <c r="J41" s="106"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="103"/>
-      <c r="B42" s="104"/>
-      <c r="C42" s="104"/>
-      <c r="D42" s="104"/>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="104"/>
-      <c r="H42" s="104"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="105"/>
+      <c r="A42" s="104"/>
+      <c r="B42" s="105"/>
+      <c r="C42" s="105"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="105"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="105"/>
+      <c r="H42" s="105"/>
+      <c r="I42" s="105"/>
+      <c r="J42" s="106"/>
     </row>
     <row r="43" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="103"/>
-      <c r="B43" s="104"/>
-      <c r="C43" s="104"/>
-      <c r="D43" s="104"/>
-      <c r="E43" s="104"/>
-      <c r="F43" s="104"/>
-      <c r="G43" s="104"/>
-      <c r="H43" s="104"/>
-      <c r="I43" s="104"/>
-      <c r="J43" s="105"/>
+      <c r="A43" s="104"/>
+      <c r="B43" s="105"/>
+      <c r="C43" s="105"/>
+      <c r="D43" s="105"/>
+      <c r="E43" s="105"/>
+      <c r="F43" s="105"/>
+      <c r="G43" s="105"/>
+      <c r="H43" s="105"/>
+      <c r="I43" s="105"/>
+      <c r="J43" s="106"/>
     </row>
     <row r="44" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="103"/>
-      <c r="B44" s="104"/>
-      <c r="C44" s="104"/>
-      <c r="D44" s="104"/>
-      <c r="E44" s="104"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="104"/>
-      <c r="H44" s="104"/>
-      <c r="I44" s="104"/>
-      <c r="J44" s="105"/>
+      <c r="A44" s="104"/>
+      <c r="B44" s="105"/>
+      <c r="C44" s="105"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="105"/>
+      <c r="F44" s="105"/>
+      <c r="G44" s="105"/>
+      <c r="H44" s="105"/>
+      <c r="I44" s="105"/>
+      <c r="J44" s="106"/>
     </row>
     <row r="45" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="103" t="s">
+      <c r="A45" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="104"/>
-      <c r="C45" s="104"/>
-      <c r="D45" s="104"/>
-      <c r="E45" s="104"/>
-      <c r="F45" s="104"/>
-      <c r="G45" s="104"/>
-      <c r="H45" s="104"/>
-      <c r="I45" s="104"/>
-      <c r="J45" s="105"/>
+      <c r="B45" s="105"/>
+      <c r="C45" s="105"/>
+      <c r="D45" s="105"/>
+      <c r="E45" s="105"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="105"/>
+      <c r="H45" s="105"/>
+      <c r="I45" s="105"/>
+      <c r="J45" s="106"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="103"/>
-      <c r="B46" s="104"/>
-      <c r="C46" s="104"/>
-      <c r="D46" s="104"/>
-      <c r="E46" s="104"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="104"/>
-      <c r="H46" s="104"/>
-      <c r="I46" s="104"/>
-      <c r="J46" s="105"/>
+      <c r="A46" s="104"/>
+      <c r="B46" s="105"/>
+      <c r="C46" s="105"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="105"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="105"/>
+      <c r="H46" s="105"/>
+      <c r="I46" s="105"/>
+      <c r="J46" s="106"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="103"/>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="105"/>
+      <c r="A47" s="104"/>
+      <c r="B47" s="105"/>
+      <c r="C47" s="105"/>
+      <c r="D47" s="105"/>
+      <c r="E47" s="105"/>
+      <c r="F47" s="105"/>
+      <c r="G47" s="105"/>
+      <c r="H47" s="105"/>
+      <c r="I47" s="105"/>
+      <c r="J47" s="106"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="103"/>
-      <c r="B48" s="104"/>
-      <c r="C48" s="104"/>
-      <c r="D48" s="104"/>
-      <c r="E48" s="104"/>
-      <c r="F48" s="104"/>
-      <c r="G48" s="104"/>
-      <c r="H48" s="104"/>
-      <c r="I48" s="104"/>
-      <c r="J48" s="105"/>
+      <c r="A48" s="104"/>
+      <c r="B48" s="105"/>
+      <c r="C48" s="105"/>
+      <c r="D48" s="105"/>
+      <c r="E48" s="105"/>
+      <c r="F48" s="105"/>
+      <c r="G48" s="105"/>
+      <c r="H48" s="105"/>
+      <c r="I48" s="105"/>
+      <c r="J48" s="106"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="103"/>
-      <c r="B49" s="104"/>
-      <c r="C49" s="104"/>
-      <c r="D49" s="104"/>
-      <c r="E49" s="104"/>
-      <c r="F49" s="104"/>
-      <c r="G49" s="104"/>
-      <c r="H49" s="104"/>
-      <c r="I49" s="104"/>
-      <c r="J49" s="105"/>
+      <c r="A49" s="104"/>
+      <c r="B49" s="105"/>
+      <c r="C49" s="105"/>
+      <c r="D49" s="105"/>
+      <c r="E49" s="105"/>
+      <c r="F49" s="105"/>
+      <c r="G49" s="105"/>
+      <c r="H49" s="105"/>
+      <c r="I49" s="105"/>
+      <c r="J49" s="106"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="106" t="s">
+      <c r="A50" s="107" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="107"/>
-      <c r="C50" s="107"/>
-      <c r="D50" s="107"/>
-      <c r="E50" s="107"/>
-      <c r="F50" s="107" t="s">
+      <c r="B50" s="108"/>
+      <c r="C50" s="108"/>
+      <c r="D50" s="108"/>
+      <c r="E50" s="108"/>
+      <c r="F50" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="G50" s="107"/>
-      <c r="H50" s="107"/>
-      <c r="I50" s="107"/>
-      <c r="J50" s="110"/>
+      <c r="G50" s="108"/>
+      <c r="H50" s="108"/>
+      <c r="I50" s="108"/>
+      <c r="J50" s="111"/>
     </row>
     <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="108"/>
-      <c r="B51" s="109"/>
-      <c r="C51" s="109"/>
-      <c r="D51" s="109"/>
-      <c r="E51" s="109"/>
-      <c r="F51" s="109"/>
-      <c r="G51" s="109"/>
-      <c r="H51" s="109"/>
-      <c r="I51" s="109"/>
-      <c r="J51" s="111"/>
+      <c r="A51" s="109"/>
+      <c r="B51" s="110"/>
+      <c r="C51" s="110"/>
+      <c r="D51" s="110"/>
+      <c r="E51" s="110"/>
+      <c r="F51" s="110"/>
+      <c r="G51" s="110"/>
+      <c r="H51" s="110"/>
+      <c r="I51" s="110"/>
+      <c r="J51" s="112"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="76"/>

--- a/tedarikci-proses-kontrol-formu.xlsx
+++ b/tedarikci-proses-kontrol-formu.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Desktop\Opencode\Akıs-fmea programi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9573CA3E-E9BC-4FA7-934C-A40342C18FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA01447C-1068-44E7-9250-CD08286FB6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Günlük-1" sheetId="8" r:id="rId1"/>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="52">
   <si>
     <t>Proses Adımları</t>
   </si>
@@ -1520,7 +1520,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="227">
+  <cellXfs count="225">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1690,26 +1690,14 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1748,198 +1736,48 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -1994,6 +1832,30 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2013,6 +1875,87 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2023,6 +1966,45 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -2126,20 +2108,13 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2159,6 +2134,14 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2195,6 +2178,14 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2214,124 +2205,127 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3558,373 +3552,367 @@
       <c r="AD9" s="2"/>
     </row>
     <row r="11" spans="2:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="123" t="s">
+      <c r="B11" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="123"/>
-      <c r="D11" s="123"/>
-      <c r="E11" s="123"/>
-      <c r="F11" s="123"/>
-      <c r="G11" s="123"/>
-      <c r="H11" s="123"/>
-      <c r="I11" s="123"/>
-      <c r="J11" s="123"/>
-      <c r="K11" s="123"/>
-      <c r="L11" s="123"/>
-      <c r="M11" s="123"/>
-      <c r="N11" s="123"/>
-      <c r="O11" s="123"/>
-      <c r="P11" s="123"/>
-      <c r="Q11" s="123"/>
-      <c r="R11" s="123"/>
-      <c r="S11" s="123"/>
-      <c r="T11" s="123"/>
-      <c r="U11" s="123"/>
-      <c r="V11" s="123"/>
-      <c r="W11" s="123"/>
-      <c r="X11" s="123"/>
-      <c r="Y11" s="123"/>
-      <c r="Z11" s="123"/>
-      <c r="AA11" s="123"/>
-      <c r="AB11" s="123"/>
-      <c r="AC11" s="123"/>
-      <c r="AD11" s="124"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="71"/>
+      <c r="V11" s="71"/>
+      <c r="W11" s="71"/>
+      <c r="X11" s="71"/>
+      <c r="Y11" s="71"/>
+      <c r="Z11" s="71"/>
+      <c r="AA11" s="71"/>
+      <c r="AB11" s="71"/>
+      <c r="AC11" s="71"/>
+      <c r="AD11" s="72"/>
     </row>
     <row r="12" spans="2:30" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="125"/>
-      <c r="C12" s="125"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="125"/>
-      <c r="F12" s="125"/>
-      <c r="G12" s="125"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="125"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="125"/>
-      <c r="L12" s="125"/>
-      <c r="M12" s="125"/>
-      <c r="N12" s="125"/>
-      <c r="O12" s="125"/>
-      <c r="P12" s="125"/>
-      <c r="Q12" s="125"/>
-      <c r="R12" s="125"/>
-      <c r="S12" s="125"/>
-      <c r="T12" s="125"/>
-      <c r="U12" s="125"/>
-      <c r="V12" s="125"/>
-      <c r="W12" s="125"/>
-      <c r="X12" s="125"/>
-      <c r="Y12" s="125"/>
-      <c r="Z12" s="125"/>
-      <c r="AA12" s="125"/>
-      <c r="AB12" s="125"/>
-      <c r="AC12" s="125"/>
-      <c r="AD12" s="126"/>
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
+      <c r="J12" s="73"/>
+      <c r="K12" s="73"/>
+      <c r="L12" s="73"/>
+      <c r="M12" s="73"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="73"/>
+      <c r="P12" s="73"/>
+      <c r="Q12" s="73"/>
+      <c r="R12" s="73"/>
+      <c r="S12" s="73"/>
+      <c r="T12" s="73"/>
+      <c r="U12" s="73"/>
+      <c r="V12" s="73"/>
+      <c r="W12" s="73"/>
+      <c r="X12" s="73"/>
+      <c r="Y12" s="73"/>
+      <c r="Z12" s="73"/>
+      <c r="AA12" s="73"/>
+      <c r="AB12" s="73"/>
+      <c r="AC12" s="73"/>
+      <c r="AD12" s="74"/>
     </row>
     <row r="13" spans="2:30" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="196" t="s">
+      <c r="B13" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="197"/>
-      <c r="D13" s="139" t="b">
+      <c r="C13" s="70"/>
+      <c r="D13" s="93" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="140"/>
-      <c r="F13" s="196" t="s">
+      <c r="E13" s="94"/>
+      <c r="F13" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="197"/>
-      <c r="H13" s="110"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="111"/>
-      <c r="K13" s="111"/>
-      <c r="L13" s="112"/>
-      <c r="M13" s="198"/>
-      <c r="N13" s="199"/>
-      <c r="O13" s="199"/>
-      <c r="P13" s="199"/>
-      <c r="Q13" s="199"/>
-      <c r="R13" s="199"/>
-      <c r="S13" s="199"/>
-      <c r="T13" s="199"/>
-      <c r="U13" s="199"/>
-      <c r="V13" s="199"/>
-      <c r="W13" s="199"/>
-      <c r="X13" s="199"/>
-      <c r="Y13" s="199"/>
-      <c r="Z13" s="199"/>
-      <c r="AA13" s="199"/>
-      <c r="AB13" s="202"/>
-      <c r="AC13" s="204" t="s">
+      <c r="G13" s="70"/>
+      <c r="H13" s="104"/>
+      <c r="I13" s="105"/>
+      <c r="J13" s="105"/>
+      <c r="K13" s="105"/>
+      <c r="L13" s="106"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="112"/>
+      <c r="O13" s="112"/>
+      <c r="P13" s="112"/>
+      <c r="Q13" s="112"/>
+      <c r="R13" s="112"/>
+      <c r="S13" s="112"/>
+      <c r="T13" s="112"/>
+      <c r="U13" s="112"/>
+      <c r="V13" s="112"/>
+      <c r="W13" s="112"/>
+      <c r="X13" s="112"/>
+      <c r="Y13" s="112"/>
+      <c r="Z13" s="112"/>
+      <c r="AA13" s="112"/>
+      <c r="AB13" s="113"/>
+      <c r="AC13" s="60" t="s">
         <v>15</v>
       </c>
       <c r="AD13" s="5"/>
     </row>
     <row r="14" spans="2:30" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="196" t="s">
+      <c r="B14" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="197"/>
-      <c r="D14" s="139" t="b">
+      <c r="C14" s="70"/>
+      <c r="D14" s="93" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="140"/>
-      <c r="F14" s="196" t="s">
+      <c r="E14" s="94"/>
+      <c r="F14" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="197"/>
-      <c r="H14" s="110"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="111"/>
-      <c r="L14" s="113"/>
-      <c r="M14" s="200"/>
-      <c r="N14" s="201"/>
-      <c r="O14" s="201"/>
-      <c r="P14" s="201"/>
-      <c r="Q14" s="201"/>
-      <c r="R14" s="201"/>
-      <c r="S14" s="201"/>
-      <c r="T14" s="201"/>
-      <c r="U14" s="201"/>
-      <c r="V14" s="201"/>
-      <c r="W14" s="201"/>
-      <c r="X14" s="201"/>
-      <c r="Y14" s="201"/>
-      <c r="Z14" s="201"/>
-      <c r="AA14" s="201"/>
-      <c r="AB14" s="203"/>
-      <c r="AC14" s="205" t="s">
+      <c r="G14" s="70"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="105"/>
+      <c r="J14" s="105"/>
+      <c r="K14" s="105"/>
+      <c r="L14" s="107"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="115"/>
+      <c r="O14" s="115"/>
+      <c r="P14" s="115"/>
+      <c r="Q14" s="115"/>
+      <c r="R14" s="115"/>
+      <c r="S14" s="115"/>
+      <c r="T14" s="115"/>
+      <c r="U14" s="115"/>
+      <c r="V14" s="115"/>
+      <c r="W14" s="115"/>
+      <c r="X14" s="115"/>
+      <c r="Y14" s="115"/>
+      <c r="Z14" s="115"/>
+      <c r="AA14" s="115"/>
+      <c r="AB14" s="116"/>
+      <c r="AC14" s="61" t="s">
         <v>13</v>
       </c>
       <c r="AD14" s="5"/>
     </row>
     <row r="15" spans="2:30" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="136" t="s">
+      <c r="B15" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="137" t="s">
+      <c r="C15" s="85" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="114" t="s">
+      <c r="D15" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="116"/>
-      <c r="F15" s="114" t="s">
+      <c r="E15" s="88"/>
+      <c r="F15" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="104"/>
-      <c r="K15" s="105"/>
-      <c r="L15" s="54" t="s">
+      <c r="G15" s="108"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="98"/>
+      <c r="K15" s="99"/>
+      <c r="L15" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="M15" s="103" t="s">
+      <c r="M15" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="103"/>
-      <c r="O15" s="103"/>
-      <c r="P15" s="103"/>
-      <c r="Q15" s="103"/>
-      <c r="R15" s="103"/>
-      <c r="S15" s="103"/>
-      <c r="T15" s="103"/>
-      <c r="U15" s="103"/>
-      <c r="V15" s="103"/>
-      <c r="W15" s="103"/>
-      <c r="X15" s="103"/>
-      <c r="Y15" s="103"/>
-      <c r="Z15" s="103"/>
-      <c r="AA15" s="103"/>
-      <c r="AB15" s="127" t="s">
+      <c r="N15" s="96"/>
+      <c r="O15" s="96"/>
+      <c r="P15" s="96"/>
+      <c r="Q15" s="96"/>
+      <c r="R15" s="96"/>
+      <c r="S15" s="96"/>
+      <c r="T15" s="96"/>
+      <c r="U15" s="96"/>
+      <c r="V15" s="96"/>
+      <c r="W15" s="96"/>
+      <c r="X15" s="96"/>
+      <c r="Y15" s="96"/>
+      <c r="Z15" s="96"/>
+      <c r="AA15" s="96"/>
+      <c r="AB15" s="75" t="s">
         <v>51</v>
       </c>
-      <c r="AC15" s="130" t="s">
+      <c r="AC15" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="AD15" s="131"/>
+      <c r="AD15" s="79"/>
     </row>
     <row r="16" spans="2:30" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="136"/>
-      <c r="C16" s="137"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="119"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="106"/>
-      <c r="K16" s="107"/>
-      <c r="L16" s="55" t="s">
+      <c r="B16" s="84"/>
+      <c r="C16" s="85"/>
+      <c r="D16" s="89"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="100"/>
+      <c r="K16" s="101"/>
+      <c r="L16" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="N16" s="224"/>
-      <c r="O16" s="225"/>
-      <c r="P16" s="225"/>
-      <c r="Q16" s="225"/>
-      <c r="R16" s="225"/>
-      <c r="S16" s="225"/>
-      <c r="T16" s="225"/>
-      <c r="U16" s="225"/>
-      <c r="V16" s="225"/>
-      <c r="W16" s="225"/>
-      <c r="X16" s="225"/>
-      <c r="Y16" s="225"/>
-      <c r="Z16" s="225"/>
-      <c r="AA16" s="225"/>
-      <c r="AB16" s="127"/>
-      <c r="AC16" s="132"/>
-      <c r="AD16" s="133"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+      <c r="Y16" s="7"/>
+      <c r="Z16" s="7"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="75"/>
+      <c r="AC16" s="80"/>
+      <c r="AD16" s="81"/>
     </row>
     <row r="17" spans="2:34" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="136"/>
-      <c r="C17" s="137"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="119"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="107"/>
-      <c r="L17" s="56" t="s">
+      <c r="B17" s="84"/>
+      <c r="C17" s="85"/>
+      <c r="D17" s="89"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="101"/>
+      <c r="L17" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="M17" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="N17" s="224"/>
-      <c r="O17" s="224"/>
-      <c r="P17" s="224"/>
-      <c r="Q17" s="224"/>
-      <c r="R17" s="224"/>
-      <c r="S17" s="224"/>
-      <c r="T17" s="224"/>
-      <c r="U17" s="224"/>
-      <c r="V17" s="224"/>
-      <c r="W17" s="224"/>
-      <c r="X17" s="224"/>
-      <c r="Y17" s="224"/>
-      <c r="Z17" s="224"/>
-      <c r="AA17" s="224"/>
-      <c r="AB17" s="127"/>
-      <c r="AC17" s="132"/>
-      <c r="AD17" s="133"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="75"/>
+      <c r="AC17" s="80"/>
+      <c r="AD17" s="81"/>
     </row>
     <row r="18" spans="2:34" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="136"/>
-      <c r="C18" s="137"/>
-      <c r="D18" s="120"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="108"/>
-      <c r="K18" s="109"/>
-      <c r="L18" s="56" t="s">
+      <c r="B18" s="84"/>
+      <c r="C18" s="85"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="102"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="52" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="54" t="s">
-        <v>30</v>
-      </c>
-      <c r="N18" s="224"/>
-      <c r="O18" s="224"/>
-      <c r="P18" s="224"/>
-      <c r="Q18" s="224"/>
-      <c r="R18" s="224"/>
-      <c r="S18" s="224"/>
-      <c r="T18" s="224"/>
-      <c r="U18" s="224"/>
-      <c r="V18" s="224"/>
-      <c r="W18" s="224"/>
-      <c r="X18" s="224"/>
-      <c r="Y18" s="224"/>
-      <c r="Z18" s="224"/>
-      <c r="AA18" s="224"/>
-      <c r="AB18" s="127"/>
-      <c r="AC18" s="132"/>
-      <c r="AD18" s="133"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="75"/>
+      <c r="AC18" s="80"/>
+      <c r="AD18" s="81"/>
     </row>
     <row r="19" spans="2:34" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="136"/>
-      <c r="C19" s="137"/>
-      <c r="D19" s="52" t="s">
+      <c r="B19" s="84"/>
+      <c r="C19" s="85"/>
+      <c r="D19" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E19" s="52" t="s">
+      <c r="E19" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F19" s="52" t="s">
+      <c r="F19" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G19" s="52" t="s">
+      <c r="G19" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="52" t="s">
+      <c r="I19" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="138" t="s">
+      <c r="J19" s="86" t="s">
         <v>29</v>
       </c>
-      <c r="K19" s="138"/>
-      <c r="L19" s="138"/>
-      <c r="M19" s="57">
+      <c r="K19" s="86"/>
+      <c r="L19" s="86"/>
+      <c r="M19" s="53">
         <v>1</v>
       </c>
-      <c r="N19" s="57">
+      <c r="N19" s="53">
         <v>2</v>
       </c>
-      <c r="O19" s="57">
+      <c r="O19" s="53">
         <v>3</v>
       </c>
-      <c r="P19" s="57">
+      <c r="P19" s="53">
         <v>4</v>
       </c>
-      <c r="Q19" s="57">
+      <c r="Q19" s="53">
         <v>5</v>
       </c>
-      <c r="R19" s="57">
+      <c r="R19" s="53">
         <v>6</v>
       </c>
-      <c r="S19" s="57">
+      <c r="S19" s="53">
         <v>7</v>
       </c>
-      <c r="T19" s="57">
+      <c r="T19" s="53">
         <v>8</v>
       </c>
-      <c r="U19" s="57">
+      <c r="U19" s="53">
         <v>9</v>
       </c>
-      <c r="V19" s="57">
+      <c r="V19" s="53">
         <v>10</v>
       </c>
-      <c r="W19" s="57">
+      <c r="W19" s="53">
         <v>11</v>
       </c>
-      <c r="X19" s="57">
+      <c r="X19" s="53">
         <v>12</v>
       </c>
-      <c r="Y19" s="57">
+      <c r="Y19" s="53">
         <v>13</v>
       </c>
-      <c r="Z19" s="57">
+      <c r="Z19" s="53">
         <v>14</v>
       </c>
-      <c r="AA19" s="57">
+      <c r="AA19" s="53">
         <v>15</v>
       </c>
-      <c r="AB19" s="127"/>
-      <c r="AC19" s="134"/>
-      <c r="AD19" s="135"/>
+      <c r="AB19" s="75"/>
+      <c r="AC19" s="82"/>
+      <c r="AD19" s="83"/>
     </row>
     <row r="20" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="9">
@@ -3936,10 +3924,10 @@
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="7"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="102"/>
-      <c r="K20" s="102"/>
-      <c r="L20" s="102"/>
+      <c r="I20" s="54"/>
+      <c r="J20" s="95"/>
+      <c r="K20" s="95"/>
+      <c r="L20" s="95"/>
       <c r="M20" s="14"/>
       <c r="N20" s="15"/>
       <c r="O20" s="15"/>
@@ -3956,8 +3944,8 @@
       <c r="Z20" s="15"/>
       <c r="AA20" s="15"/>
       <c r="AB20" s="42"/>
-      <c r="AC20" s="128"/>
-      <c r="AD20" s="129"/>
+      <c r="AC20" s="76"/>
+      <c r="AD20" s="77"/>
     </row>
     <row r="21" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="9">
@@ -3969,10 +3957,10 @@
       <c r="F21" s="9"/>
       <c r="G21" s="9"/>
       <c r="H21" s="7"/>
-      <c r="I21" s="58"/>
-      <c r="J21" s="102"/>
-      <c r="K21" s="102"/>
-      <c r="L21" s="102"/>
+      <c r="I21" s="54"/>
+      <c r="J21" s="95"/>
+      <c r="K21" s="95"/>
+      <c r="L21" s="95"/>
       <c r="M21" s="16"/>
       <c r="N21" s="16"/>
       <c r="O21" s="16"/>
@@ -3989,8 +3977,8 @@
       <c r="Z21" s="16"/>
       <c r="AA21" s="16"/>
       <c r="AB21" s="42"/>
-      <c r="AC21" s="99"/>
-      <c r="AD21" s="101"/>
+      <c r="AC21" s="67"/>
+      <c r="AD21" s="68"/>
     </row>
     <row r="22" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="9">
@@ -3998,14 +3986,14 @@
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="8"/>
-      <c r="E22" s="63"/>
+      <c r="E22" s="59"/>
       <c r="F22" s="9"/>
       <c r="G22" s="9"/>
       <c r="H22" s="7"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="99"/>
-      <c r="K22" s="100"/>
-      <c r="L22" s="101"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="67"/>
+      <c r="K22" s="97"/>
+      <c r="L22" s="68"/>
       <c r="M22" s="16"/>
       <c r="N22" s="16"/>
       <c r="O22" s="16"/>
@@ -4022,8 +4010,8 @@
       <c r="Z22" s="16"/>
       <c r="AA22" s="16"/>
       <c r="AB22" s="42"/>
-      <c r="AC22" s="99"/>
-      <c r="AD22" s="101"/>
+      <c r="AC22" s="67"/>
+      <c r="AD22" s="68"/>
     </row>
     <row r="23" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="9">
@@ -4035,10 +4023,10 @@
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
       <c r="H23" s="7"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="99"/>
-      <c r="K23" s="100"/>
-      <c r="L23" s="101"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="67"/>
+      <c r="K23" s="97"/>
+      <c r="L23" s="68"/>
       <c r="M23" s="16"/>
       <c r="N23" s="16"/>
       <c r="O23" s="16"/>
@@ -4055,8 +4043,8 @@
       <c r="Z23" s="16"/>
       <c r="AA23" s="16"/>
       <c r="AB23" s="42"/>
-      <c r="AC23" s="99"/>
-      <c r="AD23" s="101"/>
+      <c r="AC23" s="67"/>
+      <c r="AD23" s="68"/>
     </row>
     <row r="24" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="9">
@@ -4068,10 +4056,10 @@
       <c r="F24" s="9"/>
       <c r="G24" s="9"/>
       <c r="H24" s="7"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="99"/>
-      <c r="K24" s="100"/>
-      <c r="L24" s="101"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="67"/>
+      <c r="K24" s="97"/>
+      <c r="L24" s="68"/>
       <c r="M24" s="16"/>
       <c r="N24" s="16"/>
       <c r="O24" s="16"/>
@@ -4088,8 +4076,8 @@
       <c r="Z24" s="16"/>
       <c r="AA24" s="16"/>
       <c r="AB24" s="42"/>
-      <c r="AC24" s="99"/>
-      <c r="AD24" s="101"/>
+      <c r="AC24" s="67"/>
+      <c r="AD24" s="68"/>
     </row>
     <row r="25" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="9">
@@ -4101,10 +4089,10 @@
       <c r="F25" s="9"/>
       <c r="G25" s="9"/>
       <c r="H25" s="7"/>
-      <c r="I25" s="58"/>
-      <c r="J25" s="99"/>
-      <c r="K25" s="100"/>
-      <c r="L25" s="101"/>
+      <c r="I25" s="54"/>
+      <c r="J25" s="67"/>
+      <c r="K25" s="97"/>
+      <c r="L25" s="68"/>
       <c r="M25" s="16"/>
       <c r="N25" s="16"/>
       <c r="O25" s="16"/>
@@ -4121,8 +4109,8 @@
       <c r="Z25" s="16"/>
       <c r="AA25" s="16"/>
       <c r="AB25" s="42"/>
-      <c r="AC25" s="99"/>
-      <c r="AD25" s="101"/>
+      <c r="AC25" s="67"/>
+      <c r="AD25" s="68"/>
     </row>
     <row r="26" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="9">
@@ -4134,10 +4122,10 @@
       <c r="F26" s="9"/>
       <c r="G26" s="9"/>
       <c r="H26" s="7"/>
-      <c r="I26" s="58"/>
-      <c r="J26" s="99"/>
-      <c r="K26" s="100"/>
-      <c r="L26" s="101"/>
+      <c r="I26" s="54"/>
+      <c r="J26" s="67"/>
+      <c r="K26" s="97"/>
+      <c r="L26" s="68"/>
       <c r="M26" s="16"/>
       <c r="N26" s="16"/>
       <c r="O26" s="16"/>
@@ -4154,8 +4142,8 @@
       <c r="Z26" s="16"/>
       <c r="AA26" s="16"/>
       <c r="AB26" s="42"/>
-      <c r="AC26" s="99"/>
-      <c r="AD26" s="101"/>
+      <c r="AC26" s="67"/>
+      <c r="AD26" s="68"/>
       <c r="AG26" s="4" t="s">
         <v>19</v>
       </c>
@@ -4170,10 +4158,10 @@
       <c r="F27" s="9"/>
       <c r="G27" s="9"/>
       <c r="H27" s="7"/>
-      <c r="I27" s="58"/>
-      <c r="J27" s="99"/>
-      <c r="K27" s="100"/>
-      <c r="L27" s="101"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="67"/>
+      <c r="K27" s="97"/>
+      <c r="L27" s="68"/>
       <c r="M27" s="16"/>
       <c r="N27" s="16"/>
       <c r="O27" s="16"/>
@@ -4190,8 +4178,8 @@
       <c r="Z27" s="16"/>
       <c r="AA27" s="16"/>
       <c r="AB27" s="42"/>
-      <c r="AC27" s="99"/>
-      <c r="AD27" s="101"/>
+      <c r="AC27" s="67"/>
+      <c r="AD27" s="68"/>
       <c r="AG27" s="4" t="s">
         <v>20</v>
       </c>
@@ -4206,10 +4194,10 @@
       <c r="F28" s="9"/>
       <c r="G28" s="9"/>
       <c r="H28" s="7"/>
-      <c r="I28" s="58"/>
-      <c r="J28" s="99"/>
-      <c r="K28" s="100"/>
-      <c r="L28" s="101"/>
+      <c r="I28" s="54"/>
+      <c r="J28" s="67"/>
+      <c r="K28" s="97"/>
+      <c r="L28" s="68"/>
       <c r="M28" s="16"/>
       <c r="N28" s="16"/>
       <c r="O28" s="16"/>
@@ -4226,8 +4214,8 @@
       <c r="Z28" s="16"/>
       <c r="AA28" s="16"/>
       <c r="AB28" s="42"/>
-      <c r="AC28" s="99"/>
-      <c r="AD28" s="101"/>
+      <c r="AC28" s="67"/>
+      <c r="AD28" s="68"/>
       <c r="AG28" s="4" t="s">
         <v>25</v>
       </c>
@@ -4242,10 +4230,10 @@
       <c r="F29" s="9"/>
       <c r="G29" s="9"/>
       <c r="H29" s="7"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="99"/>
-      <c r="K29" s="100"/>
-      <c r="L29" s="101"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="97"/>
+      <c r="L29" s="68"/>
       <c r="M29" s="16"/>
       <c r="N29" s="16"/>
       <c r="O29" s="16"/>
@@ -4262,8 +4250,8 @@
       <c r="Z29" s="16"/>
       <c r="AA29" s="16"/>
       <c r="AB29" s="42"/>
-      <c r="AC29" s="99"/>
-      <c r="AD29" s="101"/>
+      <c r="AC29" s="67"/>
+      <c r="AD29" s="68"/>
     </row>
     <row r="30" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="9">
@@ -4275,10 +4263,10 @@
       <c r="F30" s="9"/>
       <c r="G30" s="9"/>
       <c r="H30" s="7"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="99"/>
-      <c r="K30" s="100"/>
-      <c r="L30" s="101"/>
+      <c r="I30" s="54"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="97"/>
+      <c r="L30" s="68"/>
       <c r="M30" s="16"/>
       <c r="N30" s="16"/>
       <c r="O30" s="16"/>
@@ -4295,8 +4283,8 @@
       <c r="Z30" s="16"/>
       <c r="AA30" s="16"/>
       <c r="AB30" s="42"/>
-      <c r="AC30" s="99"/>
-      <c r="AD30" s="101"/>
+      <c r="AC30" s="67"/>
+      <c r="AD30" s="68"/>
       <c r="AH30" s="10" t="s">
         <v>21</v>
       </c>
@@ -4311,10 +4299,10 @@
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>
       <c r="H31" s="7"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="100"/>
-      <c r="L31" s="101"/>
+      <c r="I31" s="54"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="97"/>
+      <c r="L31" s="68"/>
       <c r="M31" s="16"/>
       <c r="N31" s="16"/>
       <c r="O31" s="16"/>
@@ -4331,8 +4319,8 @@
       <c r="Z31" s="16"/>
       <c r="AA31" s="16"/>
       <c r="AB31" s="42"/>
-      <c r="AC31" s="99"/>
-      <c r="AD31" s="101"/>
+      <c r="AC31" s="67"/>
+      <c r="AD31" s="68"/>
       <c r="AH31" s="10" t="s">
         <v>22</v>
       </c>
@@ -4347,10 +4335,10 @@
       <c r="F32" s="9"/>
       <c r="G32" s="9"/>
       <c r="H32" s="7"/>
-      <c r="I32" s="58"/>
-      <c r="J32" s="99"/>
-      <c r="K32" s="100"/>
-      <c r="L32" s="101"/>
+      <c r="I32" s="54"/>
+      <c r="J32" s="67"/>
+      <c r="K32" s="97"/>
+      <c r="L32" s="68"/>
       <c r="M32" s="16"/>
       <c r="N32" s="16"/>
       <c r="O32" s="16"/>
@@ -4367,8 +4355,8 @@
       <c r="Z32" s="16"/>
       <c r="AA32" s="16"/>
       <c r="AB32" s="42"/>
-      <c r="AC32" s="99"/>
-      <c r="AD32" s="101"/>
+      <c r="AC32" s="67"/>
+      <c r="AD32" s="68"/>
       <c r="AH32" s="10" t="s">
         <v>23</v>
       </c>
@@ -4383,10 +4371,10 @@
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
       <c r="H33" s="7"/>
-      <c r="I33" s="58"/>
-      <c r="J33" s="99"/>
-      <c r="K33" s="100"/>
-      <c r="L33" s="101"/>
+      <c r="I33" s="54"/>
+      <c r="J33" s="67"/>
+      <c r="K33" s="97"/>
+      <c r="L33" s="68"/>
       <c r="M33" s="17"/>
       <c r="N33" s="17"/>
       <c r="O33" s="17"/>
@@ -4403,8 +4391,8 @@
       <c r="Z33" s="17"/>
       <c r="AA33" s="17"/>
       <c r="AB33" s="43"/>
-      <c r="AC33" s="99"/>
-      <c r="AD33" s="101"/>
+      <c r="AC33" s="67"/>
+      <c r="AD33" s="68"/>
       <c r="AH33" s="10" t="s">
         <v>24</v>
       </c>
@@ -4419,10 +4407,10 @@
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
       <c r="H34" s="7"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="99"/>
-      <c r="K34" s="100"/>
-      <c r="L34" s="101"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="67"/>
+      <c r="K34" s="97"/>
+      <c r="L34" s="68"/>
       <c r="M34" s="16"/>
       <c r="N34" s="16"/>
       <c r="O34" s="16"/>
@@ -4439,8 +4427,8 @@
       <c r="Z34" s="16"/>
       <c r="AA34" s="16"/>
       <c r="AB34" s="42"/>
-      <c r="AC34" s="99"/>
-      <c r="AD34" s="101"/>
+      <c r="AC34" s="67"/>
+      <c r="AD34" s="68"/>
     </row>
     <row r="35" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="9">
@@ -4452,10 +4440,10 @@
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="99"/>
-      <c r="K35" s="100"/>
-      <c r="L35" s="101"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="67"/>
+      <c r="K35" s="97"/>
+      <c r="L35" s="68"/>
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
       <c r="O35" s="16"/>
@@ -4472,8 +4460,8 @@
       <c r="Z35" s="16"/>
       <c r="AA35" s="16"/>
       <c r="AB35" s="42"/>
-      <c r="AC35" s="99"/>
-      <c r="AD35" s="101"/>
+      <c r="AC35" s="67"/>
+      <c r="AD35" s="68"/>
     </row>
     <row r="36" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="9">
@@ -4485,10 +4473,10 @@
       <c r="F36" s="12"/>
       <c r="G36" s="12"/>
       <c r="H36" s="7"/>
-      <c r="I36" s="58"/>
-      <c r="J36" s="99"/>
-      <c r="K36" s="100"/>
-      <c r="L36" s="101"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="67"/>
+      <c r="K36" s="97"/>
+      <c r="L36" s="68"/>
       <c r="M36" s="17"/>
       <c r="N36" s="17"/>
       <c r="O36" s="17"/>
@@ -4505,8 +4493,8 @@
       <c r="Z36" s="17"/>
       <c r="AA36" s="17"/>
       <c r="AB36" s="43"/>
-      <c r="AC36" s="99"/>
-      <c r="AD36" s="101"/>
+      <c r="AC36" s="67"/>
+      <c r="AD36" s="68"/>
     </row>
     <row r="37" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="9">
@@ -4518,10 +4506,10 @@
       <c r="F37" s="9"/>
       <c r="G37" s="9"/>
       <c r="H37" s="7"/>
-      <c r="I37" s="58"/>
-      <c r="J37" s="99"/>
-      <c r="K37" s="100"/>
-      <c r="L37" s="101"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="67"/>
+      <c r="K37" s="97"/>
+      <c r="L37" s="68"/>
       <c r="M37" s="16"/>
       <c r="N37" s="16"/>
       <c r="O37" s="16"/>
@@ -4538,8 +4526,8 @@
       <c r="Z37" s="16"/>
       <c r="AA37" s="16"/>
       <c r="AB37" s="42"/>
-      <c r="AC37" s="99"/>
-      <c r="AD37" s="101"/>
+      <c r="AC37" s="67"/>
+      <c r="AD37" s="68"/>
     </row>
     <row r="38" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="9">
@@ -4551,10 +4539,10 @@
       <c r="F38" s="9"/>
       <c r="G38" s="9"/>
       <c r="H38" s="7"/>
-      <c r="I38" s="58"/>
-      <c r="J38" s="99"/>
-      <c r="K38" s="100"/>
-      <c r="L38" s="101"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="67"/>
+      <c r="K38" s="97"/>
+      <c r="L38" s="68"/>
       <c r="M38" s="16"/>
       <c r="N38" s="16"/>
       <c r="O38" s="16"/>
@@ -4571,8 +4559,8 @@
       <c r="Z38" s="16"/>
       <c r="AA38" s="16"/>
       <c r="AB38" s="42"/>
-      <c r="AC38" s="99"/>
-      <c r="AD38" s="101"/>
+      <c r="AC38" s="67"/>
+      <c r="AD38" s="68"/>
     </row>
     <row r="39" spans="2:34" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="9">
@@ -4584,10 +4572,10 @@
       <c r="F39" s="12"/>
       <c r="G39" s="12"/>
       <c r="H39" s="7"/>
-      <c r="I39" s="58"/>
-      <c r="J39" s="99"/>
-      <c r="K39" s="100"/>
-      <c r="L39" s="101"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="67"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="68"/>
       <c r="M39" s="17"/>
       <c r="N39" s="17"/>
       <c r="O39" s="17"/>
@@ -4604,12 +4592,55 @@
       <c r="Z39" s="17"/>
       <c r="AA39" s="17"/>
       <c r="AB39" s="43"/>
-      <c r="AC39" s="99"/>
-      <c r="AD39" s="101"/>
+      <c r="AC39" s="67"/>
+      <c r="AD39" s="68"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
   <mergeCells count="59">
+    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="J31:L31"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="J25:L25"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="M15:AA15"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="J15:K18"/>
+    <mergeCell ref="H13:L13"/>
+    <mergeCell ref="H14:L14"/>
+    <mergeCell ref="F15:I18"/>
+    <mergeCell ref="M13:AB14"/>
+    <mergeCell ref="AC37:AD37"/>
+    <mergeCell ref="AC38:AD38"/>
+    <mergeCell ref="AC39:AD39"/>
+    <mergeCell ref="AC31:AD31"/>
+    <mergeCell ref="AC32:AD32"/>
+    <mergeCell ref="AC33:AD33"/>
+    <mergeCell ref="AC34:AD34"/>
+    <mergeCell ref="AC35:AD35"/>
+    <mergeCell ref="AC27:AD27"/>
+    <mergeCell ref="AC28:AD28"/>
+    <mergeCell ref="AC29:AD29"/>
+    <mergeCell ref="AC30:AD30"/>
+    <mergeCell ref="AC36:AD36"/>
+    <mergeCell ref="AC22:AD22"/>
+    <mergeCell ref="AC23:AD23"/>
+    <mergeCell ref="AC24:AD24"/>
+    <mergeCell ref="AC25:AD25"/>
+    <mergeCell ref="AC26:AD26"/>
     <mergeCell ref="AC21:AD21"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
@@ -4626,49 +4657,6 @@
     <mergeCell ref="F13:G13"/>
     <mergeCell ref="F14:G14"/>
     <mergeCell ref="J20:L20"/>
-    <mergeCell ref="AC22:AD22"/>
-    <mergeCell ref="AC23:AD23"/>
-    <mergeCell ref="AC24:AD24"/>
-    <mergeCell ref="AC25:AD25"/>
-    <mergeCell ref="AC26:AD26"/>
-    <mergeCell ref="AC27:AD27"/>
-    <mergeCell ref="AC28:AD28"/>
-    <mergeCell ref="AC29:AD29"/>
-    <mergeCell ref="AC30:AD30"/>
-    <mergeCell ref="AC36:AD36"/>
-    <mergeCell ref="AC37:AD37"/>
-    <mergeCell ref="AC38:AD38"/>
-    <mergeCell ref="AC39:AD39"/>
-    <mergeCell ref="AC31:AD31"/>
-    <mergeCell ref="AC32:AD32"/>
-    <mergeCell ref="AC33:AD33"/>
-    <mergeCell ref="AC34:AD34"/>
-    <mergeCell ref="AC35:AD35"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="M15:AA15"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="J15:K18"/>
-    <mergeCell ref="H13:L13"/>
-    <mergeCell ref="H14:L14"/>
-    <mergeCell ref="F15:I18"/>
-    <mergeCell ref="M13:AB14"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="J25:L25"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="J31:L31"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="J38:L38"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="J36:L36"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M20:AA39" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -4786,378 +4774,378 @@
       <c r="AE9" s="18"/>
     </row>
     <row r="11" spans="2:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="144" t="s">
+      <c r="B11" s="131" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="144"/>
-      <c r="L11" s="144"/>
-      <c r="M11" s="144"/>
-      <c r="N11" s="144"/>
-      <c r="O11" s="144"/>
-      <c r="P11" s="144"/>
-      <c r="Q11" s="144"/>
-      <c r="R11" s="144"/>
-      <c r="S11" s="144"/>
-      <c r="T11" s="144"/>
-      <c r="U11" s="144"/>
-      <c r="V11" s="144"/>
-      <c r="W11" s="144"/>
-      <c r="X11" s="144"/>
-      <c r="Y11" s="144"/>
-      <c r="Z11" s="144"/>
-      <c r="AA11" s="144"/>
-      <c r="AB11" s="144"/>
-      <c r="AC11" s="144"/>
-      <c r="AD11" s="144"/>
-      <c r="AE11" s="145"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="131"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="131"/>
+      <c r="N11" s="131"/>
+      <c r="O11" s="131"/>
+      <c r="P11" s="131"/>
+      <c r="Q11" s="131"/>
+      <c r="R11" s="131"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="131"/>
+      <c r="U11" s="131"/>
+      <c r="V11" s="131"/>
+      <c r="W11" s="131"/>
+      <c r="X11" s="131"/>
+      <c r="Y11" s="131"/>
+      <c r="Z11" s="131"/>
+      <c r="AA11" s="131"/>
+      <c r="AB11" s="131"/>
+      <c r="AC11" s="131"/>
+      <c r="AD11" s="131"/>
+      <c r="AE11" s="132"/>
     </row>
     <row r="12" spans="2:31" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="146"/>
-      <c r="C12" s="146"/>
-      <c r="D12" s="146"/>
-      <c r="E12" s="146"/>
-      <c r="F12" s="146"/>
-      <c r="G12" s="146"/>
-      <c r="H12" s="146"/>
-      <c r="I12" s="146"/>
-      <c r="J12" s="146"/>
-      <c r="K12" s="146"/>
-      <c r="L12" s="146"/>
-      <c r="M12" s="146"/>
-      <c r="N12" s="146"/>
-      <c r="O12" s="146"/>
-      <c r="P12" s="146"/>
-      <c r="Q12" s="146"/>
-      <c r="R12" s="146"/>
-      <c r="S12" s="146"/>
-      <c r="T12" s="146"/>
-      <c r="U12" s="146"/>
-      <c r="V12" s="146"/>
-      <c r="W12" s="146"/>
-      <c r="X12" s="146"/>
-      <c r="Y12" s="146"/>
-      <c r="Z12" s="146"/>
-      <c r="AA12" s="146"/>
-      <c r="AB12" s="146"/>
-      <c r="AC12" s="146"/>
-      <c r="AD12" s="146"/>
-      <c r="AE12" s="147"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="133"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="133"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="133"/>
+      <c r="M12" s="133"/>
+      <c r="N12" s="133"/>
+      <c r="O12" s="133"/>
+      <c r="P12" s="133"/>
+      <c r="Q12" s="133"/>
+      <c r="R12" s="133"/>
+      <c r="S12" s="133"/>
+      <c r="T12" s="133"/>
+      <c r="U12" s="133"/>
+      <c r="V12" s="133"/>
+      <c r="W12" s="133"/>
+      <c r="X12" s="133"/>
+      <c r="Y12" s="133"/>
+      <c r="Z12" s="133"/>
+      <c r="AA12" s="133"/>
+      <c r="AB12" s="133"/>
+      <c r="AC12" s="133"/>
+      <c r="AD12" s="133"/>
+      <c r="AE12" s="134"/>
     </row>
     <row r="13" spans="2:31" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="206" t="s">
+      <c r="B13" s="160" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="207"/>
-      <c r="D13" s="139" t="b">
+      <c r="C13" s="161"/>
+      <c r="D13" s="93" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="140"/>
-      <c r="F13" s="196" t="s">
+      <c r="E13" s="94"/>
+      <c r="F13" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="197"/>
-      <c r="H13" s="170"/>
-      <c r="I13" s="171"/>
-      <c r="J13" s="171"/>
-      <c r="K13" s="171"/>
-      <c r="L13" s="172"/>
-      <c r="M13" s="218"/>
-      <c r="N13" s="219"/>
-      <c r="O13" s="219"/>
-      <c r="P13" s="219"/>
-      <c r="Q13" s="219"/>
-      <c r="R13" s="219"/>
-      <c r="S13" s="219"/>
-      <c r="T13" s="219"/>
-      <c r="U13" s="219"/>
-      <c r="V13" s="219"/>
-      <c r="W13" s="219"/>
-      <c r="X13" s="219"/>
-      <c r="Y13" s="219"/>
-      <c r="Z13" s="219"/>
-      <c r="AA13" s="219"/>
-      <c r="AB13" s="219"/>
-      <c r="AC13" s="220"/>
-      <c r="AD13" s="208" t="s">
+      <c r="G13" s="70"/>
+      <c r="H13" s="157"/>
+      <c r="I13" s="158"/>
+      <c r="J13" s="158"/>
+      <c r="K13" s="158"/>
+      <c r="L13" s="159"/>
+      <c r="M13" s="125"/>
+      <c r="N13" s="126"/>
+      <c r="O13" s="126"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="126"/>
+      <c r="S13" s="126"/>
+      <c r="T13" s="126"/>
+      <c r="U13" s="126"/>
+      <c r="V13" s="126"/>
+      <c r="W13" s="126"/>
+      <c r="X13" s="126"/>
+      <c r="Y13" s="126"/>
+      <c r="Z13" s="126"/>
+      <c r="AA13" s="126"/>
+      <c r="AB13" s="126"/>
+      <c r="AC13" s="127"/>
+      <c r="AD13" s="62" t="s">
         <v>15</v>
       </c>
       <c r="AE13" s="21"/>
     </row>
     <row r="14" spans="2:31" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="206" t="s">
+      <c r="B14" s="160" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="207"/>
-      <c r="D14" s="139" t="b">
+      <c r="C14" s="161"/>
+      <c r="D14" s="93" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="140"/>
-      <c r="F14" s="196" t="s">
+      <c r="E14" s="94"/>
+      <c r="F14" s="69" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="197"/>
-      <c r="H14" s="170"/>
-      <c r="I14" s="171"/>
-      <c r="J14" s="171"/>
-      <c r="K14" s="171"/>
-      <c r="L14" s="172"/>
-      <c r="M14" s="221"/>
-      <c r="N14" s="222"/>
-      <c r="O14" s="222"/>
-      <c r="P14" s="222"/>
-      <c r="Q14" s="222"/>
-      <c r="R14" s="222"/>
-      <c r="S14" s="222"/>
-      <c r="T14" s="222"/>
-      <c r="U14" s="222"/>
-      <c r="V14" s="222"/>
-      <c r="W14" s="222"/>
-      <c r="X14" s="222"/>
-      <c r="Y14" s="222"/>
-      <c r="Z14" s="222"/>
-      <c r="AA14" s="222"/>
-      <c r="AB14" s="222"/>
-      <c r="AC14" s="223"/>
-      <c r="AD14" s="209" t="s">
+      <c r="G14" s="70"/>
+      <c r="H14" s="157"/>
+      <c r="I14" s="158"/>
+      <c r="J14" s="158"/>
+      <c r="K14" s="158"/>
+      <c r="L14" s="159"/>
+      <c r="M14" s="128"/>
+      <c r="N14" s="129"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="129"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="129"/>
+      <c r="S14" s="129"/>
+      <c r="T14" s="129"/>
+      <c r="U14" s="129"/>
+      <c r="V14" s="129"/>
+      <c r="W14" s="129"/>
+      <c r="X14" s="129"/>
+      <c r="Y14" s="129"/>
+      <c r="Z14" s="129"/>
+      <c r="AA14" s="129"/>
+      <c r="AB14" s="129"/>
+      <c r="AC14" s="130"/>
+      <c r="AD14" s="63" t="s">
         <v>13</v>
       </c>
       <c r="AE14" s="21"/>
     </row>
     <row r="15" spans="2:31" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="148" t="s">
+      <c r="B15" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="149" t="s">
+      <c r="C15" s="136" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="150" t="s">
+      <c r="D15" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="151"/>
-      <c r="F15" s="114" t="s">
+      <c r="E15" s="138"/>
+      <c r="F15" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="164"/>
-      <c r="K15" s="165"/>
-      <c r="L15" s="46" t="s">
+      <c r="G15" s="108"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="151"/>
+      <c r="K15" s="152"/>
+      <c r="L15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="M15" s="156" t="s">
+      <c r="M15" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="156"/>
-      <c r="O15" s="156"/>
-      <c r="P15" s="156"/>
-      <c r="Q15" s="156"/>
-      <c r="R15" s="156"/>
-      <c r="S15" s="156"/>
-      <c r="T15" s="156"/>
-      <c r="U15" s="156"/>
-      <c r="V15" s="156"/>
-      <c r="W15" s="156"/>
-      <c r="X15" s="156"/>
-      <c r="Y15" s="156"/>
-      <c r="Z15" s="156"/>
-      <c r="AA15" s="156"/>
-      <c r="AB15" s="156"/>
-      <c r="AC15" s="149" t="s">
+      <c r="N15" s="143"/>
+      <c r="O15" s="143"/>
+      <c r="P15" s="143"/>
+      <c r="Q15" s="143"/>
+      <c r="R15" s="143"/>
+      <c r="S15" s="143"/>
+      <c r="T15" s="143"/>
+      <c r="U15" s="143"/>
+      <c r="V15" s="143"/>
+      <c r="W15" s="143"/>
+      <c r="X15" s="143"/>
+      <c r="Y15" s="143"/>
+      <c r="Z15" s="143"/>
+      <c r="AA15" s="143"/>
+      <c r="AB15" s="143"/>
+      <c r="AC15" s="136" t="s">
         <v>51</v>
       </c>
-      <c r="AD15" s="157" t="s">
+      <c r="AD15" s="144" t="s">
         <v>10</v>
       </c>
-      <c r="AE15" s="158"/>
+      <c r="AE15" s="145"/>
     </row>
     <row r="16" spans="2:31" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="148"/>
-      <c r="C16" s="149"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="153"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="166"/>
-      <c r="K16" s="167"/>
-      <c r="L16" s="48" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="153"/>
+      <c r="K16" s="154"/>
+      <c r="L16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="M16" s="217"/>
-      <c r="N16" s="217"/>
-      <c r="O16" s="226"/>
-      <c r="P16" s="226"/>
-      <c r="Q16" s="226"/>
-      <c r="R16" s="226"/>
-      <c r="S16" s="226"/>
-      <c r="T16" s="226"/>
-      <c r="U16" s="226"/>
-      <c r="V16" s="226"/>
-      <c r="W16" s="226"/>
-      <c r="X16" s="226"/>
-      <c r="Y16" s="226"/>
-      <c r="Z16" s="226"/>
-      <c r="AA16" s="226"/>
-      <c r="AB16" s="226"/>
-      <c r="AC16" s="149"/>
-      <c r="AD16" s="159"/>
-      <c r="AE16" s="160"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="U16" s="1"/>
+      <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
+      <c r="X16" s="1"/>
+      <c r="Y16" s="1"/>
+      <c r="Z16" s="1"/>
+      <c r="AA16" s="1"/>
+      <c r="AB16" s="1"/>
+      <c r="AC16" s="136"/>
+      <c r="AD16" s="146"/>
+      <c r="AE16" s="147"/>
     </row>
     <row r="17" spans="2:35" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="148"/>
-      <c r="C17" s="149"/>
-      <c r="D17" s="152"/>
-      <c r="E17" s="153"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="166"/>
-      <c r="K17" s="167"/>
-      <c r="L17" s="49" t="s">
+      <c r="B17" s="135"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="153"/>
+      <c r="K17" s="154"/>
+      <c r="L17" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="M17" s="217"/>
-      <c r="N17" s="217"/>
-      <c r="O17" s="217"/>
-      <c r="P17" s="217"/>
-      <c r="Q17" s="217"/>
-      <c r="R17" s="217"/>
-      <c r="S17" s="217"/>
-      <c r="T17" s="217"/>
-      <c r="U17" s="217"/>
-      <c r="V17" s="217"/>
-      <c r="W17" s="217"/>
-      <c r="X17" s="217"/>
-      <c r="Y17" s="217"/>
-      <c r="Z17" s="217"/>
-      <c r="AA17" s="217"/>
-      <c r="AB17" s="217"/>
-      <c r="AC17" s="149"/>
-      <c r="AD17" s="159"/>
-      <c r="AE17" s="160"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="22"/>
+      <c r="Z17" s="22"/>
+      <c r="AA17" s="22"/>
+      <c r="AB17" s="22"/>
+      <c r="AC17" s="136"/>
+      <c r="AD17" s="146"/>
+      <c r="AE17" s="147"/>
     </row>
     <row r="18" spans="2:35" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="148"/>
-      <c r="C18" s="149"/>
-      <c r="D18" s="154"/>
-      <c r="E18" s="155"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="168"/>
-      <c r="K18" s="169"/>
-      <c r="L18" s="49" t="s">
+      <c r="B18" s="135"/>
+      <c r="C18" s="136"/>
+      <c r="D18" s="141"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="155"/>
+      <c r="K18" s="156"/>
+      <c r="L18" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="M18" s="217"/>
-      <c r="N18" s="217"/>
-      <c r="O18" s="217"/>
-      <c r="P18" s="217"/>
-      <c r="Q18" s="217"/>
-      <c r="R18" s="217"/>
-      <c r="S18" s="217"/>
-      <c r="T18" s="217"/>
-      <c r="U18" s="217"/>
-      <c r="V18" s="217"/>
-      <c r="W18" s="217"/>
-      <c r="X18" s="217"/>
-      <c r="Y18" s="217"/>
-      <c r="Z18" s="217"/>
-      <c r="AA18" s="217"/>
-      <c r="AB18" s="217"/>
-      <c r="AC18" s="149"/>
-      <c r="AD18" s="159"/>
-      <c r="AE18" s="160"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="22"/>
+      <c r="Y18" s="22"/>
+      <c r="Z18" s="22"/>
+      <c r="AA18" s="22"/>
+      <c r="AB18" s="22"/>
+      <c r="AC18" s="136"/>
+      <c r="AD18" s="146"/>
+      <c r="AE18" s="147"/>
     </row>
     <row r="19" spans="2:35" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="148"/>
-      <c r="C19" s="149"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="136"/>
       <c r="D19" s="44" t="s">
         <v>1</v>
       </c>
       <c r="E19" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="F19" s="52" t="s">
+      <c r="F19" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G19" s="52" t="s">
+      <c r="G19" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="52" t="s">
+      <c r="I19" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="163" t="s">
+      <c r="J19" s="150" t="s">
         <v>29</v>
       </c>
-      <c r="K19" s="163"/>
-      <c r="L19" s="163"/>
-      <c r="M19" s="53">
+      <c r="K19" s="150"/>
+      <c r="L19" s="150"/>
+      <c r="M19" s="49">
         <v>16</v>
       </c>
-      <c r="N19" s="53">
+      <c r="N19" s="49">
         <v>17</v>
       </c>
-      <c r="O19" s="53">
+      <c r="O19" s="49">
         <v>18</v>
       </c>
-      <c r="P19" s="53">
+      <c r="P19" s="49">
         <v>19</v>
       </c>
-      <c r="Q19" s="53">
+      <c r="Q19" s="49">
         <v>20</v>
       </c>
-      <c r="R19" s="53">
+      <c r="R19" s="49">
         <v>21</v>
       </c>
-      <c r="S19" s="53">
+      <c r="S19" s="49">
         <v>22</v>
       </c>
-      <c r="T19" s="53">
+      <c r="T19" s="49">
         <v>23</v>
       </c>
-      <c r="U19" s="53">
+      <c r="U19" s="49">
         <v>24</v>
       </c>
-      <c r="V19" s="53">
+      <c r="V19" s="49">
         <v>25</v>
       </c>
-      <c r="W19" s="53">
+      <c r="W19" s="49">
         <v>26</v>
       </c>
-      <c r="X19" s="53">
+      <c r="X19" s="49">
         <v>27</v>
       </c>
-      <c r="Y19" s="53">
+      <c r="Y19" s="49">
         <v>28</v>
       </c>
-      <c r="Z19" s="53">
+      <c r="Z19" s="49">
         <v>29</v>
       </c>
-      <c r="AA19" s="53">
+      <c r="AA19" s="49">
         <v>30</v>
       </c>
-      <c r="AB19" s="53">
+      <c r="AB19" s="49">
         <v>31</v>
       </c>
-      <c r="AC19" s="149"/>
-      <c r="AD19" s="161"/>
-      <c r="AE19" s="162"/>
+      <c r="AC19" s="136"/>
+      <c r="AD19" s="148"/>
+      <c r="AE19" s="149"/>
     </row>
     <row r="20" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="27">
@@ -5170,9 +5158,9 @@
       <c r="G20" s="22"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="175"/>
-      <c r="K20" s="176"/>
-      <c r="L20" s="177"/>
+      <c r="J20" s="122"/>
+      <c r="K20" s="123"/>
+      <c r="L20" s="124"/>
       <c r="M20" s="23"/>
       <c r="N20" s="24"/>
       <c r="O20" s="24"/>
@@ -5190,8 +5178,8 @@
       <c r="AA20" s="24"/>
       <c r="AB20" s="24"/>
       <c r="AC20" s="25"/>
-      <c r="AD20" s="173"/>
-      <c r="AE20" s="174"/>
+      <c r="AD20" s="120"/>
+      <c r="AE20" s="121"/>
     </row>
     <row r="21" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="27">
@@ -5204,9 +5192,9 @@
       <c r="G21" s="27"/>
       <c r="H21" s="31"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="141"/>
-      <c r="K21" s="142"/>
-      <c r="L21" s="143"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="118"/>
+      <c r="L21" s="119"/>
       <c r="M21" s="28"/>
       <c r="N21" s="28"/>
       <c r="O21" s="28"/>
@@ -5224,8 +5212,8 @@
       <c r="AA21" s="28"/>
       <c r="AB21" s="28"/>
       <c r="AC21" s="29"/>
-      <c r="AD21" s="141"/>
-      <c r="AE21" s="143"/>
+      <c r="AD21" s="117"/>
+      <c r="AE21" s="119"/>
     </row>
     <row r="22" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="27">
@@ -5238,9 +5226,9 @@
       <c r="G22" s="27"/>
       <c r="H22" s="31"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="142"/>
-      <c r="L22" s="143"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="118"/>
+      <c r="L22" s="119"/>
       <c r="M22" s="28"/>
       <c r="N22" s="28"/>
       <c r="O22" s="28"/>
@@ -5258,8 +5246,8 @@
       <c r="AA22" s="28"/>
       <c r="AB22" s="28"/>
       <c r="AC22" s="29"/>
-      <c r="AD22" s="141"/>
-      <c r="AE22" s="143"/>
+      <c r="AD22" s="117"/>
+      <c r="AE22" s="119"/>
     </row>
     <row r="23" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="27">
@@ -5272,9 +5260,9 @@
       <c r="G23" s="27"/>
       <c r="H23" s="31"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="141"/>
-      <c r="K23" s="142"/>
-      <c r="L23" s="143"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="118"/>
+      <c r="L23" s="119"/>
       <c r="M23" s="28"/>
       <c r="N23" s="28"/>
       <c r="O23" s="28"/>
@@ -5292,8 +5280,8 @@
       <c r="AA23" s="28"/>
       <c r="AB23" s="28"/>
       <c r="AC23" s="29"/>
-      <c r="AD23" s="141"/>
-      <c r="AE23" s="143"/>
+      <c r="AD23" s="117"/>
+      <c r="AE23" s="119"/>
     </row>
     <row r="24" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="27">
@@ -5306,9 +5294,9 @@
       <c r="G24" s="27"/>
       <c r="H24" s="31"/>
       <c r="I24" s="1"/>
-      <c r="J24" s="141"/>
-      <c r="K24" s="142"/>
-      <c r="L24" s="143"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="118"/>
+      <c r="L24" s="119"/>
       <c r="M24" s="28"/>
       <c r="N24" s="28"/>
       <c r="O24" s="28"/>
@@ -5326,8 +5314,8 @@
       <c r="AA24" s="28"/>
       <c r="AB24" s="28"/>
       <c r="AC24" s="29"/>
-      <c r="AD24" s="141"/>
-      <c r="AE24" s="143"/>
+      <c r="AD24" s="117"/>
+      <c r="AE24" s="119"/>
     </row>
     <row r="25" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="27">
@@ -5340,9 +5328,9 @@
       <c r="G25" s="27"/>
       <c r="H25" s="31"/>
       <c r="I25" s="1"/>
-      <c r="J25" s="141"/>
-      <c r="K25" s="142"/>
-      <c r="L25" s="143"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="118"/>
+      <c r="L25" s="119"/>
       <c r="M25" s="28"/>
       <c r="N25" s="28"/>
       <c r="O25" s="28"/>
@@ -5360,8 +5348,8 @@
       <c r="AA25" s="28"/>
       <c r="AB25" s="28"/>
       <c r="AC25" s="29"/>
-      <c r="AD25" s="141"/>
-      <c r="AE25" s="143"/>
+      <c r="AD25" s="117"/>
+      <c r="AE25" s="119"/>
     </row>
     <row r="26" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="27">
@@ -5374,9 +5362,9 @@
       <c r="G26" s="27"/>
       <c r="H26" s="31"/>
       <c r="I26" s="1"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="142"/>
-      <c r="L26" s="143"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="118"/>
+      <c r="L26" s="119"/>
       <c r="M26" s="28"/>
       <c r="N26" s="28"/>
       <c r="O26" s="28"/>
@@ -5394,8 +5382,8 @@
       <c r="AA26" s="28"/>
       <c r="AB26" s="28"/>
       <c r="AC26" s="29"/>
-      <c r="AD26" s="141"/>
-      <c r="AE26" s="143"/>
+      <c r="AD26" s="117"/>
+      <c r="AE26" s="119"/>
       <c r="AH26" s="20" t="s">
         <v>19</v>
       </c>
@@ -5411,9 +5399,9 @@
       <c r="G27" s="27"/>
       <c r="H27" s="31"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="141"/>
-      <c r="K27" s="142"/>
-      <c r="L27" s="143"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="118"/>
+      <c r="L27" s="119"/>
       <c r="M27" s="28"/>
       <c r="N27" s="28"/>
       <c r="O27" s="28"/>
@@ -5431,8 +5419,8 @@
       <c r="AA27" s="28"/>
       <c r="AB27" s="28"/>
       <c r="AC27" s="29"/>
-      <c r="AD27" s="141"/>
-      <c r="AE27" s="143"/>
+      <c r="AD27" s="117"/>
+      <c r="AE27" s="119"/>
       <c r="AH27" s="20" t="s">
         <v>20</v>
       </c>
@@ -5448,9 +5436,9 @@
       <c r="G28" s="27"/>
       <c r="H28" s="31"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="142"/>
-      <c r="L28" s="143"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="118"/>
+      <c r="L28" s="119"/>
       <c r="M28" s="28"/>
       <c r="N28" s="28"/>
       <c r="O28" s="28"/>
@@ -5468,8 +5456,8 @@
       <c r="AA28" s="28"/>
       <c r="AB28" s="28"/>
       <c r="AC28" s="29"/>
-      <c r="AD28" s="141"/>
-      <c r="AE28" s="143"/>
+      <c r="AD28" s="117"/>
+      <c r="AE28" s="119"/>
       <c r="AH28" s="20" t="s">
         <v>25</v>
       </c>
@@ -5485,9 +5473,9 @@
       <c r="G29" s="27"/>
       <c r="H29" s="31"/>
       <c r="I29" s="1"/>
-      <c r="J29" s="141"/>
-      <c r="K29" s="142"/>
-      <c r="L29" s="143"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="118"/>
+      <c r="L29" s="119"/>
       <c r="M29" s="28"/>
       <c r="N29" s="28"/>
       <c r="O29" s="28"/>
@@ -5505,8 +5493,8 @@
       <c r="AA29" s="28"/>
       <c r="AB29" s="28"/>
       <c r="AC29" s="29"/>
-      <c r="AD29" s="141"/>
-      <c r="AE29" s="143"/>
+      <c r="AD29" s="117"/>
+      <c r="AE29" s="119"/>
     </row>
     <row r="30" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="27">
@@ -5519,9 +5507,9 @@
       <c r="G30" s="27"/>
       <c r="H30" s="31"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="141"/>
-      <c r="K30" s="142"/>
-      <c r="L30" s="143"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="118"/>
+      <c r="L30" s="119"/>
       <c r="M30" s="28"/>
       <c r="N30" s="28"/>
       <c r="O30" s="28"/>
@@ -5539,8 +5527,8 @@
       <c r="AA30" s="28"/>
       <c r="AB30" s="28"/>
       <c r="AC30" s="29"/>
-      <c r="AD30" s="141"/>
-      <c r="AE30" s="143"/>
+      <c r="AD30" s="117"/>
+      <c r="AE30" s="119"/>
       <c r="AI30" t="s">
         <v>21</v>
       </c>
@@ -5556,9 +5544,9 @@
       <c r="G31" s="27"/>
       <c r="H31" s="31"/>
       <c r="I31" s="1"/>
-      <c r="J31" s="141"/>
-      <c r="K31" s="142"/>
-      <c r="L31" s="143"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="118"/>
+      <c r="L31" s="119"/>
       <c r="M31" s="28"/>
       <c r="N31" s="28"/>
       <c r="O31" s="28"/>
@@ -5576,8 +5564,8 @@
       <c r="AA31" s="28"/>
       <c r="AB31" s="28"/>
       <c r="AC31" s="29"/>
-      <c r="AD31" s="141"/>
-      <c r="AE31" s="143"/>
+      <c r="AD31" s="117"/>
+      <c r="AE31" s="119"/>
       <c r="AI31" t="s">
         <v>22</v>
       </c>
@@ -5593,9 +5581,9 @@
       <c r="G32" s="27"/>
       <c r="H32" s="31"/>
       <c r="I32" s="1"/>
-      <c r="J32" s="141"/>
-      <c r="K32" s="142"/>
-      <c r="L32" s="143"/>
+      <c r="J32" s="117"/>
+      <c r="K32" s="118"/>
+      <c r="L32" s="119"/>
       <c r="M32" s="28"/>
       <c r="N32" s="28"/>
       <c r="O32" s="28"/>
@@ -5613,8 +5601,8 @@
       <c r="AA32" s="28"/>
       <c r="AB32" s="28"/>
       <c r="AC32" s="29"/>
-      <c r="AD32" s="141"/>
-      <c r="AE32" s="143"/>
+      <c r="AD32" s="117"/>
+      <c r="AE32" s="119"/>
       <c r="AI32" t="s">
         <v>23</v>
       </c>
@@ -5630,9 +5618,9 @@
       <c r="G33" s="31"/>
       <c r="H33" s="31"/>
       <c r="I33" s="1"/>
-      <c r="J33" s="141"/>
-      <c r="K33" s="142"/>
-      <c r="L33" s="143"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="118"/>
+      <c r="L33" s="119"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
       <c r="O33" s="32"/>
@@ -5650,8 +5638,8 @@
       <c r="AA33" s="32"/>
       <c r="AB33" s="32"/>
       <c r="AC33" s="33"/>
-      <c r="AD33" s="141"/>
-      <c r="AE33" s="143"/>
+      <c r="AD33" s="117"/>
+      <c r="AE33" s="119"/>
       <c r="AI33" t="s">
         <v>24</v>
       </c>
@@ -5667,9 +5655,9 @@
       <c r="G34" s="27"/>
       <c r="H34" s="31"/>
       <c r="I34" s="1"/>
-      <c r="J34" s="141"/>
-      <c r="K34" s="142"/>
-      <c r="L34" s="143"/>
+      <c r="J34" s="117"/>
+      <c r="K34" s="118"/>
+      <c r="L34" s="119"/>
       <c r="M34" s="28"/>
       <c r="N34" s="28"/>
       <c r="O34" s="28"/>
@@ -5687,8 +5675,8 @@
       <c r="AA34" s="28"/>
       <c r="AB34" s="28"/>
       <c r="AC34" s="29"/>
-      <c r="AD34" s="141"/>
-      <c r="AE34" s="143"/>
+      <c r="AD34" s="117"/>
+      <c r="AE34" s="119"/>
     </row>
     <row r="35" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="27">
@@ -5701,9 +5689,9 @@
       <c r="G35" s="27"/>
       <c r="H35" s="31"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="141"/>
-      <c r="K35" s="142"/>
-      <c r="L35" s="143"/>
+      <c r="J35" s="117"/>
+      <c r="K35" s="118"/>
+      <c r="L35" s="119"/>
       <c r="M35" s="28"/>
       <c r="N35" s="28"/>
       <c r="O35" s="28"/>
@@ -5721,8 +5709,8 @@
       <c r="AA35" s="28"/>
       <c r="AB35" s="28"/>
       <c r="AC35" s="29"/>
-      <c r="AD35" s="141"/>
-      <c r="AE35" s="143"/>
+      <c r="AD35" s="117"/>
+      <c r="AE35" s="119"/>
     </row>
     <row r="36" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="27">
@@ -5735,9 +5723,9 @@
       <c r="G36" s="31"/>
       <c r="H36" s="31"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="141"/>
-      <c r="K36" s="142"/>
-      <c r="L36" s="143"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="118"/>
+      <c r="L36" s="119"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
       <c r="O36" s="32"/>
@@ -5755,8 +5743,8 @@
       <c r="AA36" s="32"/>
       <c r="AB36" s="32"/>
       <c r="AC36" s="33"/>
-      <c r="AD36" s="141"/>
-      <c r="AE36" s="143"/>
+      <c r="AD36" s="117"/>
+      <c r="AE36" s="119"/>
     </row>
     <row r="37" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="27">
@@ -5769,9 +5757,9 @@
       <c r="G37" s="27"/>
       <c r="H37" s="31"/>
       <c r="I37" s="1"/>
-      <c r="J37" s="141"/>
-      <c r="K37" s="142"/>
-      <c r="L37" s="143"/>
+      <c r="J37" s="117"/>
+      <c r="K37" s="118"/>
+      <c r="L37" s="119"/>
       <c r="M37" s="28"/>
       <c r="N37" s="28"/>
       <c r="O37" s="28"/>
@@ -5789,8 +5777,8 @@
       <c r="AA37" s="28"/>
       <c r="AB37" s="28"/>
       <c r="AC37" s="29"/>
-      <c r="AD37" s="141"/>
-      <c r="AE37" s="143"/>
+      <c r="AD37" s="117"/>
+      <c r="AE37" s="119"/>
     </row>
     <row r="38" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="27">
@@ -5803,9 +5791,9 @@
       <c r="G38" s="27"/>
       <c r="H38" s="31"/>
       <c r="I38" s="1"/>
-      <c r="J38" s="141"/>
-      <c r="K38" s="142"/>
-      <c r="L38" s="143"/>
+      <c r="J38" s="117"/>
+      <c r="K38" s="118"/>
+      <c r="L38" s="119"/>
       <c r="M38" s="28"/>
       <c r="N38" s="28"/>
       <c r="O38" s="28"/>
@@ -5823,8 +5811,8 @@
       <c r="AA38" s="28"/>
       <c r="AB38" s="28"/>
       <c r="AC38" s="29"/>
-      <c r="AD38" s="141"/>
-      <c r="AE38" s="143"/>
+      <c r="AD38" s="117"/>
+      <c r="AE38" s="119"/>
     </row>
     <row r="39" spans="2:35" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="27">
@@ -5837,9 +5825,9 @@
       <c r="G39" s="31"/>
       <c r="H39" s="31"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="141"/>
-      <c r="K39" s="142"/>
-      <c r="L39" s="143"/>
+      <c r="J39" s="117"/>
+      <c r="K39" s="118"/>
+      <c r="L39" s="119"/>
       <c r="M39" s="32"/>
       <c r="N39" s="32"/>
       <c r="O39" s="32"/>
@@ -5857,26 +5845,45 @@
       <c r="AA39" s="32"/>
       <c r="AB39" s="32"/>
       <c r="AC39" s="33"/>
-      <c r="AD39" s="141"/>
-      <c r="AE39" s="143"/>
+      <c r="AD39" s="117"/>
+      <c r="AE39" s="119"/>
     </row>
     <row r="40" spans="2:35" ht="25.8" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
   <mergeCells count="59">
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="J20:L20"/>
-    <mergeCell ref="M13:AC14"/>
+    <mergeCell ref="J39:L39"/>
+    <mergeCell ref="AD39:AE39"/>
+    <mergeCell ref="J35:L35"/>
+    <mergeCell ref="AD35:AE35"/>
+    <mergeCell ref="J36:L36"/>
+    <mergeCell ref="AD36:AE36"/>
+    <mergeCell ref="J37:L37"/>
+    <mergeCell ref="AD37:AE37"/>
+    <mergeCell ref="J33:L33"/>
+    <mergeCell ref="AD33:AE33"/>
+    <mergeCell ref="J34:L34"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="J38:L38"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="J31:L31"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="AD28:AE28"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="AD29:AE29"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="J25:L25"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="J24:L24"/>
     <mergeCell ref="B11:AE12"/>
     <mergeCell ref="B15:B19"/>
     <mergeCell ref="C15:C19"/>
@@ -5891,38 +5898,19 @@
     <mergeCell ref="H14:L14"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="J25:L25"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="AD28:AE28"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="AD29:AE29"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="J31:L31"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="J33:L33"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="J34:L34"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="J38:L38"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="J39:L39"/>
-    <mergeCell ref="AD39:AE39"/>
-    <mergeCell ref="J35:L35"/>
-    <mergeCell ref="AD35:AE35"/>
-    <mergeCell ref="J36:L36"/>
-    <mergeCell ref="AD36:AE36"/>
-    <mergeCell ref="J37:L37"/>
-    <mergeCell ref="AD37:AE37"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="M13:AC14"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="J23:L23"/>
+    <mergeCell ref="AD23:AE23"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M20:AB39" xr:uid="{00000000-0002-0000-0100-000001000000}">
@@ -6016,74 +6004,74 @@
       <c r="R9" s="18"/>
     </row>
     <row r="11" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="144" t="s">
+      <c r="B11" s="131" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="144"/>
-      <c r="L11" s="144"/>
-      <c r="M11" s="144"/>
-      <c r="N11" s="144"/>
-      <c r="O11" s="144"/>
-      <c r="P11" s="144"/>
-      <c r="Q11" s="144"/>
-      <c r="R11" s="145"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="131"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="131"/>
+      <c r="N11" s="131"/>
+      <c r="O11" s="131"/>
+      <c r="P11" s="131"/>
+      <c r="Q11" s="131"/>
+      <c r="R11" s="132"/>
       <c r="U11" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="146"/>
-      <c r="C12" s="146"/>
-      <c r="D12" s="146"/>
-      <c r="E12" s="146"/>
-      <c r="F12" s="146"/>
-      <c r="G12" s="146"/>
-      <c r="H12" s="146"/>
-      <c r="I12" s="146"/>
-      <c r="J12" s="146"/>
-      <c r="K12" s="146"/>
-      <c r="L12" s="146"/>
-      <c r="M12" s="146"/>
-      <c r="N12" s="146"/>
-      <c r="O12" s="146"/>
-      <c r="P12" s="146"/>
-      <c r="Q12" s="146"/>
-      <c r="R12" s="147"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="133"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="133"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="133"/>
+      <c r="M12" s="133"/>
+      <c r="N12" s="133"/>
+      <c r="O12" s="133"/>
+      <c r="P12" s="133"/>
+      <c r="Q12" s="133"/>
+      <c r="R12" s="134"/>
       <c r="U12" s="20" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="13" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="196" t="s">
+      <c r="B13" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="197"/>
-      <c r="D13" s="178" t="b">
+      <c r="C13" s="70"/>
+      <c r="D13" s="162" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="179"/>
-      <c r="F13" s="210" t="s">
+      <c r="E13" s="163"/>
+      <c r="F13" s="164" t="s">
         <v>40</v>
       </c>
-      <c r="G13" s="211"/>
-      <c r="H13" s="184"/>
-      <c r="I13" s="185"/>
-      <c r="J13" s="186"/>
-      <c r="K13" s="218"/>
-      <c r="L13" s="219"/>
-      <c r="M13" s="219"/>
-      <c r="N13" s="219"/>
-      <c r="O13" s="219"/>
-      <c r="P13" s="220"/>
-      <c r="Q13" s="214" t="s">
+      <c r="G13" s="165"/>
+      <c r="H13" s="170"/>
+      <c r="I13" s="171"/>
+      <c r="J13" s="172"/>
+      <c r="K13" s="125"/>
+      <c r="L13" s="126"/>
+      <c r="M13" s="126"/>
+      <c r="N13" s="126"/>
+      <c r="O13" s="126"/>
+      <c r="P13" s="127"/>
+      <c r="Q13" s="66" t="s">
         <v>15</v>
       </c>
       <c r="R13" s="21"/>
@@ -6092,182 +6080,182 @@
       </c>
     </row>
     <row r="14" spans="2:22" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="196" t="s">
+      <c r="B14" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="197"/>
-      <c r="D14" s="178" t="b">
+      <c r="C14" s="70"/>
+      <c r="D14" s="162" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="179"/>
-      <c r="F14" s="212" t="s">
+      <c r="E14" s="163"/>
+      <c r="F14" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="213"/>
-      <c r="H14" s="187"/>
-      <c r="I14" s="188"/>
-      <c r="J14" s="189"/>
-      <c r="K14" s="221"/>
-      <c r="L14" s="222"/>
-      <c r="M14" s="222"/>
-      <c r="N14" s="222"/>
-      <c r="O14" s="222"/>
-      <c r="P14" s="223"/>
-      <c r="Q14" s="214" t="s">
+      <c r="G14" s="65"/>
+      <c r="H14" s="173"/>
+      <c r="I14" s="174"/>
+      <c r="J14" s="175"/>
+      <c r="K14" s="128"/>
+      <c r="L14" s="129"/>
+      <c r="M14" s="129"/>
+      <c r="N14" s="129"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="130"/>
+      <c r="Q14" s="66" t="s">
         <v>35</v>
       </c>
       <c r="R14" s="21"/>
     </row>
     <row r="15" spans="2:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="148" t="s">
+      <c r="B15" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="149" t="s">
+      <c r="C15" s="136" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="150" t="s">
+      <c r="D15" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="151"/>
-      <c r="F15" s="114" t="s">
+      <c r="E15" s="138"/>
+      <c r="F15" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="50"/>
-      <c r="K15" s="46" t="s">
+      <c r="G15" s="108"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="222"/>
+      <c r="K15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="L15" s="156" t="s">
+      <c r="L15" s="143" t="s">
         <v>33</v>
       </c>
-      <c r="M15" s="156"/>
-      <c r="N15" s="156"/>
-      <c r="O15" s="156"/>
-      <c r="P15" s="149" t="s">
+      <c r="M15" s="143"/>
+      <c r="N15" s="143"/>
+      <c r="O15" s="143"/>
+      <c r="P15" s="136" t="s">
         <v>51</v>
       </c>
-      <c r="Q15" s="182" t="s">
+      <c r="Q15" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="R15" s="158"/>
+      <c r="R15" s="145"/>
       <c r="V15" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="148"/>
-      <c r="C16" s="149"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="153"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="51"/>
-      <c r="K16" s="48" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="223"/>
+      <c r="K16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="L16" s="226"/>
-      <c r="M16" s="226"/>
-      <c r="N16" s="226"/>
-      <c r="O16" s="226"/>
-      <c r="P16" s="149"/>
-      <c r="Q16" s="183"/>
-      <c r="R16" s="160"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="136"/>
+      <c r="Q16" s="169"/>
+      <c r="R16" s="147"/>
       <c r="V16" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="148"/>
-      <c r="C17" s="149"/>
-      <c r="D17" s="152"/>
-      <c r="E17" s="153"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="49" t="s">
+      <c r="B17" s="135"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="223"/>
+      <c r="K17" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="226"/>
-      <c r="M17" s="226"/>
-      <c r="N17" s="226"/>
-      <c r="O17" s="226"/>
-      <c r="P17" s="149"/>
-      <c r="Q17" s="183"/>
-      <c r="R17" s="160"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="136"/>
+      <c r="Q17" s="169"/>
+      <c r="R17" s="147"/>
       <c r="V17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="2:22" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="148"/>
-      <c r="C18" s="149"/>
-      <c r="D18" s="154"/>
-      <c r="E18" s="155"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="49" t="s">
+      <c r="B18" s="135"/>
+      <c r="C18" s="136"/>
+      <c r="D18" s="141"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="224"/>
+      <c r="K18" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="L18" s="226"/>
-      <c r="M18" s="226"/>
-      <c r="N18" s="226"/>
-      <c r="O18" s="226"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="183"/>
-      <c r="R18" s="160"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="136"/>
+      <c r="Q18" s="169"/>
+      <c r="R18" s="147"/>
       <c r="V18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" spans="2:22" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="148"/>
-      <c r="C19" s="149"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="136"/>
       <c r="D19" s="44" t="s">
         <v>1</v>
       </c>
       <c r="E19" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="F19" s="52" t="s">
+      <c r="F19" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G19" s="52" t="s">
+      <c r="G19" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="52" t="s">
+      <c r="I19" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="180" t="s">
+      <c r="J19" s="166" t="s">
         <v>29</v>
       </c>
-      <c r="K19" s="181"/>
-      <c r="L19" s="53">
+      <c r="K19" s="167"/>
+      <c r="L19" s="49">
         <v>1</v>
       </c>
-      <c r="M19" s="53">
+      <c r="M19" s="49">
         <v>2</v>
       </c>
-      <c r="N19" s="53">
+      <c r="N19" s="49">
         <v>3</v>
       </c>
-      <c r="O19" s="53">
+      <c r="O19" s="49">
         <v>4</v>
       </c>
-      <c r="P19" s="149"/>
-      <c r="Q19" s="161"/>
-      <c r="R19" s="162"/>
+      <c r="P19" s="136"/>
+      <c r="Q19" s="148"/>
+      <c r="R19" s="149"/>
     </row>
     <row r="20" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="27">
@@ -6280,15 +6268,15 @@
       <c r="G20" s="27"/>
       <c r="H20" s="27"/>
       <c r="I20" s="36"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="143"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="119"/>
       <c r="L20" s="37"/>
       <c r="M20" s="37"/>
       <c r="N20" s="37"/>
       <c r="O20" s="37"/>
       <c r="P20" s="40"/>
-      <c r="Q20" s="141"/>
-      <c r="R20" s="143"/>
+      <c r="Q20" s="117"/>
+      <c r="R20" s="119"/>
     </row>
     <row r="21" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="27">
@@ -6301,15 +6289,15 @@
       <c r="G21" s="27"/>
       <c r="H21" s="27"/>
       <c r="I21" s="36"/>
-      <c r="J21" s="141"/>
-      <c r="K21" s="143"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="119"/>
       <c r="L21" s="37"/>
       <c r="M21" s="37"/>
       <c r="N21" s="37"/>
       <c r="O21" s="37"/>
       <c r="P21" s="40"/>
-      <c r="Q21" s="141"/>
-      <c r="R21" s="143"/>
+      <c r="Q21" s="117"/>
+      <c r="R21" s="119"/>
     </row>
     <row r="22" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="27">
@@ -6322,15 +6310,15 @@
       <c r="G22" s="27"/>
       <c r="H22" s="27"/>
       <c r="I22" s="36"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="143"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="119"/>
       <c r="L22" s="37"/>
       <c r="M22" s="37"/>
       <c r="N22" s="37"/>
       <c r="O22" s="37"/>
       <c r="P22" s="40"/>
-      <c r="Q22" s="141"/>
-      <c r="R22" s="143"/>
+      <c r="Q22" s="117"/>
+      <c r="R22" s="119"/>
     </row>
     <row r="23" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="27">
@@ -6343,15 +6331,15 @@
       <c r="G23" s="27"/>
       <c r="H23" s="27"/>
       <c r="I23" s="36"/>
-      <c r="J23" s="141"/>
-      <c r="K23" s="143"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="119"/>
       <c r="L23" s="37"/>
       <c r="M23" s="37"/>
       <c r="N23" s="37"/>
       <c r="O23" s="37"/>
       <c r="P23" s="40"/>
-      <c r="Q23" s="141"/>
-      <c r="R23" s="143"/>
+      <c r="Q23" s="117"/>
+      <c r="R23" s="119"/>
     </row>
     <row r="24" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="27">
@@ -6364,15 +6352,15 @@
       <c r="G24" s="27"/>
       <c r="H24" s="27"/>
       <c r="I24" s="36"/>
-      <c r="J24" s="141"/>
-      <c r="K24" s="143"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="119"/>
       <c r="L24" s="37"/>
       <c r="M24" s="37"/>
       <c r="N24" s="37"/>
       <c r="O24" s="37"/>
       <c r="P24" s="40"/>
-      <c r="Q24" s="141"/>
-      <c r="R24" s="143"/>
+      <c r="Q24" s="117"/>
+      <c r="R24" s="119"/>
     </row>
     <row r="25" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="27">
@@ -6385,15 +6373,15 @@
       <c r="G25" s="27"/>
       <c r="H25" s="27"/>
       <c r="I25" s="36"/>
-      <c r="J25" s="141"/>
-      <c r="K25" s="143"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="119"/>
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
       <c r="N25" s="37"/>
       <c r="O25" s="37"/>
       <c r="P25" s="40"/>
-      <c r="Q25" s="141"/>
-      <c r="R25" s="143"/>
+      <c r="Q25" s="117"/>
+      <c r="R25" s="119"/>
     </row>
     <row r="26" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="27">
@@ -6406,15 +6394,15 @@
       <c r="G26" s="27"/>
       <c r="H26" s="27"/>
       <c r="I26" s="36"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="143"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="119"/>
       <c r="L26" s="37"/>
       <c r="M26" s="37"/>
       <c r="N26" s="37"/>
       <c r="O26" s="37"/>
       <c r="P26" s="40"/>
-      <c r="Q26" s="141"/>
-      <c r="R26" s="143"/>
+      <c r="Q26" s="117"/>
+      <c r="R26" s="119"/>
     </row>
     <row r="27" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="27">
@@ -6427,15 +6415,15 @@
       <c r="G27" s="27"/>
       <c r="H27" s="27"/>
       <c r="I27" s="36"/>
-      <c r="J27" s="141"/>
-      <c r="K27" s="143"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="119"/>
       <c r="L27" s="37"/>
       <c r="M27" s="37"/>
       <c r="N27" s="37"/>
       <c r="O27" s="37"/>
       <c r="P27" s="40"/>
-      <c r="Q27" s="141"/>
-      <c r="R27" s="143"/>
+      <c r="Q27" s="117"/>
+      <c r="R27" s="119"/>
     </row>
     <row r="28" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="27">
@@ -6448,15 +6436,15 @@
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>
       <c r="I28" s="36"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="143"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="119"/>
       <c r="L28" s="37"/>
       <c r="M28" s="37"/>
       <c r="N28" s="37"/>
       <c r="O28" s="37"/>
       <c r="P28" s="40"/>
-      <c r="Q28" s="141"/>
-      <c r="R28" s="143"/>
+      <c r="Q28" s="117"/>
+      <c r="R28" s="119"/>
     </row>
     <row r="29" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="27">
@@ -6469,15 +6457,15 @@
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="I29" s="36"/>
-      <c r="J29" s="141"/>
-      <c r="K29" s="143"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="119"/>
       <c r="L29" s="37"/>
       <c r="M29" s="37"/>
       <c r="N29" s="37"/>
       <c r="O29" s="37"/>
       <c r="P29" s="40"/>
-      <c r="Q29" s="141"/>
-      <c r="R29" s="143"/>
+      <c r="Q29" s="117"/>
+      <c r="R29" s="119"/>
     </row>
     <row r="30" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="27">
@@ -6490,15 +6478,15 @@
       <c r="G30" s="27"/>
       <c r="H30" s="27"/>
       <c r="I30" s="36"/>
-      <c r="J30" s="141"/>
-      <c r="K30" s="143"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="119"/>
       <c r="L30" s="37"/>
       <c r="M30" s="37"/>
       <c r="N30" s="37"/>
       <c r="O30" s="37"/>
       <c r="P30" s="40"/>
-      <c r="Q30" s="141"/>
-      <c r="R30" s="143"/>
+      <c r="Q30" s="117"/>
+      <c r="R30" s="119"/>
     </row>
     <row r="31" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="27">
@@ -6511,15 +6499,15 @@
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="I31" s="36"/>
-      <c r="J31" s="141"/>
-      <c r="K31" s="143"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="119"/>
       <c r="L31" s="37"/>
       <c r="M31" s="37"/>
       <c r="N31" s="37"/>
       <c r="O31" s="37"/>
       <c r="P31" s="40"/>
-      <c r="Q31" s="141"/>
-      <c r="R31" s="143"/>
+      <c r="Q31" s="117"/>
+      <c r="R31" s="119"/>
     </row>
     <row r="32" spans="2:22" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="27">
@@ -6532,15 +6520,15 @@
       <c r="G32" s="31"/>
       <c r="H32" s="31"/>
       <c r="I32" s="38"/>
-      <c r="J32" s="141"/>
-      <c r="K32" s="143"/>
+      <c r="J32" s="117"/>
+      <c r="K32" s="119"/>
       <c r="L32" s="39"/>
       <c r="M32" s="39"/>
       <c r="N32" s="39"/>
       <c r="O32" s="39"/>
       <c r="P32" s="41"/>
-      <c r="Q32" s="141"/>
-      <c r="R32" s="143"/>
+      <c r="Q32" s="117"/>
+      <c r="R32" s="119"/>
     </row>
     <row r="33" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="27">
@@ -6553,15 +6541,15 @@
       <c r="G33" s="27"/>
       <c r="H33" s="27"/>
       <c r="I33" s="36"/>
-      <c r="J33" s="141"/>
-      <c r="K33" s="143"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="119"/>
       <c r="L33" s="37"/>
       <c r="M33" s="37"/>
       <c r="N33" s="37"/>
       <c r="O33" s="37"/>
       <c r="P33" s="40"/>
-      <c r="Q33" s="141"/>
-      <c r="R33" s="143"/>
+      <c r="Q33" s="117"/>
+      <c r="R33" s="119"/>
     </row>
     <row r="34" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="27">
@@ -6574,15 +6562,15 @@
       <c r="G34" s="27"/>
       <c r="H34" s="27"/>
       <c r="I34" s="36"/>
-      <c r="J34" s="141"/>
-      <c r="K34" s="143"/>
+      <c r="J34" s="117"/>
+      <c r="K34" s="119"/>
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
       <c r="N34" s="37"/>
       <c r="O34" s="37"/>
       <c r="P34" s="40"/>
-      <c r="Q34" s="141"/>
-      <c r="R34" s="143"/>
+      <c r="Q34" s="117"/>
+      <c r="R34" s="119"/>
     </row>
     <row r="35" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="27">
@@ -6595,15 +6583,15 @@
       <c r="G35" s="31"/>
       <c r="H35" s="31"/>
       <c r="I35" s="38"/>
-      <c r="J35" s="141"/>
-      <c r="K35" s="143"/>
+      <c r="J35" s="117"/>
+      <c r="K35" s="119"/>
       <c r="L35" s="39"/>
       <c r="M35" s="39"/>
       <c r="N35" s="39"/>
       <c r="O35" s="39"/>
       <c r="P35" s="41"/>
-      <c r="Q35" s="141"/>
-      <c r="R35" s="143"/>
+      <c r="Q35" s="117"/>
+      <c r="R35" s="119"/>
     </row>
     <row r="36" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="27">
@@ -6616,15 +6604,15 @@
       <c r="G36" s="27"/>
       <c r="H36" s="27"/>
       <c r="I36" s="36"/>
-      <c r="J36" s="141"/>
-      <c r="K36" s="143"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="119"/>
       <c r="L36" s="37"/>
       <c r="M36" s="37"/>
       <c r="N36" s="37"/>
       <c r="O36" s="37"/>
       <c r="P36" s="40"/>
-      <c r="Q36" s="141"/>
-      <c r="R36" s="143"/>
+      <c r="Q36" s="117"/>
+      <c r="R36" s="119"/>
     </row>
     <row r="37" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="27">
@@ -6637,15 +6625,15 @@
       <c r="G37" s="27"/>
       <c r="H37" s="27"/>
       <c r="I37" s="36"/>
-      <c r="J37" s="141"/>
-      <c r="K37" s="143"/>
+      <c r="J37" s="117"/>
+      <c r="K37" s="119"/>
       <c r="L37" s="37"/>
       <c r="M37" s="37"/>
       <c r="N37" s="37"/>
       <c r="O37" s="37"/>
       <c r="P37" s="40"/>
-      <c r="Q37" s="141"/>
-      <c r="R37" s="143"/>
+      <c r="Q37" s="117"/>
+      <c r="R37" s="119"/>
     </row>
     <row r="38" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="27">
@@ -6658,15 +6646,15 @@
       <c r="G38" s="31"/>
       <c r="H38" s="31"/>
       <c r="I38" s="38"/>
-      <c r="J38" s="141"/>
-      <c r="K38" s="143"/>
+      <c r="J38" s="117"/>
+      <c r="K38" s="119"/>
       <c r="L38" s="39"/>
       <c r="M38" s="39"/>
       <c r="N38" s="39"/>
       <c r="O38" s="39"/>
       <c r="P38" s="41"/>
-      <c r="Q38" s="141"/>
-      <c r="R38" s="143"/>
+      <c r="Q38" s="117"/>
+      <c r="R38" s="119"/>
     </row>
     <row r="39" spans="2:18" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="27">
@@ -6679,19 +6667,61 @@
       <c r="G39" s="27"/>
       <c r="H39" s="27"/>
       <c r="I39" s="36"/>
-      <c r="J39" s="141"/>
-      <c r="K39" s="143"/>
+      <c r="J39" s="117"/>
+      <c r="K39" s="119"/>
       <c r="L39" s="37"/>
       <c r="M39" s="37"/>
       <c r="N39" s="37"/>
       <c r="O39" s="37"/>
       <c r="P39" s="40"/>
-      <c r="Q39" s="141"/>
-      <c r="R39" s="143"/>
+      <c r="Q39" s="117"/>
+      <c r="R39" s="119"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
-  <mergeCells count="57">
+  <mergeCells count="58">
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="B11:R12"/>
+    <mergeCell ref="P15:P19"/>
+    <mergeCell ref="K13:P14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="C15:C19"/>
+    <mergeCell ref="L15:O15"/>
+    <mergeCell ref="Q15:R19"/>
+    <mergeCell ref="D15:E18"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="F15:I18"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J15:J18"/>
     <mergeCell ref="Q24:R24"/>
     <mergeCell ref="Q37:R37"/>
     <mergeCell ref="Q38:R38"/>
@@ -6708,47 +6738,6 @@
     <mergeCell ref="Q27:R27"/>
     <mergeCell ref="Q28:R28"/>
     <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="B11:R12"/>
-    <mergeCell ref="P15:P19"/>
-    <mergeCell ref="K13:P14"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="B15:B19"/>
-    <mergeCell ref="C15:C19"/>
-    <mergeCell ref="L15:O15"/>
-    <mergeCell ref="Q15:R19"/>
-    <mergeCell ref="D15:E18"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="F15:I18"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="J35:K35"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L20:O39" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -6854,295 +6843,295 @@
       <c r="Z9" s="18"/>
     </row>
     <row r="11" spans="2:29" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="144" t="s">
+      <c r="B11" s="131" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="144"/>
-      <c r="D11" s="144"/>
-      <c r="E11" s="144"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="144"/>
-      <c r="I11" s="144"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="144"/>
-      <c r="L11" s="144"/>
-      <c r="M11" s="144"/>
-      <c r="N11" s="144"/>
-      <c r="O11" s="144"/>
-      <c r="P11" s="144"/>
-      <c r="Q11" s="144"/>
-      <c r="R11" s="144"/>
-      <c r="S11" s="144"/>
-      <c r="T11" s="144"/>
-      <c r="U11" s="144"/>
-      <c r="V11" s="144"/>
-      <c r="W11" s="144"/>
-      <c r="X11" s="144"/>
-      <c r="Y11" s="144"/>
-      <c r="Z11" s="145"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131"/>
+      <c r="E11" s="131"/>
+      <c r="F11" s="131"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="131"/>
+      <c r="I11" s="131"/>
+      <c r="J11" s="131"/>
+      <c r="K11" s="131"/>
+      <c r="L11" s="131"/>
+      <c r="M11" s="131"/>
+      <c r="N11" s="131"/>
+      <c r="O11" s="131"/>
+      <c r="P11" s="131"/>
+      <c r="Q11" s="131"/>
+      <c r="R11" s="131"/>
+      <c r="S11" s="131"/>
+      <c r="T11" s="131"/>
+      <c r="U11" s="131"/>
+      <c r="V11" s="131"/>
+      <c r="W11" s="131"/>
+      <c r="X11" s="131"/>
+      <c r="Y11" s="131"/>
+      <c r="Z11" s="132"/>
     </row>
     <row r="12" spans="2:29" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="146"/>
-      <c r="C12" s="146"/>
-      <c r="D12" s="146"/>
-      <c r="E12" s="146"/>
-      <c r="F12" s="146"/>
-      <c r="G12" s="146"/>
-      <c r="H12" s="146"/>
-      <c r="I12" s="146"/>
-      <c r="J12" s="146"/>
-      <c r="K12" s="146"/>
-      <c r="L12" s="146"/>
-      <c r="M12" s="146"/>
-      <c r="N12" s="146"/>
-      <c r="O12" s="146"/>
-      <c r="P12" s="146"/>
-      <c r="Q12" s="146"/>
-      <c r="R12" s="146"/>
-      <c r="S12" s="146"/>
-      <c r="T12" s="146"/>
-      <c r="U12" s="146"/>
-      <c r="V12" s="146"/>
-      <c r="W12" s="146"/>
-      <c r="X12" s="146"/>
-      <c r="Y12" s="146"/>
-      <c r="Z12" s="147"/>
+      <c r="B12" s="133"/>
+      <c r="C12" s="133"/>
+      <c r="D12" s="133"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="133"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="133"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="133"/>
+      <c r="M12" s="133"/>
+      <c r="N12" s="133"/>
+      <c r="O12" s="133"/>
+      <c r="P12" s="133"/>
+      <c r="Q12" s="133"/>
+      <c r="R12" s="133"/>
+      <c r="S12" s="133"/>
+      <c r="T12" s="133"/>
+      <c r="U12" s="133"/>
+      <c r="V12" s="133"/>
+      <c r="W12" s="133"/>
+      <c r="X12" s="133"/>
+      <c r="Y12" s="133"/>
+      <c r="Z12" s="134"/>
     </row>
     <row r="13" spans="2:29" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="215" t="s">
+      <c r="B13" s="176" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="216"/>
+      <c r="C13" s="177"/>
       <c r="D13" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="210" t="s">
+      <c r="E13" s="164" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="211"/>
-      <c r="G13" s="195"/>
-      <c r="H13" s="195"/>
-      <c r="I13" s="195"/>
-      <c r="J13" s="195"/>
-      <c r="K13" s="218"/>
-      <c r="L13" s="219"/>
-      <c r="M13" s="219"/>
-      <c r="N13" s="219"/>
-      <c r="O13" s="219"/>
-      <c r="P13" s="219"/>
-      <c r="Q13" s="219"/>
-      <c r="R13" s="219"/>
-      <c r="S13" s="219"/>
-      <c r="T13" s="219"/>
-      <c r="U13" s="219"/>
-      <c r="V13" s="219"/>
-      <c r="W13" s="219"/>
-      <c r="X13" s="220"/>
-      <c r="Y13" s="214" t="s">
+      <c r="F13" s="165"/>
+      <c r="G13" s="183"/>
+      <c r="H13" s="183"/>
+      <c r="I13" s="183"/>
+      <c r="J13" s="183"/>
+      <c r="K13" s="125"/>
+      <c r="L13" s="126"/>
+      <c r="M13" s="126"/>
+      <c r="N13" s="126"/>
+      <c r="O13" s="126"/>
+      <c r="P13" s="126"/>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="126"/>
+      <c r="S13" s="126"/>
+      <c r="T13" s="126"/>
+      <c r="U13" s="126"/>
+      <c r="V13" s="126"/>
+      <c r="W13" s="126"/>
+      <c r="X13" s="127"/>
+      <c r="Y13" s="66" t="s">
         <v>14</v>
       </c>
       <c r="Z13" s="21"/>
     </row>
     <row r="14" spans="2:29" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="215" t="s">
+      <c r="B14" s="176" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="216"/>
+      <c r="C14" s="177"/>
       <c r="D14" s="35" t="b">
         <v>0</v>
       </c>
-      <c r="E14" s="212" t="s">
+      <c r="E14" s="64" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="213"/>
-      <c r="G14" s="195"/>
-      <c r="H14" s="195"/>
-      <c r="I14" s="195"/>
-      <c r="J14" s="195"/>
-      <c r="K14" s="221"/>
-      <c r="L14" s="222"/>
-      <c r="M14" s="222"/>
-      <c r="N14" s="222"/>
-      <c r="O14" s="222"/>
-      <c r="P14" s="222"/>
-      <c r="Q14" s="222"/>
-      <c r="R14" s="222"/>
-      <c r="S14" s="222"/>
-      <c r="T14" s="222"/>
-      <c r="U14" s="222"/>
-      <c r="V14" s="222"/>
-      <c r="W14" s="222"/>
-      <c r="X14" s="223"/>
-      <c r="Y14" s="214" t="s">
+      <c r="F14" s="65"/>
+      <c r="G14" s="183"/>
+      <c r="H14" s="183"/>
+      <c r="I14" s="183"/>
+      <c r="J14" s="183"/>
+      <c r="K14" s="128"/>
+      <c r="L14" s="129"/>
+      <c r="M14" s="129"/>
+      <c r="N14" s="129"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="129"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="129"/>
+      <c r="S14" s="129"/>
+      <c r="T14" s="129"/>
+      <c r="U14" s="129"/>
+      <c r="V14" s="129"/>
+      <c r="W14" s="129"/>
+      <c r="X14" s="130"/>
+      <c r="Y14" s="66" t="s">
         <v>35</v>
       </c>
       <c r="Z14" s="21"/>
     </row>
     <row r="15" spans="2:29" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="148" t="s">
+      <c r="B15" s="135" t="s">
         <v>4</v>
       </c>
-      <c r="C15" s="149" t="s">
+      <c r="C15" s="136" t="s">
         <v>5</v>
       </c>
-      <c r="D15" s="150" t="s">
+      <c r="D15" s="137" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="151"/>
-      <c r="F15" s="114" t="s">
+      <c r="E15" s="138"/>
+      <c r="F15" s="87" t="s">
         <v>28</v>
       </c>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="116"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="46" t="s">
+      <c r="G15" s="108"/>
+      <c r="H15" s="108"/>
+      <c r="I15" s="88"/>
+      <c r="J15" s="219"/>
+      <c r="K15" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="L15" s="190" t="s">
+      <c r="L15" s="178" t="s">
         <v>34</v>
       </c>
-      <c r="M15" s="191"/>
-      <c r="N15" s="191"/>
-      <c r="O15" s="191"/>
-      <c r="P15" s="191"/>
-      <c r="Q15" s="191"/>
-      <c r="R15" s="191"/>
-      <c r="S15" s="191"/>
-      <c r="T15" s="191"/>
-      <c r="U15" s="191"/>
-      <c r="V15" s="191"/>
-      <c r="W15" s="192"/>
-      <c r="X15" s="149" t="s">
+      <c r="M15" s="179"/>
+      <c r="N15" s="179"/>
+      <c r="O15" s="179"/>
+      <c r="P15" s="179"/>
+      <c r="Q15" s="179"/>
+      <c r="R15" s="179"/>
+      <c r="S15" s="179"/>
+      <c r="T15" s="179"/>
+      <c r="U15" s="179"/>
+      <c r="V15" s="179"/>
+      <c r="W15" s="180"/>
+      <c r="X15" s="136" t="s">
         <v>51</v>
       </c>
-      <c r="Y15" s="182" t="s">
+      <c r="Y15" s="168" t="s">
         <v>10</v>
       </c>
-      <c r="Z15" s="158"/>
+      <c r="Z15" s="145"/>
     </row>
     <row r="16" spans="2:29" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="148"/>
-      <c r="C16" s="149"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="153"/>
-      <c r="F16" s="117"/>
-      <c r="G16" s="118"/>
-      <c r="H16" s="118"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="47"/>
-      <c r="K16" s="48" t="s">
+      <c r="B16" s="135"/>
+      <c r="C16" s="136"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="89"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="90"/>
+      <c r="J16" s="220"/>
+      <c r="K16" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="L16" s="217"/>
-      <c r="M16" s="217"/>
-      <c r="N16" s="217"/>
-      <c r="O16" s="217"/>
-      <c r="P16" s="217"/>
-      <c r="Q16" s="217"/>
-      <c r="R16" s="217"/>
-      <c r="S16" s="217"/>
-      <c r="T16" s="217"/>
-      <c r="U16" s="217"/>
-      <c r="V16" s="217"/>
-      <c r="W16" s="217"/>
-      <c r="X16" s="149"/>
-      <c r="Y16" s="183"/>
-      <c r="Z16" s="160"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22"/>
+      <c r="W16" s="22"/>
+      <c r="X16" s="136"/>
+      <c r="Y16" s="169"/>
+      <c r="Z16" s="147"/>
       <c r="AC16" s="20" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="2:30" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="148"/>
-      <c r="C17" s="149"/>
-      <c r="D17" s="152"/>
-      <c r="E17" s="153"/>
-      <c r="F17" s="117"/>
-      <c r="G17" s="118"/>
-      <c r="H17" s="118"/>
-      <c r="I17" s="119"/>
-      <c r="J17" s="47"/>
-      <c r="K17" s="49" t="s">
+      <c r="B17" s="135"/>
+      <c r="C17" s="136"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="140"/>
+      <c r="F17" s="89"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="90"/>
+      <c r="J17" s="220"/>
+      <c r="K17" s="47" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="217"/>
-      <c r="M17" s="217"/>
-      <c r="N17" s="217"/>
-      <c r="O17" s="217"/>
-      <c r="P17" s="217"/>
-      <c r="Q17" s="217"/>
-      <c r="R17" s="217"/>
-      <c r="S17" s="217"/>
-      <c r="T17" s="217"/>
-      <c r="U17" s="217"/>
-      <c r="V17" s="217"/>
-      <c r="W17" s="217"/>
-      <c r="X17" s="149"/>
-      <c r="Y17" s="183"/>
-      <c r="Z17" s="160"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+      <c r="T17" s="22"/>
+      <c r="U17" s="22"/>
+      <c r="V17" s="22"/>
+      <c r="W17" s="22"/>
+      <c r="X17" s="136"/>
+      <c r="Y17" s="169"/>
+      <c r="Z17" s="147"/>
       <c r="AC17" s="20" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="2:30" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="148"/>
-      <c r="C18" s="149"/>
-      <c r="D18" s="154"/>
-      <c r="E18" s="155"/>
-      <c r="F18" s="120"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="121"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="47"/>
-      <c r="K18" s="49" t="s">
+      <c r="B18" s="135"/>
+      <c r="C18" s="136"/>
+      <c r="D18" s="141"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="110"/>
+      <c r="H18" s="110"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="221"/>
+      <c r="K18" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="L18" s="217"/>
-      <c r="M18" s="217"/>
-      <c r="N18" s="217"/>
-      <c r="O18" s="217"/>
-      <c r="P18" s="217"/>
-      <c r="Q18" s="217"/>
-      <c r="R18" s="217"/>
-      <c r="S18" s="217"/>
-      <c r="T18" s="217"/>
-      <c r="U18" s="217"/>
-      <c r="V18" s="217"/>
-      <c r="W18" s="217"/>
-      <c r="X18" s="149"/>
-      <c r="Y18" s="183"/>
-      <c r="Z18" s="160"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22"/>
+      <c r="W18" s="22"/>
+      <c r="X18" s="136"/>
+      <c r="Y18" s="169"/>
+      <c r="Z18" s="147"/>
       <c r="AC18" s="20" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="19" spans="2:30" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="148"/>
-      <c r="C19" s="149"/>
+      <c r="B19" s="135"/>
+      <c r="C19" s="136"/>
       <c r="D19" s="44" t="s">
         <v>1</v>
       </c>
       <c r="E19" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="F19" s="52" t="s">
+      <c r="F19" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G19" s="52" t="s">
+      <c r="G19" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H19" s="52" t="s">
+      <c r="H19" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="52" t="s">
+      <c r="I19" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="193" t="s">
+      <c r="J19" s="181" t="s">
         <v>29</v>
       </c>
-      <c r="K19" s="194"/>
+      <c r="K19" s="182"/>
       <c r="L19" s="44">
         <v>1</v>
       </c>
@@ -7179,9 +7168,9 @@
       <c r="W19" s="44">
         <v>12</v>
       </c>
-      <c r="X19" s="149"/>
-      <c r="Y19" s="161"/>
-      <c r="Z19" s="162"/>
+      <c r="X19" s="136"/>
+      <c r="Y19" s="148"/>
+      <c r="Z19" s="149"/>
     </row>
     <row r="20" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="27">
@@ -7194,8 +7183,8 @@
       <c r="G20" s="27"/>
       <c r="H20" s="27"/>
       <c r="I20" s="26"/>
-      <c r="J20" s="141"/>
-      <c r="K20" s="143"/>
+      <c r="J20" s="117"/>
+      <c r="K20" s="119"/>
       <c r="L20" s="37"/>
       <c r="M20" s="37"/>
       <c r="N20" s="37"/>
@@ -7209,8 +7198,8 @@
       <c r="V20" s="37"/>
       <c r="W20" s="37"/>
       <c r="X20" s="40"/>
-      <c r="Y20" s="141"/>
-      <c r="Z20" s="143"/>
+      <c r="Y20" s="117"/>
+      <c r="Z20" s="119"/>
       <c r="AD20" t="s">
         <v>21</v>
       </c>
@@ -7226,8 +7215,8 @@
       <c r="G21" s="27"/>
       <c r="H21" s="27"/>
       <c r="I21" s="26"/>
-      <c r="J21" s="141"/>
-      <c r="K21" s="143"/>
+      <c r="J21" s="117"/>
+      <c r="K21" s="119"/>
       <c r="L21" s="37"/>
       <c r="M21" s="37"/>
       <c r="N21" s="37"/>
@@ -7241,8 +7230,8 @@
       <c r="V21" s="37"/>
       <c r="W21" s="37"/>
       <c r="X21" s="40"/>
-      <c r="Y21" s="141"/>
-      <c r="Z21" s="143"/>
+      <c r="Y21" s="117"/>
+      <c r="Z21" s="119"/>
       <c r="AD21" t="s">
         <v>22</v>
       </c>
@@ -7258,8 +7247,8 @@
       <c r="G22" s="27"/>
       <c r="H22" s="27"/>
       <c r="I22" s="26"/>
-      <c r="J22" s="141"/>
-      <c r="K22" s="143"/>
+      <c r="J22" s="117"/>
+      <c r="K22" s="119"/>
       <c r="L22" s="37"/>
       <c r="M22" s="37"/>
       <c r="N22" s="37"/>
@@ -7273,8 +7262,8 @@
       <c r="V22" s="37"/>
       <c r="W22" s="37"/>
       <c r="X22" s="40"/>
-      <c r="Y22" s="141"/>
-      <c r="Z22" s="143"/>
+      <c r="Y22" s="117"/>
+      <c r="Z22" s="119"/>
       <c r="AD22" t="s">
         <v>23</v>
       </c>
@@ -7290,8 +7279,8 @@
       <c r="G23" s="27"/>
       <c r="H23" s="27"/>
       <c r="I23" s="26"/>
-      <c r="J23" s="141"/>
-      <c r="K23" s="143"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="119"/>
       <c r="L23" s="37"/>
       <c r="M23" s="37"/>
       <c r="N23" s="37"/>
@@ -7305,8 +7294,8 @@
       <c r="V23" s="37"/>
       <c r="W23" s="37"/>
       <c r="X23" s="40"/>
-      <c r="Y23" s="141"/>
-      <c r="Z23" s="143"/>
+      <c r="Y23" s="117"/>
+      <c r="Z23" s="119"/>
       <c r="AD23" t="s">
         <v>24</v>
       </c>
@@ -7322,8 +7311,8 @@
       <c r="G24" s="27"/>
       <c r="H24" s="27"/>
       <c r="I24" s="26"/>
-      <c r="J24" s="141"/>
-      <c r="K24" s="143"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="119"/>
       <c r="L24" s="37"/>
       <c r="M24" s="37"/>
       <c r="N24" s="37"/>
@@ -7337,8 +7326,8 @@
       <c r="V24" s="37"/>
       <c r="W24" s="37"/>
       <c r="X24" s="40"/>
-      <c r="Y24" s="141"/>
-      <c r="Z24" s="143"/>
+      <c r="Y24" s="117"/>
+      <c r="Z24" s="119"/>
     </row>
     <row r="25" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="27">
@@ -7351,8 +7340,8 @@
       <c r="G25" s="27"/>
       <c r="H25" s="27"/>
       <c r="I25" s="26"/>
-      <c r="J25" s="141"/>
-      <c r="K25" s="143"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="119"/>
       <c r="L25" s="37"/>
       <c r="M25" s="37"/>
       <c r="N25" s="37"/>
@@ -7366,8 +7355,8 @@
       <c r="V25" s="37"/>
       <c r="W25" s="37"/>
       <c r="X25" s="40"/>
-      <c r="Y25" s="141"/>
-      <c r="Z25" s="143"/>
+      <c r="Y25" s="117"/>
+      <c r="Z25" s="119"/>
     </row>
     <row r="26" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="27">
@@ -7380,8 +7369,8 @@
       <c r="G26" s="27"/>
       <c r="H26" s="27"/>
       <c r="I26" s="26"/>
-      <c r="J26" s="141"/>
-      <c r="K26" s="143"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="119"/>
       <c r="L26" s="37"/>
       <c r="M26" s="37"/>
       <c r="N26" s="37"/>
@@ -7395,8 +7384,8 @@
       <c r="V26" s="37"/>
       <c r="W26" s="37"/>
       <c r="X26" s="40"/>
-      <c r="Y26" s="141"/>
-      <c r="Z26" s="143"/>
+      <c r="Y26" s="117"/>
+      <c r="Z26" s="119"/>
     </row>
     <row r="27" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="27">
@@ -7409,8 +7398,8 @@
       <c r="G27" s="27"/>
       <c r="H27" s="27"/>
       <c r="I27" s="26"/>
-      <c r="J27" s="141"/>
-      <c r="K27" s="143"/>
+      <c r="J27" s="117"/>
+      <c r="K27" s="119"/>
       <c r="L27" s="37"/>
       <c r="M27" s="37"/>
       <c r="N27" s="37"/>
@@ -7424,8 +7413,8 @@
       <c r="V27" s="37"/>
       <c r="W27" s="37"/>
       <c r="X27" s="40"/>
-      <c r="Y27" s="141"/>
-      <c r="Z27" s="143"/>
+      <c r="Y27" s="117"/>
+      <c r="Z27" s="119"/>
     </row>
     <row r="28" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="27">
@@ -7438,8 +7427,8 @@
       <c r="G28" s="27"/>
       <c r="H28" s="27"/>
       <c r="I28" s="26"/>
-      <c r="J28" s="141"/>
-      <c r="K28" s="143"/>
+      <c r="J28" s="117"/>
+      <c r="K28" s="119"/>
       <c r="L28" s="37"/>
       <c r="M28" s="37"/>
       <c r="N28" s="37"/>
@@ -7453,8 +7442,8 @@
       <c r="V28" s="37"/>
       <c r="W28" s="37"/>
       <c r="X28" s="40"/>
-      <c r="Y28" s="141"/>
-      <c r="Z28" s="143"/>
+      <c r="Y28" s="117"/>
+      <c r="Z28" s="119"/>
     </row>
     <row r="29" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="27">
@@ -7467,8 +7456,8 @@
       <c r="G29" s="27"/>
       <c r="H29" s="27"/>
       <c r="I29" s="26"/>
-      <c r="J29" s="141"/>
-      <c r="K29" s="143"/>
+      <c r="J29" s="117"/>
+      <c r="K29" s="119"/>
       <c r="L29" s="37"/>
       <c r="M29" s="37"/>
       <c r="N29" s="37"/>
@@ -7482,8 +7471,8 @@
       <c r="V29" s="37"/>
       <c r="W29" s="37"/>
       <c r="X29" s="40"/>
-      <c r="Y29" s="141"/>
-      <c r="Z29" s="143"/>
+      <c r="Y29" s="117"/>
+      <c r="Z29" s="119"/>
     </row>
     <row r="30" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="27">
@@ -7496,8 +7485,8 @@
       <c r="G30" s="27"/>
       <c r="H30" s="27"/>
       <c r="I30" s="26"/>
-      <c r="J30" s="141"/>
-      <c r="K30" s="143"/>
+      <c r="J30" s="117"/>
+      <c r="K30" s="119"/>
       <c r="L30" s="37"/>
       <c r="M30" s="37"/>
       <c r="N30" s="37"/>
@@ -7511,8 +7500,8 @@
       <c r="V30" s="37"/>
       <c r="W30" s="37"/>
       <c r="X30" s="40"/>
-      <c r="Y30" s="141"/>
-      <c r="Z30" s="143"/>
+      <c r="Y30" s="117"/>
+      <c r="Z30" s="119"/>
     </row>
     <row r="31" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="27">
@@ -7525,8 +7514,8 @@
       <c r="G31" s="27"/>
       <c r="H31" s="27"/>
       <c r="I31" s="26"/>
-      <c r="J31" s="141"/>
-      <c r="K31" s="143"/>
+      <c r="J31" s="117"/>
+      <c r="K31" s="119"/>
       <c r="L31" s="37"/>
       <c r="M31" s="37"/>
       <c r="N31" s="37"/>
@@ -7540,8 +7529,8 @@
       <c r="V31" s="37"/>
       <c r="W31" s="37"/>
       <c r="X31" s="40"/>
-      <c r="Y31" s="141"/>
-      <c r="Z31" s="143"/>
+      <c r="Y31" s="117"/>
+      <c r="Z31" s="119"/>
     </row>
     <row r="32" spans="2:30" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="27">
@@ -7554,8 +7543,8 @@
       <c r="G32" s="31"/>
       <c r="H32" s="31"/>
       <c r="I32" s="26"/>
-      <c r="J32" s="141"/>
-      <c r="K32" s="143"/>
+      <c r="J32" s="117"/>
+      <c r="K32" s="119"/>
       <c r="L32" s="39"/>
       <c r="M32" s="39"/>
       <c r="N32" s="39"/>
@@ -7569,8 +7558,8 @@
       <c r="V32" s="39"/>
       <c r="W32" s="39"/>
       <c r="X32" s="41"/>
-      <c r="Y32" s="141"/>
-      <c r="Z32" s="143"/>
+      <c r="Y32" s="117"/>
+      <c r="Z32" s="119"/>
     </row>
     <row r="33" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="27">
@@ -7583,8 +7572,8 @@
       <c r="G33" s="27"/>
       <c r="H33" s="27"/>
       <c r="I33" s="26"/>
-      <c r="J33" s="141"/>
-      <c r="K33" s="143"/>
+      <c r="J33" s="117"/>
+      <c r="K33" s="119"/>
       <c r="L33" s="37"/>
       <c r="M33" s="37"/>
       <c r="N33" s="37"/>
@@ -7598,8 +7587,8 @@
       <c r="V33" s="37"/>
       <c r="W33" s="37"/>
       <c r="X33" s="40"/>
-      <c r="Y33" s="141"/>
-      <c r="Z33" s="143"/>
+      <c r="Y33" s="117"/>
+      <c r="Z33" s="119"/>
     </row>
     <row r="34" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="27">
@@ -7612,8 +7601,8 @@
       <c r="G34" s="27"/>
       <c r="H34" s="27"/>
       <c r="I34" s="26"/>
-      <c r="J34" s="141"/>
-      <c r="K34" s="143"/>
+      <c r="J34" s="117"/>
+      <c r="K34" s="119"/>
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
       <c r="N34" s="37"/>
@@ -7627,8 +7616,8 @@
       <c r="V34" s="37"/>
       <c r="W34" s="37"/>
       <c r="X34" s="40"/>
-      <c r="Y34" s="141"/>
-      <c r="Z34" s="143"/>
+      <c r="Y34" s="117"/>
+      <c r="Z34" s="119"/>
     </row>
     <row r="35" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="27">
@@ -7641,8 +7630,8 @@
       <c r="G35" s="31"/>
       <c r="H35" s="31"/>
       <c r="I35" s="26"/>
-      <c r="J35" s="141"/>
-      <c r="K35" s="143"/>
+      <c r="J35" s="117"/>
+      <c r="K35" s="119"/>
       <c r="L35" s="39"/>
       <c r="M35" s="39"/>
       <c r="N35" s="39"/>
@@ -7656,8 +7645,8 @@
       <c r="V35" s="39"/>
       <c r="W35" s="39"/>
       <c r="X35" s="41"/>
-      <c r="Y35" s="141"/>
-      <c r="Z35" s="143"/>
+      <c r="Y35" s="117"/>
+      <c r="Z35" s="119"/>
     </row>
     <row r="36" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="27">
@@ -7670,8 +7659,8 @@
       <c r="G36" s="27"/>
       <c r="H36" s="27"/>
       <c r="I36" s="26"/>
-      <c r="J36" s="141"/>
-      <c r="K36" s="143"/>
+      <c r="J36" s="117"/>
+      <c r="K36" s="119"/>
       <c r="L36" s="37"/>
       <c r="M36" s="37"/>
       <c r="N36" s="37"/>
@@ -7685,8 +7674,8 @@
       <c r="V36" s="37"/>
       <c r="W36" s="37"/>
       <c r="X36" s="40"/>
-      <c r="Y36" s="141"/>
-      <c r="Z36" s="143"/>
+      <c r="Y36" s="117"/>
+      <c r="Z36" s="119"/>
     </row>
     <row r="37" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="27">
@@ -7699,8 +7688,8 @@
       <c r="G37" s="27"/>
       <c r="H37" s="27"/>
       <c r="I37" s="26"/>
-      <c r="J37" s="141"/>
-      <c r="K37" s="143"/>
+      <c r="J37" s="117"/>
+      <c r="K37" s="119"/>
       <c r="L37" s="37"/>
       <c r="M37" s="37"/>
       <c r="N37" s="37"/>
@@ -7714,8 +7703,8 @@
       <c r="V37" s="37"/>
       <c r="W37" s="37"/>
       <c r="X37" s="40"/>
-      <c r="Y37" s="141"/>
-      <c r="Z37" s="143"/>
+      <c r="Y37" s="117"/>
+      <c r="Z37" s="119"/>
     </row>
     <row r="38" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="27">
@@ -7728,8 +7717,8 @@
       <c r="G38" s="31"/>
       <c r="H38" s="31"/>
       <c r="I38" s="26"/>
-      <c r="J38" s="141"/>
-      <c r="K38" s="143"/>
+      <c r="J38" s="117"/>
+      <c r="K38" s="119"/>
       <c r="L38" s="39"/>
       <c r="M38" s="39"/>
       <c r="N38" s="39"/>
@@ -7743,8 +7732,8 @@
       <c r="V38" s="39"/>
       <c r="W38" s="39"/>
       <c r="X38" s="41"/>
-      <c r="Y38" s="141"/>
-      <c r="Z38" s="143"/>
+      <c r="Y38" s="117"/>
+      <c r="Z38" s="119"/>
     </row>
     <row r="39" spans="2:26" ht="50.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="27">
@@ -7757,8 +7746,8 @@
       <c r="G39" s="27"/>
       <c r="H39" s="27"/>
       <c r="I39" s="26"/>
-      <c r="J39" s="141"/>
-      <c r="K39" s="143"/>
+      <c r="J39" s="117"/>
+      <c r="K39" s="119"/>
       <c r="L39" s="37"/>
       <c r="M39" s="37"/>
       <c r="N39" s="37"/>
@@ -7772,51 +7761,12 @@
       <c r="V39" s="37"/>
       <c r="W39" s="37"/>
       <c r="X39" s="40"/>
-      <c r="Y39" s="141"/>
-      <c r="Z39" s="143"/>
+      <c r="Y39" s="117"/>
+      <c r="Z39" s="119"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
-  <mergeCells count="55">
-    <mergeCell ref="B11:Z12"/>
-    <mergeCell ref="K13:X14"/>
-    <mergeCell ref="X15:X19"/>
-    <mergeCell ref="F15:I18"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="L15:W15"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="G14:J14"/>
-    <mergeCell ref="Y15:Z19"/>
-    <mergeCell ref="B15:B19"/>
-    <mergeCell ref="C15:C19"/>
-    <mergeCell ref="D15:E18"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="J37:K37"/>
-    <mergeCell ref="J38:K38"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="J32:K32"/>
-    <mergeCell ref="J33:K33"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="Y30:Z30"/>
-    <mergeCell ref="Y31:Z31"/>
-    <mergeCell ref="Y32:Z32"/>
-    <mergeCell ref="Y33:Z33"/>
-    <mergeCell ref="J35:K35"/>
+  <mergeCells count="56">
     <mergeCell ref="Y20:Z20"/>
     <mergeCell ref="Y21:Z21"/>
     <mergeCell ref="Y22:Z22"/>
@@ -7833,6 +7783,46 @@
     <mergeCell ref="Y27:Z27"/>
     <mergeCell ref="Y28:Z28"/>
     <mergeCell ref="Y29:Z29"/>
+    <mergeCell ref="Y30:Z30"/>
+    <mergeCell ref="Y31:Z31"/>
+    <mergeCell ref="Y32:Z32"/>
+    <mergeCell ref="Y33:Z33"/>
+    <mergeCell ref="J35:K35"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="J38:K38"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="J32:K32"/>
+    <mergeCell ref="J33:K33"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="B11:Z12"/>
+    <mergeCell ref="K13:X14"/>
+    <mergeCell ref="X15:X19"/>
+    <mergeCell ref="F15:I18"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="L15:W15"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="G14:J14"/>
+    <mergeCell ref="Y15:Z19"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="C15:C19"/>
+    <mergeCell ref="D15:E18"/>
+    <mergeCell ref="J15:J18"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L20:W39" xr:uid="{00000000-0002-0000-0300-000000000000}">
@@ -7859,6 +7849,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06398501-6A15-4E38-A0B6-B671C9B4D7D7}">
   <sheetPr codeName="Sayfa6">
     <tabColor theme="3" tint="0.39997558519241921"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -7867,679 +7858,685 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="85"/>
-      <c r="B1" s="88" t="s">
+      <c r="A1" s="184"/>
+      <c r="B1" s="187" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
-      <c r="G1" s="88"/>
-      <c r="H1" s="88"/>
-      <c r="I1" s="91" t="s">
+      <c r="C1" s="187"/>
+      <c r="D1" s="187"/>
+      <c r="E1" s="187"/>
+      <c r="F1" s="187"/>
+      <c r="G1" s="187"/>
+      <c r="H1" s="187"/>
+      <c r="I1" s="190" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="92"/>
+      <c r="J1" s="191"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="86"/>
-      <c r="B2" s="89"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="89"/>
-      <c r="E2" s="89"/>
-      <c r="F2" s="89"/>
-      <c r="G2" s="89"/>
-      <c r="H2" s="89"/>
-      <c r="I2" s="93" t="s">
+      <c r="A2" s="185"/>
+      <c r="B2" s="188"/>
+      <c r="C2" s="188"/>
+      <c r="D2" s="188"/>
+      <c r="E2" s="188"/>
+      <c r="F2" s="188"/>
+      <c r="G2" s="188"/>
+      <c r="H2" s="188"/>
+      <c r="I2" s="192" t="s">
         <v>43</v>
       </c>
-      <c r="J2" s="94"/>
+      <c r="J2" s="193"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="86"/>
-      <c r="B3" s="89"/>
-      <c r="C3" s="89"/>
-      <c r="D3" s="89"/>
-      <c r="E3" s="89"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="89"/>
-      <c r="H3" s="89"/>
-      <c r="I3" s="95" t="s">
+      <c r="A3" s="185"/>
+      <c r="B3" s="188"/>
+      <c r="C3" s="188"/>
+      <c r="D3" s="188"/>
+      <c r="E3" s="188"/>
+      <c r="F3" s="188"/>
+      <c r="G3" s="188"/>
+      <c r="H3" s="188"/>
+      <c r="I3" s="194" t="s">
         <v>44</v>
       </c>
-      <c r="J3" s="96"/>
+      <c r="J3" s="195"/>
     </row>
     <row r="4" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="86"/>
-      <c r="B4" s="89"/>
-      <c r="C4" s="89"/>
-      <c r="D4" s="89"/>
-      <c r="E4" s="89"/>
-      <c r="F4" s="89"/>
-      <c r="G4" s="89"/>
-      <c r="H4" s="89"/>
-      <c r="I4" s="93" t="s">
+      <c r="A4" s="185"/>
+      <c r="B4" s="188"/>
+      <c r="C4" s="188"/>
+      <c r="D4" s="188"/>
+      <c r="E4" s="188"/>
+      <c r="F4" s="188"/>
+      <c r="G4" s="188"/>
+      <c r="H4" s="188"/>
+      <c r="I4" s="192" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="94"/>
+      <c r="J4" s="193"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A5" s="86"/>
-      <c r="B5" s="89"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="89"/>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="95" t="s">
+      <c r="A5" s="185"/>
+      <c r="B5" s="188"/>
+      <c r="C5" s="188"/>
+      <c r="D5" s="188"/>
+      <c r="E5" s="188"/>
+      <c r="F5" s="188"/>
+      <c r="G5" s="188"/>
+      <c r="H5" s="188"/>
+      <c r="I5" s="194" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="96"/>
+      <c r="J5" s="195"/>
     </row>
     <row r="6" spans="1:10" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="87"/>
-      <c r="B6" s="90"/>
-      <c r="C6" s="90"/>
-      <c r="D6" s="90"/>
-      <c r="E6" s="90"/>
-      <c r="F6" s="90"/>
-      <c r="G6" s="90"/>
-      <c r="H6" s="90"/>
-      <c r="I6" s="97">
+      <c r="A6" s="186"/>
+      <c r="B6" s="189"/>
+      <c r="C6" s="189"/>
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="196">
         <v>46237</v>
       </c>
-      <c r="J6" s="98"/>
+      <c r="J6" s="197"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A7" s="64"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="65"/>
-      <c r="E7" s="65"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
-      <c r="I7" s="65"/>
-      <c r="J7" s="66"/>
+      <c r="A7" s="198"/>
+      <c r="B7" s="199"/>
+      <c r="C7" s="199"/>
+      <c r="D7" s="199"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
+      <c r="G7" s="199"/>
+      <c r="H7" s="199"/>
+      <c r="I7" s="199"/>
+      <c r="J7" s="200"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="201" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="69"/>
+      <c r="B8" s="202"/>
+      <c r="C8" s="202"/>
+      <c r="D8" s="202"/>
+      <c r="E8" s="202"/>
+      <c r="F8" s="202"/>
+      <c r="G8" s="202"/>
+      <c r="H8" s="202"/>
+      <c r="I8" s="202"/>
+      <c r="J8" s="203"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A9" s="70"/>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
-      <c r="G9" s="71"/>
-      <c r="H9" s="71"/>
-      <c r="I9" s="71"/>
-      <c r="J9" s="72"/>
+      <c r="A9" s="204"/>
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
+      <c r="D9" s="205"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="205"/>
+      <c r="G9" s="205"/>
+      <c r="H9" s="205"/>
+      <c r="I9" s="205"/>
+      <c r="J9" s="206"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A10" s="73"/>
-      <c r="B10" s="74"/>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74"/>
-      <c r="G10" s="74"/>
-      <c r="H10" s="74"/>
-      <c r="I10" s="74"/>
-      <c r="J10" s="75"/>
+      <c r="A10" s="207"/>
+      <c r="B10" s="208"/>
+      <c r="C10" s="208"/>
+      <c r="D10" s="208"/>
+      <c r="E10" s="208"/>
+      <c r="F10" s="208"/>
+      <c r="G10" s="208"/>
+      <c r="H10" s="208"/>
+      <c r="I10" s="208"/>
+      <c r="J10" s="209"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A11" s="59"/>
-      <c r="B11" s="60"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="60"/>
-      <c r="E11" s="60"/>
-      <c r="F11" s="60"/>
-      <c r="G11" s="60"/>
-      <c r="H11" s="60"/>
-      <c r="I11" s="60"/>
-      <c r="J11" s="61"/>
+      <c r="A11" s="55"/>
+      <c r="B11" s="56"/>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="57"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="210" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="77"/>
-      <c r="C12" s="77"/>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="77"/>
-      <c r="G12" s="77"/>
-      <c r="H12" s="77"/>
-      <c r="I12" s="77"/>
-      <c r="J12" s="78"/>
+      <c r="B12" s="211"/>
+      <c r="C12" s="211"/>
+      <c r="D12" s="211"/>
+      <c r="E12" s="211"/>
+      <c r="F12" s="211"/>
+      <c r="G12" s="211"/>
+      <c r="H12" s="211"/>
+      <c r="I12" s="211"/>
+      <c r="J12" s="212"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="76"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77"/>
-      <c r="G13" s="77"/>
-      <c r="H13" s="77"/>
-      <c r="I13" s="77"/>
-      <c r="J13" s="78"/>
+      <c r="A13" s="210"/>
+      <c r="B13" s="211"/>
+      <c r="C13" s="211"/>
+      <c r="D13" s="211"/>
+      <c r="E13" s="211"/>
+      <c r="F13" s="211"/>
+      <c r="G13" s="211"/>
+      <c r="H13" s="211"/>
+      <c r="I13" s="211"/>
+      <c r="J13" s="212"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A14" s="76"/>
-      <c r="B14" s="77"/>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77"/>
-      <c r="G14" s="77"/>
-      <c r="H14" s="77"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="78"/>
+      <c r="A14" s="210"/>
+      <c r="B14" s="211"/>
+      <c r="C14" s="211"/>
+      <c r="D14" s="211"/>
+      <c r="E14" s="211"/>
+      <c r="F14" s="211"/>
+      <c r="G14" s="211"/>
+      <c r="H14" s="211"/>
+      <c r="I14" s="211"/>
+      <c r="J14" s="212"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="76"/>
-      <c r="B15" s="77"/>
-      <c r="C15" s="77"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="78"/>
+      <c r="A15" s="210"/>
+      <c r="B15" s="211"/>
+      <c r="C15" s="211"/>
+      <c r="D15" s="211"/>
+      <c r="E15" s="211"/>
+      <c r="F15" s="211"/>
+      <c r="G15" s="211"/>
+      <c r="H15" s="211"/>
+      <c r="I15" s="211"/>
+      <c r="J15" s="212"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="76"/>
-      <c r="B16" s="77"/>
-      <c r="C16" s="77"/>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="78"/>
+      <c r="A16" s="210"/>
+      <c r="B16" s="211"/>
+      <c r="C16" s="211"/>
+      <c r="D16" s="211"/>
+      <c r="E16" s="211"/>
+      <c r="F16" s="211"/>
+      <c r="G16" s="211"/>
+      <c r="H16" s="211"/>
+      <c r="I16" s="211"/>
+      <c r="J16" s="212"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="76"/>
-      <c r="B17" s="77"/>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="77"/>
-      <c r="H17" s="77"/>
-      <c r="I17" s="77"/>
-      <c r="J17" s="78"/>
+      <c r="A17" s="210"/>
+      <c r="B17" s="211"/>
+      <c r="C17" s="211"/>
+      <c r="D17" s="211"/>
+      <c r="E17" s="211"/>
+      <c r="F17" s="211"/>
+      <c r="G17" s="211"/>
+      <c r="H17" s="211"/>
+      <c r="I17" s="211"/>
+      <c r="J17" s="212"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="76"/>
-      <c r="B18" s="77"/>
-      <c r="C18" s="77"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="78"/>
+      <c r="A18" s="210"/>
+      <c r="B18" s="211"/>
+      <c r="C18" s="211"/>
+      <c r="D18" s="211"/>
+      <c r="E18" s="211"/>
+      <c r="F18" s="211"/>
+      <c r="G18" s="211"/>
+      <c r="H18" s="211"/>
+      <c r="I18" s="211"/>
+      <c r="J18" s="212"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="76"/>
-      <c r="B19" s="77"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="78"/>
+      <c r="A19" s="210"/>
+      <c r="B19" s="211"/>
+      <c r="C19" s="211"/>
+      <c r="D19" s="211"/>
+      <c r="E19" s="211"/>
+      <c r="F19" s="211"/>
+      <c r="G19" s="211"/>
+      <c r="H19" s="211"/>
+      <c r="I19" s="211"/>
+      <c r="J19" s="212"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="76"/>
-      <c r="B20" s="77"/>
-      <c r="C20" s="77"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="78"/>
+      <c r="A20" s="210"/>
+      <c r="B20" s="211"/>
+      <c r="C20" s="211"/>
+      <c r="D20" s="211"/>
+      <c r="E20" s="211"/>
+      <c r="F20" s="211"/>
+      <c r="G20" s="211"/>
+      <c r="H20" s="211"/>
+      <c r="I20" s="211"/>
+      <c r="J20" s="212"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="76"/>
-      <c r="B21" s="77"/>
-      <c r="C21" s="77"/>
-      <c r="D21" s="77"/>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="78"/>
+      <c r="A21" s="210"/>
+      <c r="B21" s="211"/>
+      <c r="C21" s="211"/>
+      <c r="D21" s="211"/>
+      <c r="E21" s="211"/>
+      <c r="F21" s="211"/>
+      <c r="G21" s="211"/>
+      <c r="H21" s="211"/>
+      <c r="I21" s="211"/>
+      <c r="J21" s="212"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="76"/>
-      <c r="B22" s="77"/>
-      <c r="C22" s="77"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="78"/>
+      <c r="A22" s="210"/>
+      <c r="B22" s="211"/>
+      <c r="C22" s="211"/>
+      <c r="D22" s="211"/>
+      <c r="E22" s="211"/>
+      <c r="F22" s="211"/>
+      <c r="G22" s="211"/>
+      <c r="H22" s="211"/>
+      <c r="I22" s="211"/>
+      <c r="J22" s="212"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="76"/>
-      <c r="B23" s="77"/>
-      <c r="C23" s="77"/>
-      <c r="D23" s="77"/>
-      <c r="E23" s="77"/>
-      <c r="F23" s="77"/>
-      <c r="G23" s="77"/>
-      <c r="H23" s="77"/>
-      <c r="I23" s="77"/>
-      <c r="J23" s="78"/>
+      <c r="A23" s="210"/>
+      <c r="B23" s="211"/>
+      <c r="C23" s="211"/>
+      <c r="D23" s="211"/>
+      <c r="E23" s="211"/>
+      <c r="F23" s="211"/>
+      <c r="G23" s="211"/>
+      <c r="H23" s="211"/>
+      <c r="I23" s="211"/>
+      <c r="J23" s="212"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="76"/>
-      <c r="B24" s="77"/>
-      <c r="C24" s="77"/>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="77"/>
-      <c r="J24" s="78"/>
+      <c r="A24" s="210"/>
+      <c r="B24" s="211"/>
+      <c r="C24" s="211"/>
+      <c r="D24" s="211"/>
+      <c r="E24" s="211"/>
+      <c r="F24" s="211"/>
+      <c r="G24" s="211"/>
+      <c r="H24" s="211"/>
+      <c r="I24" s="211"/>
+      <c r="J24" s="212"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="76"/>
-      <c r="B25" s="77"/>
-      <c r="C25" s="77"/>
-      <c r="D25" s="77"/>
-      <c r="E25" s="77"/>
-      <c r="F25" s="77"/>
-      <c r="G25" s="77"/>
-      <c r="H25" s="77"/>
-      <c r="I25" s="77"/>
-      <c r="J25" s="78"/>
+      <c r="A25" s="210"/>
+      <c r="B25" s="211"/>
+      <c r="C25" s="211"/>
+      <c r="D25" s="211"/>
+      <c r="E25" s="211"/>
+      <c r="F25" s="211"/>
+      <c r="G25" s="211"/>
+      <c r="H25" s="211"/>
+      <c r="I25" s="211"/>
+      <c r="J25" s="212"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="76"/>
-      <c r="B26" s="77"/>
-      <c r="C26" s="77"/>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="77"/>
-      <c r="J26" s="78"/>
+      <c r="A26" s="210"/>
+      <c r="B26" s="211"/>
+      <c r="C26" s="211"/>
+      <c r="D26" s="211"/>
+      <c r="E26" s="211"/>
+      <c r="F26" s="211"/>
+      <c r="G26" s="211"/>
+      <c r="H26" s="211"/>
+      <c r="I26" s="211"/>
+      <c r="J26" s="212"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="76"/>
-      <c r="B27" s="77"/>
-      <c r="C27" s="77"/>
-      <c r="D27" s="77"/>
-      <c r="E27" s="77"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="77"/>
-      <c r="H27" s="77"/>
-      <c r="I27" s="77"/>
-      <c r="J27" s="78"/>
+      <c r="A27" s="210"/>
+      <c r="B27" s="211"/>
+      <c r="C27" s="211"/>
+      <c r="D27" s="211"/>
+      <c r="E27" s="211"/>
+      <c r="F27" s="211"/>
+      <c r="G27" s="211"/>
+      <c r="H27" s="211"/>
+      <c r="I27" s="211"/>
+      <c r="J27" s="212"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="76"/>
-      <c r="B28" s="77"/>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
-      <c r="E28" s="77"/>
-      <c r="F28" s="77"/>
-      <c r="G28" s="77"/>
-      <c r="H28" s="77"/>
-      <c r="I28" s="77"/>
-      <c r="J28" s="78"/>
+      <c r="A28" s="210"/>
+      <c r="B28" s="211"/>
+      <c r="C28" s="211"/>
+      <c r="D28" s="211"/>
+      <c r="E28" s="211"/>
+      <c r="F28" s="211"/>
+      <c r="G28" s="211"/>
+      <c r="H28" s="211"/>
+      <c r="I28" s="211"/>
+      <c r="J28" s="212"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="76"/>
-      <c r="B29" s="77"/>
-      <c r="C29" s="77"/>
-      <c r="D29" s="77"/>
-      <c r="E29" s="77"/>
-      <c r="F29" s="77"/>
-      <c r="G29" s="77"/>
-      <c r="H29" s="77"/>
-      <c r="I29" s="77"/>
-      <c r="J29" s="78"/>
+      <c r="A29" s="210"/>
+      <c r="B29" s="211"/>
+      <c r="C29" s="211"/>
+      <c r="D29" s="211"/>
+      <c r="E29" s="211"/>
+      <c r="F29" s="211"/>
+      <c r="G29" s="211"/>
+      <c r="H29" s="211"/>
+      <c r="I29" s="211"/>
+      <c r="J29" s="212"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="76"/>
-      <c r="B30" s="77"/>
-      <c r="C30" s="77"/>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="77"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
-      <c r="I30" s="77"/>
-      <c r="J30" s="78"/>
+      <c r="A30" s="210"/>
+      <c r="B30" s="211"/>
+      <c r="C30" s="211"/>
+      <c r="D30" s="211"/>
+      <c r="E30" s="211"/>
+      <c r="F30" s="211"/>
+      <c r="G30" s="211"/>
+      <c r="H30" s="211"/>
+      <c r="I30" s="211"/>
+      <c r="J30" s="212"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="76"/>
-      <c r="B31" s="77"/>
-      <c r="C31" s="77"/>
-      <c r="D31" s="77"/>
-      <c r="E31" s="77"/>
-      <c r="F31" s="77"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-      <c r="I31" s="77"/>
-      <c r="J31" s="78"/>
+      <c r="A31" s="210"/>
+      <c r="B31" s="211"/>
+      <c r="C31" s="211"/>
+      <c r="D31" s="211"/>
+      <c r="E31" s="211"/>
+      <c r="F31" s="211"/>
+      <c r="G31" s="211"/>
+      <c r="H31" s="211"/>
+      <c r="I31" s="211"/>
+      <c r="J31" s="212"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="76"/>
-      <c r="B32" s="77"/>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
-      <c r="E32" s="77"/>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-      <c r="I32" s="77"/>
-      <c r="J32" s="78"/>
+      <c r="A32" s="210"/>
+      <c r="B32" s="211"/>
+      <c r="C32" s="211"/>
+      <c r="D32" s="211"/>
+      <c r="E32" s="211"/>
+      <c r="F32" s="211"/>
+      <c r="G32" s="211"/>
+      <c r="H32" s="211"/>
+      <c r="I32" s="211"/>
+      <c r="J32" s="212"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="76"/>
-      <c r="B33" s="77"/>
-      <c r="C33" s="77"/>
-      <c r="D33" s="77"/>
-      <c r="E33" s="77"/>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-      <c r="I33" s="77"/>
-      <c r="J33" s="78"/>
+      <c r="A33" s="210"/>
+      <c r="B33" s="211"/>
+      <c r="C33" s="211"/>
+      <c r="D33" s="211"/>
+      <c r="E33" s="211"/>
+      <c r="F33" s="211"/>
+      <c r="G33" s="211"/>
+      <c r="H33" s="211"/>
+      <c r="I33" s="211"/>
+      <c r="J33" s="212"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A34" s="76"/>
-      <c r="B34" s="77"/>
-      <c r="C34" s="77"/>
-      <c r="D34" s="77"/>
-      <c r="E34" s="77"/>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
-      <c r="I34" s="77"/>
-      <c r="J34" s="78"/>
+      <c r="A34" s="210"/>
+      <c r="B34" s="211"/>
+      <c r="C34" s="211"/>
+      <c r="D34" s="211"/>
+      <c r="E34" s="211"/>
+      <c r="F34" s="211"/>
+      <c r="G34" s="211"/>
+      <c r="H34" s="211"/>
+      <c r="I34" s="211"/>
+      <c r="J34" s="212"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="76"/>
-      <c r="B35" s="77"/>
-      <c r="C35" s="77"/>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="77"/>
-      <c r="J35" s="78"/>
+      <c r="A35" s="210"/>
+      <c r="B35" s="211"/>
+      <c r="C35" s="211"/>
+      <c r="D35" s="211"/>
+      <c r="E35" s="211"/>
+      <c r="F35" s="211"/>
+      <c r="G35" s="211"/>
+      <c r="H35" s="211"/>
+      <c r="I35" s="211"/>
+      <c r="J35" s="212"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A36" s="76"/>
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
-      <c r="J36" s="78"/>
+      <c r="A36" s="210"/>
+      <c r="B36" s="211"/>
+      <c r="C36" s="211"/>
+      <c r="D36" s="211"/>
+      <c r="E36" s="211"/>
+      <c r="F36" s="211"/>
+      <c r="G36" s="211"/>
+      <c r="H36" s="211"/>
+      <c r="I36" s="211"/>
+      <c r="J36" s="212"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="76"/>
-      <c r="B37" s="77"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="77"/>
-      <c r="E37" s="77"/>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-      <c r="I37" s="77"/>
-      <c r="J37" s="78"/>
+      <c r="A37" s="210"/>
+      <c r="B37" s="211"/>
+      <c r="C37" s="211"/>
+      <c r="D37" s="211"/>
+      <c r="E37" s="211"/>
+      <c r="F37" s="211"/>
+      <c r="G37" s="211"/>
+      <c r="H37" s="211"/>
+      <c r="I37" s="211"/>
+      <c r="J37" s="212"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" s="76"/>
-      <c r="B38" s="77"/>
-      <c r="C38" s="77"/>
-      <c r="D38" s="77"/>
-      <c r="E38" s="77"/>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-      <c r="I38" s="77"/>
-      <c r="J38" s="78"/>
+      <c r="A38" s="210"/>
+      <c r="B38" s="211"/>
+      <c r="C38" s="211"/>
+      <c r="D38" s="211"/>
+      <c r="E38" s="211"/>
+      <c r="F38" s="211"/>
+      <c r="G38" s="211"/>
+      <c r="H38" s="211"/>
+      <c r="I38" s="211"/>
+      <c r="J38" s="212"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" s="76"/>
-      <c r="B39" s="77"/>
-      <c r="C39" s="77"/>
-      <c r="D39" s="77"/>
-      <c r="E39" s="77"/>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-      <c r="I39" s="77"/>
-      <c r="J39" s="78"/>
+      <c r="A39" s="210"/>
+      <c r="B39" s="211"/>
+      <c r="C39" s="211"/>
+      <c r="D39" s="211"/>
+      <c r="E39" s="211"/>
+      <c r="F39" s="211"/>
+      <c r="G39" s="211"/>
+      <c r="H39" s="211"/>
+      <c r="I39" s="211"/>
+      <c r="J39" s="212"/>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A40" s="76"/>
-      <c r="B40" s="77"/>
-      <c r="C40" s="77"/>
-      <c r="D40" s="77"/>
-      <c r="E40" s="77"/>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-      <c r="I40" s="77"/>
-      <c r="J40" s="78"/>
+      <c r="A40" s="210"/>
+      <c r="B40" s="211"/>
+      <c r="C40" s="211"/>
+      <c r="D40" s="211"/>
+      <c r="E40" s="211"/>
+      <c r="F40" s="211"/>
+      <c r="G40" s="211"/>
+      <c r="H40" s="211"/>
+      <c r="I40" s="211"/>
+      <c r="J40" s="212"/>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A41" s="76"/>
-      <c r="B41" s="77"/>
-      <c r="C41" s="77"/>
-      <c r="D41" s="77"/>
-      <c r="E41" s="77"/>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
-      <c r="I41" s="77"/>
-      <c r="J41" s="78"/>
+      <c r="A41" s="210"/>
+      <c r="B41" s="211"/>
+      <c r="C41" s="211"/>
+      <c r="D41" s="211"/>
+      <c r="E41" s="211"/>
+      <c r="F41" s="211"/>
+      <c r="G41" s="211"/>
+      <c r="H41" s="211"/>
+      <c r="I41" s="211"/>
+      <c r="J41" s="212"/>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="76"/>
-      <c r="B42" s="77"/>
-      <c r="C42" s="77"/>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
-      <c r="I42" s="77"/>
-      <c r="J42" s="78"/>
+      <c r="A42" s="210"/>
+      <c r="B42" s="211"/>
+      <c r="C42" s="211"/>
+      <c r="D42" s="211"/>
+      <c r="E42" s="211"/>
+      <c r="F42" s="211"/>
+      <c r="G42" s="211"/>
+      <c r="H42" s="211"/>
+      <c r="I42" s="211"/>
+      <c r="J42" s="212"/>
     </row>
     <row r="43" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="76"/>
-      <c r="B43" s="77"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
-      <c r="I43" s="77"/>
-      <c r="J43" s="78"/>
+      <c r="A43" s="210"/>
+      <c r="B43" s="211"/>
+      <c r="C43" s="211"/>
+      <c r="D43" s="211"/>
+      <c r="E43" s="211"/>
+      <c r="F43" s="211"/>
+      <c r="G43" s="211"/>
+      <c r="H43" s="211"/>
+      <c r="I43" s="211"/>
+      <c r="J43" s="212"/>
     </row>
     <row r="44" spans="1:10" ht="3" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="76"/>
-      <c r="B44" s="77"/>
-      <c r="C44" s="77"/>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
-      <c r="I44" s="77"/>
-      <c r="J44" s="78"/>
+      <c r="A44" s="210"/>
+      <c r="B44" s="211"/>
+      <c r="C44" s="211"/>
+      <c r="D44" s="211"/>
+      <c r="E44" s="211"/>
+      <c r="F44" s="211"/>
+      <c r="G44" s="211"/>
+      <c r="H44" s="211"/>
+      <c r="I44" s="211"/>
+      <c r="J44" s="212"/>
     </row>
     <row r="45" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="76" t="s">
+      <c r="A45" s="210" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="77"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="77"/>
-      <c r="G45" s="77"/>
-      <c r="H45" s="77"/>
-      <c r="I45" s="77"/>
-      <c r="J45" s="78"/>
+      <c r="B45" s="211"/>
+      <c r="C45" s="211"/>
+      <c r="D45" s="211"/>
+      <c r="E45" s="211"/>
+      <c r="F45" s="211"/>
+      <c r="G45" s="211"/>
+      <c r="H45" s="211"/>
+      <c r="I45" s="211"/>
+      <c r="J45" s="212"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="76"/>
-      <c r="B46" s="77"/>
-      <c r="C46" s="77"/>
-      <c r="D46" s="77"/>
-      <c r="E46" s="77"/>
-      <c r="F46" s="77"/>
-      <c r="G46" s="77"/>
-      <c r="H46" s="77"/>
-      <c r="I46" s="77"/>
-      <c r="J46" s="78"/>
+      <c r="A46" s="210"/>
+      <c r="B46" s="211"/>
+      <c r="C46" s="211"/>
+      <c r="D46" s="211"/>
+      <c r="E46" s="211"/>
+      <c r="F46" s="211"/>
+      <c r="G46" s="211"/>
+      <c r="H46" s="211"/>
+      <c r="I46" s="211"/>
+      <c r="J46" s="212"/>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" s="76"/>
-      <c r="B47" s="77"/>
-      <c r="C47" s="77"/>
-      <c r="D47" s="77"/>
-      <c r="E47" s="77"/>
-      <c r="F47" s="77"/>
-      <c r="G47" s="77"/>
-      <c r="H47" s="77"/>
-      <c r="I47" s="77"/>
-      <c r="J47" s="78"/>
+      <c r="A47" s="210"/>
+      <c r="B47" s="211"/>
+      <c r="C47" s="211"/>
+      <c r="D47" s="211"/>
+      <c r="E47" s="211"/>
+      <c r="F47" s="211"/>
+      <c r="G47" s="211"/>
+      <c r="H47" s="211"/>
+      <c r="I47" s="211"/>
+      <c r="J47" s="212"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A48" s="76"/>
-      <c r="B48" s="77"/>
-      <c r="C48" s="77"/>
-      <c r="D48" s="77"/>
-      <c r="E48" s="77"/>
-      <c r="F48" s="77"/>
-      <c r="G48" s="77"/>
-      <c r="H48" s="77"/>
-      <c r="I48" s="77"/>
-      <c r="J48" s="78"/>
+      <c r="A48" s="210"/>
+      <c r="B48" s="211"/>
+      <c r="C48" s="211"/>
+      <c r="D48" s="211"/>
+      <c r="E48" s="211"/>
+      <c r="F48" s="211"/>
+      <c r="G48" s="211"/>
+      <c r="H48" s="211"/>
+      <c r="I48" s="211"/>
+      <c r="J48" s="212"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="76"/>
-      <c r="B49" s="77"/>
-      <c r="C49" s="77"/>
-      <c r="D49" s="77"/>
-      <c r="E49" s="77"/>
-      <c r="F49" s="77"/>
-      <c r="G49" s="77"/>
-      <c r="H49" s="77"/>
-      <c r="I49" s="77"/>
-      <c r="J49" s="78"/>
+      <c r="A49" s="210"/>
+      <c r="B49" s="211"/>
+      <c r="C49" s="211"/>
+      <c r="D49" s="211"/>
+      <c r="E49" s="211"/>
+      <c r="F49" s="211"/>
+      <c r="G49" s="211"/>
+      <c r="H49" s="211"/>
+      <c r="I49" s="211"/>
+      <c r="J49" s="212"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="79" t="s">
+      <c r="A50" s="213" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="80"/>
-      <c r="C50" s="80"/>
-      <c r="D50" s="80"/>
-      <c r="E50" s="80"/>
-      <c r="F50" s="80" t="s">
+      <c r="B50" s="214"/>
+      <c r="C50" s="214"/>
+      <c r="D50" s="214"/>
+      <c r="E50" s="214"/>
+      <c r="F50" s="214" t="s">
         <v>48</v>
       </c>
-      <c r="G50" s="80"/>
-      <c r="H50" s="80"/>
-      <c r="I50" s="80"/>
-      <c r="J50" s="83"/>
+      <c r="G50" s="214"/>
+      <c r="H50" s="214"/>
+      <c r="I50" s="214"/>
+      <c r="J50" s="217"/>
     </row>
     <row r="51" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="81"/>
-      <c r="B51" s="82"/>
-      <c r="C51" s="82"/>
-      <c r="D51" s="82"/>
-      <c r="E51" s="82"/>
-      <c r="F51" s="82"/>
-      <c r="G51" s="82"/>
-      <c r="H51" s="82"/>
-      <c r="I51" s="82"/>
-      <c r="J51" s="84"/>
+      <c r="A51" s="215"/>
+      <c r="B51" s="216"/>
+      <c r="C51" s="216"/>
+      <c r="D51" s="216"/>
+      <c r="E51" s="216"/>
+      <c r="F51" s="216"/>
+      <c r="G51" s="216"/>
+      <c r="H51" s="216"/>
+      <c r="I51" s="216"/>
+      <c r="J51" s="218"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="62"/>
-      <c r="B52" s="62"/>
-      <c r="C52" s="62"/>
-      <c r="D52" s="62"/>
-      <c r="E52" s="62"/>
-      <c r="F52" s="62"/>
-      <c r="G52" s="62"/>
-      <c r="H52" s="62"/>
-      <c r="I52" s="62"/>
-      <c r="J52" s="62"/>
+      <c r="A52" s="58"/>
+      <c r="B52" s="58"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="58"/>
+      <c r="E52" s="58"/>
+      <c r="F52" s="58"/>
+      <c r="G52" s="58"/>
+      <c r="H52" s="58"/>
+      <c r="I52" s="58"/>
+      <c r="J52" s="58"/>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="62"/>
-      <c r="B53" s="62"/>
-      <c r="C53" s="62"/>
-      <c r="D53" s="62"/>
-      <c r="E53" s="62"/>
-      <c r="F53" s="62"/>
-      <c r="G53" s="62"/>
-      <c r="H53" s="62"/>
-      <c r="I53" s="62"/>
-      <c r="J53" s="62"/>
+      <c r="A53" s="58"/>
+      <c r="B53" s="58"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
+      <c r="H53" s="58"/>
+      <c r="I53" s="58"/>
+      <c r="J53" s="58"/>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="62"/>
-      <c r="B54" s="62"/>
-      <c r="C54" s="62"/>
-      <c r="D54" s="62"/>
-      <c r="E54" s="62"/>
-      <c r="F54" s="62"/>
-      <c r="G54" s="62"/>
-      <c r="H54" s="62"/>
-      <c r="I54" s="62"/>
-      <c r="J54" s="62"/>
+      <c r="A54" s="58"/>
+      <c r="B54" s="58"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="58"/>
+      <c r="I54" s="58"/>
+      <c r="J54" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J10"/>
+    <mergeCell ref="A12:J44"/>
+    <mergeCell ref="A45:J49"/>
+    <mergeCell ref="A50:E51"/>
+    <mergeCell ref="F50:J51"/>
     <mergeCell ref="A1:A6"/>
     <mergeCell ref="B1:H6"/>
     <mergeCell ref="I1:J1"/>
@@ -8548,15 +8545,10 @@
     <mergeCell ref="I4:J4"/>
     <mergeCell ref="I5:J5"/>
     <mergeCell ref="I6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J10"/>
-    <mergeCell ref="A12:J44"/>
-    <mergeCell ref="A45:J49"/>
-    <mergeCell ref="A50:E51"/>
-    <mergeCell ref="F50:J51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="94" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/tedarikci-proses-kontrol-formu.xlsx
+++ b/tedarikci-proses-kontrol-formu.xlsx
@@ -7767,6 +7767,9 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
   <mergeCells count="56">
+    <mergeCell ref="Z14:AA14"/>
+    <mergeCell ref="Z13:AA13"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="Y20:Z20"/>
     <mergeCell ref="Y21:Z21"/>
     <mergeCell ref="Y22:Z22"/>

--- a/tedarikci-proses-kontrol-formu.xlsx
+++ b/tedarikci-proses-kontrol-formu.xlsx
@@ -6680,6 +6680,7 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" deleteRows="0" selectLockedCells="1" sort="0" autoFilter="0"/>
   <mergeCells count="58">
+    <mergeCell ref="F14:G14"/>
     <mergeCell ref="J24:K24"/>
     <mergeCell ref="J25:K25"/>
     <mergeCell ref="J26:K26"/>
